--- a/engine/techniques/kronos_forecast/resources/templates/kronos_forecast_input_template.xlsx
+++ b/engine/techniques/kronos_forecast/resources/templates/kronos_forecast_input_template.xlsx
@@ -53,7 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,13 +63,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -81,9 +96,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -626,19 +641,19 @@
       <c r="A17" s="6" t="n">
         <v>45814</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="4" t="n">
         <v>90.26361121560964</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>90.34061328714786</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>89.97486446232391</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>90.00373840332031</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="4" t="n">
         <v>7624200</v>
       </c>
     </row>
@@ -646,19 +661,19 @@
       <c r="A18" s="6" t="n">
         <v>45817</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="4" t="n">
         <v>90.01335426202118</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="4" t="n">
         <v>90.28286150074972</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="4" t="n">
         <v>90.00373451098622</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="4" t="n">
         <v>90.1673583984375</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="4" t="n">
         <v>6061200</v>
       </c>
     </row>
@@ -666,19 +681,19 @@
       <c r="A19" s="6" t="n">
         <v>45818</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="4" t="n">
         <v>90.45611502185869</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="4" t="n">
         <v>90.49460871372196</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>90.22510881074938</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="4" t="n">
         <v>90.32135772705078</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="4" t="n">
         <v>5579900</v>
       </c>
     </row>
@@ -686,19 +701,19 @@
       <c r="A20" s="6" t="n">
         <v>45819</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="4" t="n">
         <v>90.4945993178188</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="4" t="n">
         <v>90.73522525524936</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>90.41760459876488</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="4" t="n">
         <v>90.6967315673828</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="4" t="n">
         <v>6594900</v>
       </c>
     </row>
@@ -706,19 +721,19 @@
       <c r="A21" s="6" t="n">
         <v>45820</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="4" t="n">
         <v>91.04322624525842</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="4" t="n">
         <v>91.1009814637531</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>90.87960237005198</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>91.0913543701172</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="4" t="n">
         <v>7795400</v>
       </c>
     </row>
@@ -726,19 +741,19 @@
       <c r="A22" s="6" t="n">
         <v>45821</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="4" t="n">
         <v>90.88924367206336</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="4" t="n">
         <v>90.95661865140561</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>90.51386773811063</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="4" t="n">
         <v>90.75449371337891</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="4" t="n">
         <v>9195200</v>
       </c>
     </row>
@@ -746,19 +761,19 @@
       <c r="A23" s="6" t="n">
         <v>45824</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="4" t="n">
         <v>90.64861015421847</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="4" t="n">
         <v>90.84110798108718</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>90.4753591727081</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
         <v>90.49460601806641</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="4" t="n">
         <v>7508400</v>
       </c>
     </row>
@@ -766,19 +781,19 @@
       <c r="A24" s="6" t="n">
         <v>45825</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="4" t="n">
         <v>90.72561827062786</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="4" t="n">
         <v>90.97586399357584</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>90.5812412191906</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="4" t="n">
         <v>90.93737030029295</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="4" t="n">
         <v>5285000</v>
       </c>
     </row>
@@ -786,19 +801,19 @@
       <c r="A25" s="6" t="n">
         <v>45826</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="4" t="n">
         <v>91.09136610629736</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="4" t="n">
         <v>91.28386394389206</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>90.84111304276681</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="4" t="n">
         <v>90.9951171875</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="4" t="n">
         <v>6732400</v>
       </c>
     </row>
@@ -806,19 +821,19 @@
       <c r="A26" s="6" t="n">
         <v>45828</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="4" t="n">
         <v>90.81223810868332</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="4" t="n">
         <v>91.18761402821455</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>90.75449022670058</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
         <v>91.05286407470705</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="4" t="n">
         <v>6261700</v>
       </c>
     </row>
@@ -826,19 +841,19 @@
       <c r="A27" s="6" t="n">
         <v>45831</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="4" t="n">
         <v>91.31274314653469</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="4" t="n">
         <v>91.66886487229723</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>91.24536817058052</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
         <v>91.37049102783205</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="4" t="n">
         <v>9310300</v>
       </c>
     </row>
@@ -846,19 +861,19 @@
       <c r="A28" s="6" t="n">
         <v>45832</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="4" t="n">
         <v>91.28386078667523</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="4" t="n">
         <v>91.73623876703049</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>91.24536709514511</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>91.68811798095705</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="4" t="n">
         <v>7694500</v>
       </c>
     </row>
@@ -866,19 +881,19 @@
       <c r="A29" s="6" t="n">
         <v>45833</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="4" t="n">
         <v>91.51486389291787</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="4" t="n">
         <v>91.76510959598669</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>91.41861498071285</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>91.72661590576172</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="4" t="n">
         <v>6393300</v>
       </c>
     </row>
@@ -886,19 +901,19 @@
       <c r="A30" s="6" t="n">
         <v>45834</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="4" t="n">
         <v>91.89987435141001</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="4" t="n">
         <v>92.0634982497842</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>91.77474414638814</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="4" t="n">
         <v>92.05387115478516</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="4" t="n">
         <v>7131900</v>
       </c>
     </row>
@@ -906,19 +921,19 @@
       <c r="A31" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="4" t="n">
         <v>91.81324005126952</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="4" t="n">
         <v>92.09236704406506</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>91.75549217114684</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>91.81324005126952</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="4" t="n">
         <v>8402400</v>
       </c>
     </row>
@@ -926,19 +941,19 @@
       <c r="A32" s="6" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="4" t="n">
         <v>92.01536171227636</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="4" t="n">
         <v>92.21748662886024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>91.88061176788712</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="4" t="n">
         <v>92.17898559570312</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="4" t="n">
         <v>10542300</v>
       </c>
     </row>
@@ -946,19 +961,19 @@
       <c r="A33" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="4" t="n">
         <v>92.13359949434631</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="4" t="n">
         <v>92.2205035986628</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>91.84393633542214</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>92.00807952880859</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="4" t="n">
         <v>10659800</v>
       </c>
     </row>
@@ -966,19 +981,19 @@
       <c r="A34" s="6" t="n">
         <v>45840</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="4" t="n">
         <v>91.71841752854527</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="4" t="n">
         <v>91.86325280478364</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>91.6604863647012</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>91.81497192382812</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="4" t="n">
         <v>6026200</v>
       </c>
     </row>
@@ -986,19 +1001,19 @@
       <c r="A35" s="6" t="n">
         <v>45841</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="4" t="n">
         <v>91.53496875245619</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="4" t="n">
         <v>91.59289991779704</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>91.38047582270951</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>91.49634552001952</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="4" t="n">
         <v>7398900</v>
       </c>
     </row>
@@ -1006,19 +1021,19 @@
       <c r="A36" s="6" t="n">
         <v>45845</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="4" t="n">
         <v>91.35150030328847</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="4" t="n">
         <v>91.36115795200422</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>91.12941858259164</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="4" t="n">
         <v>91.2066650390625</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="4" t="n">
         <v>8518600</v>
       </c>
     </row>
@@ -1026,19 +1041,19 @@
       <c r="A37" s="6" t="n">
         <v>45846</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="4" t="n">
         <v>90.96528301126028</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="4" t="n">
         <v>91.08115270567748</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>90.9170094968909</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="4" t="n">
         <v>91.07149505615234</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="4" t="n">
         <v>5282800</v>
       </c>
     </row>
@@ -1046,19 +1061,19 @@
       <c r="A38" s="6" t="n">
         <v>45847</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="4" t="n">
         <v>91.2066650310782</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="4" t="n">
         <v>91.55426671853913</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="4" t="n">
         <v>91.2066650310782</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="4" t="n">
         <v>91.54460906982422</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="4" t="n">
         <v>6900800</v>
       </c>
     </row>
@@ -1066,19 +1081,19 @@
       <c r="A39" s="6" t="n">
         <v>45848</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="4" t="n">
         <v>91.47703022048702</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="4" t="n">
         <v>91.5156534529237</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>91.31288700760244</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>91.49634552001952</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="4" t="n">
         <v>4451900</v>
       </c>
     </row>
@@ -1086,19 +1101,19 @@
       <c r="A40" s="6" t="n">
         <v>45849</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="4" t="n">
         <v>91.18736475056954</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="4" t="n">
         <v>91.2163303325168</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>91.02321417515481</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="4" t="n">
         <v>91.07149505615234</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="4" t="n">
         <v>6004300</v>
       </c>
     </row>
@@ -1106,19 +1121,19 @@
       <c r="A41" s="6" t="n">
         <v>45852</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="4" t="n">
         <v>91.07148302861764</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="4" t="n">
         <v>91.20666063760449</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>90.92664777138113</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>91.03285980224609</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="4" t="n">
         <v>5101600</v>
       </c>
     </row>
@@ -1126,19 +1141,19 @@
       <c r="A42" s="6" t="n">
         <v>45853</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="4" t="n">
         <v>91.13908508329943</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="4" t="n">
         <v>91.14874273295318</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>90.62734015107434</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="4" t="n">
         <v>90.67562103271484</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="4" t="n">
         <v>5628100</v>
       </c>
     </row>
@@ -1146,19 +1161,19 @@
       <c r="A43" s="6" t="n">
         <v>45854</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="4" t="n">
         <v>90.82044658682167</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="4" t="n">
         <v>90.99424744293636</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>90.69492661109422</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>90.92665863037109</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="4" t="n">
         <v>12786300</v>
       </c>
     </row>
@@ -1166,19 +1181,19 @@
       <c r="A44" s="6" t="n">
         <v>45855</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="4" t="n">
         <v>90.97494391443792</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="4" t="n">
         <v>91.08115596312859</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>90.82045098302299</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="4" t="n">
         <v>90.89769744873048</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="4" t="n">
         <v>4747200</v>
       </c>
     </row>
@@ -1186,19 +1201,19 @@
       <c r="A45" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="4" t="n">
         <v>91.15838506502314</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="4" t="n">
         <v>91.2259738679858</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>91.0521730365637</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>91.1487274169922</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="4" t="n">
         <v>4035000</v>
       </c>
     </row>
@@ -1206,19 +1221,19 @@
       <c r="A46" s="6" t="n">
         <v>45859</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="4" t="n">
         <v>91.53495788667372</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="4" t="n">
         <v>91.63151227298958</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>91.41908820311816</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="4" t="n">
         <v>91.46736907958984</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="4" t="n">
         <v>5232300</v>
       </c>
     </row>
@@ -1226,19 +1241,19 @@
       <c r="A47" s="6" t="n">
         <v>45860</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="4" t="n">
         <v>91.5639375308982</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="4" t="n">
         <v>91.78601191687449</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>91.54462223069154</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
         <v>91.72808074951172</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="4" t="n">
         <v>6098000</v>
       </c>
     </row>
@@ -1246,19 +1261,19 @@
       <c r="A48" s="6" t="n">
         <v>45861</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="4" t="n">
         <v>91.51563495130084</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="4" t="n">
         <v>91.5735661049298</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>91.35149177160092</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
         <v>91.39977264404295</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="4" t="n">
         <v>5074000</v>
       </c>
     </row>
@@ -1266,19 +1281,19 @@
       <c r="A49" s="6" t="n">
         <v>45862</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="4" t="n">
         <v>91.08115152230759</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="4" t="n">
         <v>91.36116442187333</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>91.07149387290794</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>91.2646026611328</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="4" t="n">
         <v>5867400</v>
       </c>
     </row>
@@ -1286,19 +1301,19 @@
       <c r="A50" s="6" t="n">
         <v>45863</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="4" t="n">
         <v>91.235630612188</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="4" t="n">
         <v>91.47702026367188</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>91.19700738395528</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="4" t="n">
         <v>91.47702026367188</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="4" t="n">
         <v>3614000</v>
       </c>
     </row>
@@ -1306,19 +1321,19 @@
       <c r="A51" s="6" t="n">
         <v>45866</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="4" t="n">
         <v>91.31288470607257</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="4" t="n">
         <v>91.38047351947608</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>91.2356382431462</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>91.27426147460938</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="4" t="n">
         <v>5073200</v>
       </c>
     </row>
@@ -1326,19 +1341,19 @@
       <c r="A52" s="6" t="n">
         <v>45867</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="4" t="n">
         <v>91.40944573075043</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="4" t="n">
         <v>91.87291717529295</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>91.39013779693266</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="4" t="n">
         <v>91.87291717529295</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="4" t="n">
         <v>7864000</v>
       </c>
     </row>
@@ -1346,19 +1361,19 @@
       <c r="A53" s="6" t="n">
         <v>45868</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="4" t="n">
         <v>91.55427551269533</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="4" t="n">
         <v>91.80532283700396</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>91.48668669845394</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="4" t="n">
         <v>91.55427551269533</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="4" t="n">
         <v>7425600</v>
       </c>
     </row>
@@ -1366,19 +1381,19 @@
       <c r="A54" s="6" t="n">
         <v>45869</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="4" t="n">
         <v>91.699104312396</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="4" t="n">
         <v>91.8535898626214</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>91.5928922737164</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="4" t="n">
         <v>91.63151550292967</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="4" t="n">
         <v>10411800</v>
       </c>
     </row>
@@ -1386,19 +1401,19 @@
       <c r="A55" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="4" t="n">
         <v>92.37647453039052</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="4" t="n">
         <v>92.73490100980582</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>92.35709613112816</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="4" t="n">
         <v>92.68646240234376</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="4" t="n">
         <v>11870100</v>
       </c>
     </row>
@@ -1406,19 +1421,19 @@
       <c r="A56" s="6" t="n">
         <v>45873</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="4" t="n">
         <v>92.77363615412176</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="4" t="n">
         <v>92.8511349640423</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>92.54114711505346</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="4" t="n">
         <v>92.81238555908205</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="4" t="n">
         <v>8449500</v>
       </c>
     </row>
@@ -1426,19 +1441,19 @@
       <c r="A57" s="6" t="n">
         <v>45874</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="4" t="n">
         <v>92.64770568390176</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="4" t="n">
         <v>92.86082371480806</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>92.62833467686175</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="4" t="n">
         <v>92.74457550048828</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="4" t="n">
         <v>8218700</v>
       </c>
     </row>
@@ -1446,19 +1461,19 @@
       <c r="A58" s="6" t="n">
         <v>45875</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="4" t="n">
         <v>92.60894820773012</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="4" t="n">
         <v>92.7251964119182</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>92.27958938190278</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="4" t="n">
         <v>92.6767578125</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="4" t="n">
         <v>10107500</v>
       </c>
     </row>
@@ -1466,19 +1481,19 @@
       <c r="A59" s="6" t="n">
         <v>45876</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="4" t="n">
         <v>92.67676499332474</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="4" t="n">
         <v>92.77363480897422</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>92.54114577327684</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="4" t="n">
         <v>92.60895538330078</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="4" t="n">
         <v>5725900</v>
       </c>
     </row>
@@ -1486,19 +1501,19 @@
       <c r="A60" s="6" t="n">
         <v>45877</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="4" t="n">
         <v>92.48302388263993</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="4" t="n">
         <v>92.48302388263993</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>92.3474046647614</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="4" t="n">
         <v>92.39583587646484</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="4" t="n">
         <v>5623800</v>
       </c>
     </row>
@@ -1506,19 +1521,19 @@
       <c r="A61" s="6" t="n">
         <v>45880</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="4" t="n">
         <v>92.4636382502884</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="4" t="n">
         <v>92.55082624964116</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>92.37645764162812</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="4" t="n">
         <v>92.42489624023438</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="4" t="n">
         <v>4920200</v>
       </c>
     </row>
@@ -1526,19 +1541,19 @@
       <c r="A62" s="6" t="n">
         <v>45881</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="4" t="n">
         <v>92.30864777188422</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="4" t="n">
         <v>92.405517578125</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>92.20208876781165</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="4" t="n">
         <v>92.405517578125</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="4" t="n">
         <v>6724600</v>
       </c>
     </row>
@@ -1546,19 +1561,19 @@
       <c r="A63" s="6" t="n">
         <v>45882</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="4" t="n">
         <v>92.6670765642546</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="4" t="n">
         <v>92.83175597816179</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>92.64769816809334</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="4" t="n">
         <v>92.73488616943359</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="4" t="n">
         <v>5925200</v>
       </c>
     </row>
@@ -1566,19 +1581,19 @@
       <c r="A64" s="6" t="n">
         <v>45883</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="4" t="n">
         <v>92.57988634685496</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="4" t="n">
         <v>92.60894654970856</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>92.36676833833866</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="4" t="n">
         <v>92.43457794189452</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="4" t="n">
         <v>5527500</v>
       </c>
     </row>
@@ -1586,19 +1601,19 @@
       <c r="A65" s="6" t="n">
         <v>45884</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="4" t="n">
         <v>92.39582744076009</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="4" t="n">
         <v>92.45395523646744</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>92.19239863251528</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="4" t="n">
         <v>92.25052642822266</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="4" t="n">
         <v>7428500</v>
       </c>
     </row>
@@ -1606,19 +1621,19 @@
       <c r="A66" s="6" t="n">
         <v>45887</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="4" t="n">
         <v>92.3183505917184</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="4" t="n">
         <v>92.32803240028636</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>92.07617234503572</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="4" t="n">
         <v>92.16335296630859</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="4" t="n">
         <v>9669600</v>
       </c>
     </row>
@@ -1626,19 +1641,19 @@
       <c r="A67" s="6" t="n">
         <v>45888</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="4" t="n">
         <v>92.29896606236493</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="4" t="n">
         <v>92.43458528024344</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>92.28927686374701</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="4" t="n">
         <v>92.39583587646484</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="4" t="n">
         <v>6499300</v>
       </c>
     </row>
@@ -1646,19 +1661,19 @@
       <c r="A68" s="6" t="n">
         <v>45889</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="4" t="n">
         <v>92.39582915624329</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="4" t="n">
         <v>92.61863636409146</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>92.37645815110946</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="4" t="n">
         <v>92.5314483642578</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="4" t="n">
         <v>6270700</v>
       </c>
     </row>
@@ -1666,19 +1681,19 @@
       <c r="A69" s="6" t="n">
         <v>45890</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="4" t="n">
         <v>92.40551653294666</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="4" t="n">
         <v>92.4539551308654</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>92.13427812226342</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="4" t="n">
         <v>92.2602081298828</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="4" t="n">
         <v>5351300</v>
       </c>
     </row>
@@ -1686,19 +1701,19 @@
       <c r="A70" s="6" t="n">
         <v>45891</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="4" t="n">
         <v>92.41519400345044</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="4" t="n">
         <v>92.88017196541952</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>92.3861338046638</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="4" t="n">
         <v>92.77361297607422</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="4" t="n">
         <v>10867700</v>
       </c>
     </row>
@@ -1706,19 +1721,19 @@
       <c r="A71" s="6" t="n">
         <v>45894</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="4" t="n">
         <v>92.60894772644244</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="4" t="n">
         <v>92.71550673205458</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>92.54113812202496</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="4" t="n">
         <v>92.58957672119141</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="4" t="n">
         <v>9936400</v>
       </c>
     </row>
@@ -1726,19 +1741,19 @@
       <c r="A72" s="6" t="n">
         <v>45895</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="4" t="n">
         <v>92.66707717680109</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="4" t="n">
         <v>92.86081679553816</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>92.60894937862579</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="4" t="n">
         <v>92.83175659179688</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="4" t="n">
         <v>5871200</v>
       </c>
     </row>
@@ -1746,19 +1761,19 @@
       <c r="A73" s="6" t="n">
         <v>45896</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="4" t="n">
         <v>92.7058279877547</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="4" t="n">
         <v>93.00613403320312</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>92.64770757475526</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="4" t="n">
         <v>93.00613403320312</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="4" t="n">
         <v>5222800</v>
       </c>
     </row>
@@ -1766,19 +1781,19 @@
       <c r="A74" s="6" t="n">
         <v>45897</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="4" t="n">
         <v>92.97706768488661</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="4" t="n">
         <v>93.21924591064452</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>92.9383182818822</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="4" t="n">
         <v>93.21924591064452</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="4" t="n">
         <v>6544700</v>
       </c>
     </row>
@@ -1786,19 +1801,19 @@
       <c r="A75" s="6" t="n">
         <v>45898</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="4" t="n">
         <v>93.11268631659811</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="4" t="n">
         <v>93.21924532651931</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>93.02549831271126</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>93.14174652099609</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="4" t="n">
         <v>6818900</v>
       </c>
     </row>
@@ -1806,19 +1821,19 @@
       <c r="A76" s="6" t="n">
         <v>45902</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="4" t="n">
         <v>92.77632636850764</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="4" t="n">
         <v>92.94154536866878</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>92.7471709467038</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="4" t="n">
         <v>92.86380004882812</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="4" t="n">
         <v>8623200</v>
       </c>
     </row>
@@ -1826,19 +1841,19 @@
       <c r="A77" s="6" t="n">
         <v>45903</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="4" t="n">
         <v>92.87349817544307</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="4" t="n">
         <v>93.32056520373892</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>92.87349817544307</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="4" t="n">
         <v>93.18450164794922</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="4" t="n">
         <v>7586100</v>
       </c>
     </row>
@@ -1846,19 +1861,19 @@
       <c r="A78" s="6" t="n">
         <v>45904</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="4" t="n">
         <v>93.41776353905608</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="4" t="n">
         <v>93.6024169921875</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>93.30113445162468</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="4" t="n">
         <v>93.6024169921875</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="4" t="n">
         <v>6395300</v>
       </c>
     </row>
@@ -1866,19 +1881,19 @@
       <c r="A79" s="6" t="n">
         <v>45905</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="4" t="n">
         <v>94.1855541321566</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="4" t="n">
         <v>94.29245485933237</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>94.0592041015625</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="4" t="n">
         <v>94.0592041015625</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="4" t="n">
         <v>9566300</v>
       </c>
     </row>
@@ -1886,19 +1901,19 @@
       <c r="A80" s="6" t="n">
         <v>45908</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="4" t="n">
         <v>94.29245079485916</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="4" t="n">
         <v>94.36048257189736</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>94.19526360121996</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="4" t="n">
         <v>94.35076904296876</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="4" t="n">
         <v>7599600</v>
       </c>
     </row>
@@ -1906,19 +1921,19 @@
       <c r="A81" s="6" t="n">
         <v>45909</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="4" t="n">
         <v>94.30217533378048</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="4" t="n">
         <v>94.40908347533154</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="4" t="n">
         <v>94.03976915946016</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="4" t="n">
         <v>94.12723541259766</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="4" t="n">
         <v>8223100</v>
       </c>
     </row>
@@ -1926,19 +1941,19 @@
       <c r="A82" s="6" t="n">
         <v>45910</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="4" t="n">
         <v>94.32161775311396</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="4" t="n">
         <v>94.49655767528152</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>94.23414408457624</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="4" t="n">
         <v>94.3799285888672</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="4" t="n">
         <v>8864500</v>
       </c>
     </row>
@@ -1946,19 +1961,19 @@
       <c r="A83" s="6" t="n">
         <v>45911</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="4" t="n">
         <v>94.50626917146556</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="4" t="n">
         <v>94.72008545117126</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>94.49655564232094</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="4" t="n">
         <v>94.52571105957033</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="4" t="n">
         <v>8554300</v>
       </c>
     </row>
@@ -1966,19 +1981,19 @@
       <c r="A84" s="6" t="n">
         <v>45912</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="4" t="n">
         <v>94.30218334016776</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="4" t="n">
         <v>94.31190428519989</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>94.1175224591002</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="4" t="n">
         <v>94.25359344482422</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="4" t="n">
         <v>36502700</v>
       </c>
     </row>
@@ -1986,19 +2001,19 @@
       <c r="A85" s="6" t="n">
         <v>45915</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="4" t="n">
         <v>94.41880907945216</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="4" t="n">
         <v>94.48684086244155</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>94.37021177092764</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="4" t="n">
         <v>94.40908813476562</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="4" t="n">
         <v>4990100</v>
       </c>
     </row>
@@ -2006,19 +2021,19 @@
       <c r="A86" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="4" t="n">
         <v>94.41880207776036</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="4" t="n">
         <v>94.55486563364929</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="4" t="n">
         <v>94.3799257168053</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="4" t="n">
         <v>94.46739196777344</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="4" t="n">
         <v>5847700</v>
       </c>
     </row>
@@ -2026,19 +2041,19 @@
       <c r="A87" s="6" t="n">
         <v>45917</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="4" t="n">
         <v>94.56459563659998</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="4" t="n">
         <v>94.77840451997352</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>94.14668398493301</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="4" t="n">
         <v>94.2633056640625</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="4" t="n">
         <v>10701700</v>
       </c>
     </row>
@@ -2046,19 +2061,19 @@
       <c r="A88" s="6" t="n">
         <v>45918</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="4" t="n">
         <v>93.93285129510748</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="4" t="n">
         <v>94.08834931178146</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>93.7967877499276</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="4" t="n">
         <v>93.95228576660156</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="4" t="n">
         <v>7589200</v>
       </c>
     </row>
@@ -2066,19 +2081,19 @@
       <c r="A89" s="6" t="n">
         <v>45919</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="4" t="n">
         <v>93.90371572990716</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="4" t="n">
         <v>93.9814610472245</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>93.78708663156814</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="4" t="n">
         <v>93.91342926025391</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89" s="4" t="n">
         <v>5528800</v>
       </c>
     </row>
@@ -2086,19 +2101,19 @@
       <c r="A90" s="6" t="n">
         <v>45922</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="4" t="n">
         <v>93.91341734133194</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="4" t="n">
         <v>93.94258017339702</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>93.74819836750174</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="4" t="n">
         <v>93.75791931152344</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90" s="4" t="n">
         <v>5282700</v>
       </c>
     </row>
@@ -2106,19 +2121,19 @@
       <c r="A91" s="6" t="n">
         <v>45923</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="4" t="n">
         <v>93.89398209541996</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="4" t="n">
         <v>94.03004565097294</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="4" t="n">
         <v>93.7773530128427</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="4" t="n">
         <v>94.02032470703124</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="4" t="n">
         <v>7077500</v>
       </c>
     </row>
@@ -2126,19 +2141,19 @@
       <c r="A92" s="6" t="n">
         <v>45924</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="4" t="n">
         <v>93.9037027152396</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="4" t="n">
         <v>93.9134162442401</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>93.72876279943137</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="4" t="n">
         <v>93.76763916015624</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92" s="4" t="n">
         <v>5419700</v>
       </c>
     </row>
@@ -2146,19 +2161,19 @@
       <c r="A93" s="6" t="n">
         <v>45925</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="4" t="n">
         <v>93.55383169713518</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="4" t="n">
         <v>93.61214253626208</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>93.39832623958571</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="4" t="n">
         <v>93.56354522705078</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93" s="4" t="n">
         <v>6517500</v>
       </c>
     </row>
@@ -2166,19 +2181,19 @@
       <c r="A94" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="4" t="n">
         <v>93.5441090323086</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="4" t="n">
         <v>93.71904896138092</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="4" t="n">
         <v>93.42747994129098</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="4" t="n">
         <v>93.51495361328124</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94" s="4" t="n">
         <v>7295300</v>
       </c>
     </row>
@@ -2186,19 +2201,19 @@
       <c r="A95" s="6" t="n">
         <v>45929</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="4" t="n">
         <v>93.63158102260439</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="4" t="n">
         <v>93.83568379810984</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>93.62186749227264</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="4" t="n">
         <v>93.78708648681641</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95" s="4" t="n">
         <v>6357500</v>
       </c>
     </row>
@@ -2206,19 +2221,19 @@
       <c r="A96" s="6" t="n">
         <v>45930</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="4" t="n">
         <v>93.86482854779052</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="4" t="n">
         <v>94.03976846768649</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>93.70932310125733</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="4" t="n">
         <v>93.74819946289062</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96" s="4" t="n">
         <v>9257800</v>
       </c>
     </row>
@@ -2226,19 +2241,19 @@
       <c r="A97" s="6" t="n">
         <v>45931</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="4" t="n">
         <v>94.13229616627872</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="4" t="n">
         <v>94.20053593607309</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>93.91782619333158</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="4" t="n">
         <v>94.06405639648438</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97" s="4" t="n">
         <v>8347000</v>
       </c>
     </row>
@@ -2246,19 +2261,19 @@
       <c r="A98" s="6" t="n">
         <v>45932</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="4" t="n">
         <v>94.02505001762906</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="4" t="n">
         <v>94.2200260778786</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>93.9665609183423</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="4" t="n">
         <v>94.16152954101562</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98" s="4" t="n">
         <v>9420600</v>
       </c>
     </row>
@@ -2266,19 +2281,19 @@
       <c r="A99" s="6" t="n">
         <v>45933</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="4" t="n">
         <v>94.17127170566584</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="4" t="n">
         <v>94.21026691419692</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>93.95680177753262</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="4" t="n">
         <v>93.97630310058594</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99" s="4" t="n">
         <v>5154300</v>
       </c>
     </row>
@@ -2286,19 +2301,19 @@
       <c r="A100" s="6" t="n">
         <v>45936</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="4" t="n">
         <v>93.75210758614294</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="4" t="n">
         <v>93.91783168854346</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>93.6936184764904</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="4" t="n">
         <v>93.703369140625</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="4" t="n">
         <v>6319600</v>
       </c>
     </row>
@@ -2306,19 +2321,19 @@
       <c r="A101" s="6" t="n">
         <v>45937</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="4" t="n">
         <v>93.82033887761988</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="4" t="n">
         <v>94.06405339590786</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>93.76184977325536</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="4" t="n">
         <v>93.93732452392578</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101" s="4" t="n">
         <v>5119900</v>
       </c>
     </row>
@@ -2326,19 +2341,19 @@
       <c r="A102" s="6" t="n">
         <v>45938</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="4" t="n">
         <v>94.11280612944996</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="4" t="n">
         <v>94.13230001979906</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="4" t="n">
         <v>93.898336147723</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="4" t="n">
         <v>93.95682525634766</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102" s="4" t="n">
         <v>5141900</v>
       </c>
     </row>
@@ -2346,19 +2361,19 @@
       <c r="A103" s="6" t="n">
         <v>45939</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="4" t="n">
         <v>93.8690864329882</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="4" t="n">
         <v>93.93732620182466</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>93.81059732757896</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="4" t="n">
         <v>93.88858032226562</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103" s="4" t="n">
         <v>7130600</v>
       </c>
     </row>
@@ -2366,19 +2381,19 @@
       <c r="A104" s="6" t="n">
         <v>45940</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="4" t="n">
         <v>94.22003792139596</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="4" t="n">
         <v>94.58073066243853</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>94.1420474874927</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="4" t="n">
         <v>94.47350311279295</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" s="4" t="n">
         <v>10417700</v>
       </c>
     </row>
@@ -2386,19 +2401,19 @@
       <c r="A105" s="6" t="n">
         <v>45943</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="4" t="n">
         <v>94.46374295490376</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="4" t="n">
         <v>94.55147660604422</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>94.34675731580673</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="4" t="n">
         <v>94.52223205566406</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" s="4" t="n">
         <v>5607600</v>
       </c>
     </row>
@@ -2406,19 +2421,19 @@
       <c r="A106" s="6" t="n">
         <v>45944</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="4" t="n">
         <v>94.61970762920625</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="4" t="n">
         <v>94.79518235285455</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>94.54172464792144</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="4" t="n">
         <v>94.76593780517578</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" s="4" t="n">
         <v>7650600</v>
       </c>
     </row>
@@ -2426,19 +2441,19 @@
       <c r="A107" s="6" t="n">
         <v>45945</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="4" t="n">
         <v>94.76594927395068</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="4" t="n">
         <v>94.88293491639932</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="4" t="n">
         <v>94.58072386613452</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="4" t="n">
         <v>94.65871429443359</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" s="4" t="n">
         <v>7769300</v>
       </c>
     </row>
@@ -2446,19 +2461,19 @@
       <c r="A108" s="6" t="n">
         <v>45946</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="4" t="n">
         <v>94.58072347283004</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="4" t="n">
         <v>95.13639225639128</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="4" t="n">
         <v>94.56122958462464</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="4" t="n">
         <v>95.09740447998048</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" s="4" t="n">
         <v>11627200</v>
       </c>
     </row>
@@ -2466,19 +2481,19 @@
       <c r="A109" s="6" t="n">
         <v>45947</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="4" t="n">
         <v>95.00966127235247</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="4" t="n">
         <v>95.02916259769999</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="4" t="n">
         <v>94.82443586943327</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="4" t="n">
         <v>94.94142150878906</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" s="4" t="n">
         <v>12491000</v>
       </c>
     </row>
@@ -2486,19 +2501,19 @@
       <c r="A110" s="6" t="n">
         <v>45950</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="4" t="n">
         <v>94.999913615625</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="4" t="n">
         <v>95.07790404432993</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="4" t="n">
         <v>94.92193062449672</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="4" t="n">
         <v>95.06815338134766</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110" s="4" t="n">
         <v>10437800</v>
       </c>
     </row>
@@ -2506,19 +2521,19 @@
       <c r="A111" s="6" t="n">
         <v>45951</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="4" t="n">
         <v>95.23388623002488</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="4" t="n">
         <v>95.31186922224084</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="4" t="n">
         <v>95.17538968889198</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="4" t="n">
         <v>95.24362945556641</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111" s="4" t="n">
         <v>7642000</v>
       </c>
     </row>
@@ -2526,19 +2541,19 @@
       <c r="A112" s="6" t="n">
         <v>45952</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="4" t="n">
         <v>95.19489042173922</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="4" t="n">
         <v>95.31186862812235</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="4" t="n">
         <v>95.10714932937516</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="4" t="n">
         <v>95.26313018798828</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112" s="4" t="n">
         <v>6523500</v>
       </c>
     </row>
@@ -2546,19 +2561,19 @@
       <c r="A113" s="6" t="n">
         <v>45953</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="4" t="n">
         <v>95.06815771520796</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="4" t="n">
         <v>95.12665425819164</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="4" t="n">
         <v>94.93167817754096</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="4" t="n">
         <v>94.95117950439452</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113" s="4" t="n">
         <v>6138300</v>
       </c>
     </row>
@@ -2566,19 +2581,19 @@
       <c r="A114" s="6" t="n">
         <v>45954</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="4" t="n">
         <v>95.06816209555473</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="4" t="n">
         <v>95.08766342330682</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="4" t="n">
         <v>94.88294410737376</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="4" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="4" t="n">
         <v>7555200</v>
       </c>
     </row>
@@ -2586,19 +2601,19 @@
       <c r="A115" s="6" t="n">
         <v>45957</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="4" t="n">
         <v>94.89268733367248</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="4" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="4" t="n">
         <v>94.76595845359311</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="4" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115" s="4" t="n">
         <v>7272300</v>
       </c>
     </row>
@@ -2606,19 +2621,19 @@
       <c r="A116" s="6" t="n">
         <v>45958</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="4" t="n">
         <v>94.98041775782325</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="4" t="n">
         <v>95.17538638796626</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="4" t="n">
         <v>94.98041775782325</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="4" t="n">
         <v>95.12664794921876</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116" s="4" t="n">
         <v>5539600</v>
       </c>
     </row>
@@ -2626,19 +2641,19 @@
       <c r="A117" s="6" t="n">
         <v>45959</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="4" t="n">
         <v>95.07790112383094</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="4" t="n">
         <v>95.07790112383094</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="4" t="n">
         <v>94.46374325119211</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="4" t="n">
         <v>94.51248168945312</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117" s="4" t="n">
         <v>11223300</v>
       </c>
     </row>
@@ -2646,19 +2661,19 @@
       <c r="A118" s="6" t="n">
         <v>45960</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="4" t="n">
         <v>94.23953516407464</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="4" t="n">
         <v>94.52224491884976</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="4" t="n">
         <v>94.22004127369384</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="4" t="n">
         <v>94.37601470947266</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118" s="4" t="n">
         <v>8958800</v>
       </c>
     </row>
@@ -2666,19 +2681,19 @@
       <c r="A119" s="6" t="n">
         <v>45961</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="4" t="n">
         <v>94.43450987259448</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="4" t="n">
         <v>94.51249287055298</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="4" t="n">
         <v>94.35651943705868</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="4" t="n">
         <v>94.41500854492188</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119" s="4" t="n">
         <v>9739900</v>
       </c>
     </row>
@@ -2686,19 +2701,19 @@
       <c r="A120" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="4" t="n">
         <v>94.29178200291418</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="4" t="n">
         <v>94.42869127671588</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="4" t="n">
         <v>94.24289009712548</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="4" t="n">
         <v>94.37001800537109</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120" s="4" t="n">
         <v>8012500</v>
       </c>
     </row>
@@ -2706,19 +2721,19 @@
       <c r="A121" s="6" t="n">
         <v>45965</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="4" t="n">
         <v>94.43846635912506</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="4" t="n">
         <v>94.53625762519208</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="4" t="n">
         <v>94.41891109030981</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="4" t="n">
         <v>94.48736572265624</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121" s="4" t="n">
         <v>6119000</v>
       </c>
     </row>
@@ -2726,19 +2741,19 @@
       <c r="A122" s="6" t="n">
         <v>45966</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="4" t="n">
         <v>94.32112145232284</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="4" t="n">
         <v>94.34068418401856</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="4" t="n">
         <v>94.0081848941556</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="4" t="n">
         <v>94.03752899169922</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122" s="4" t="n">
         <v>11749200</v>
       </c>
     </row>
@@ -2746,19 +2761,19 @@
       <c r="A123" s="6" t="n">
         <v>45967</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="4" t="n">
         <v>94.38957300514608</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="4" t="n">
         <v>94.58516301072822</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="4" t="n">
         <v>94.37979910061384</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="4" t="n">
         <v>94.51670837402344</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123" s="4" t="n">
         <v>7665000</v>
       </c>
     </row>
@@ -2766,19 +2781,19 @@
       <c r="A124" s="6" t="n">
         <v>45968</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="4" t="n">
         <v>94.42868891372514</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="4" t="n">
         <v>94.7220701850991</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="4" t="n">
         <v>94.41891500940947</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="4" t="n">
         <v>94.55582427978516</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124" s="4" t="n">
         <v>11460300</v>
       </c>
     </row>
@@ -2786,19 +2801,19 @@
       <c r="A125" s="6" t="n">
         <v>45971</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="4" t="n">
         <v>94.43846941453818</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="4" t="n">
         <v>94.51670541432114</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="4" t="n">
         <v>94.37979614519874</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="4" t="n">
         <v>94.42868804931641</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125" s="4" t="n">
         <v>9097300</v>
       </c>
     </row>
@@ -2806,19 +2821,19 @@
       <c r="A126" s="6" t="n">
         <v>45972</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="4" t="n">
         <v>94.6731770472381</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="4" t="n">
         <v>94.75141305288368</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="4" t="n">
         <v>94.59494850258864</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="4" t="n">
         <v>94.72207641601562</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126" s="4" t="n">
         <v>4937700</v>
       </c>
     </row>
@@ -2826,19 +2841,19 @@
       <c r="A127" s="6" t="n">
         <v>45973</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="4" t="n">
         <v>94.67317591532679</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="4" t="n">
         <v>94.81008519307164</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="4" t="n">
         <v>94.64383927880949</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="4" t="n">
         <v>94.74163055419922</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127" s="4" t="n">
         <v>7188200</v>
       </c>
     </row>
@@ -2846,19 +2861,19 @@
       <c r="A128" s="6" t="n">
         <v>45974</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="4" t="n">
         <v>94.51671095245112</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="4" t="n">
         <v>94.66340159539052</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="4" t="n">
         <v>94.46781158447266</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="4" t="n">
         <v>94.46781158447266</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="4" t="n">
         <v>46965300</v>
       </c>
     </row>
@@ -2866,19 +2881,19 @@
       <c r="A129" s="6" t="n">
         <v>45975</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="4" t="n">
         <v>94.7416387318744</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="4" t="n">
         <v>94.79053810428807</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="4" t="n">
         <v>94.29179285745616</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="4" t="n">
         <v>94.31135559082033</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129" s="4" t="n">
         <v>11288500</v>
       </c>
     </row>
@@ -2886,19 +2901,19 @@
       <c r="A130" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="4" t="n">
         <v>94.4091334296328</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="4" t="n">
         <v>94.4873694299542</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="4" t="n">
         <v>94.360234064183</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="4" t="n">
         <v>94.41891479492188</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130" s="4" t="n">
         <v>6648500</v>
       </c>
     </row>
@@ -2906,19 +2921,19 @@
       <c r="A131" s="6" t="n">
         <v>45979</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="4" t="n">
         <v>94.7025216008121</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="4" t="n">
         <v>94.79053897977028</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="4" t="n">
         <v>94.4384843859311</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="4" t="n">
         <v>94.5753936767578</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131" s="4" t="n">
         <v>8769000</v>
       </c>
     </row>
@@ -2926,19 +2941,19 @@
       <c r="A132" s="6" t="n">
         <v>45980</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="4" t="n">
         <v>94.67318104289504</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="4" t="n">
         <v>94.72208041373636</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="4" t="n">
         <v>94.46781711515514</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="4" t="n">
         <v>94.50693511962891</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132" s="4" t="n">
         <v>13075900</v>
       </c>
     </row>
@@ -2946,19 +2961,19 @@
       <c r="A133" s="6" t="n">
         <v>45981</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="4" t="n">
         <v>94.60471430687321</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="4" t="n">
         <v>94.81007820836116</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="4" t="n">
         <v>94.56559630739994</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="4" t="n">
         <v>94.73184967041016</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133" s="4" t="n">
         <v>9076400</v>
       </c>
     </row>
@@ -2966,19 +2981,19 @@
       <c r="A134" s="6" t="n">
         <v>45982</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="4" t="n">
         <v>95.04479217529295</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="4" t="n">
         <v>95.08391017722336</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="4" t="n">
         <v>94.8589835313726</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="4" t="n">
         <v>95.04479217529295</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134" s="4" t="n">
         <v>12551100</v>
       </c>
     </row>
@@ -2986,19 +3001,19 @@
       <c r="A135" s="6" t="n">
         <v>45985</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="4" t="n">
         <v>95.14258300811166</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="4" t="n">
         <v>95.21103764592318</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="4" t="n">
         <v>95.03501036855128</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="4" t="n">
         <v>95.19147491455078</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135" s="4" t="n">
         <v>6903900</v>
       </c>
     </row>
@@ -3006,19 +3021,19 @@
       <c r="A136" s="6" t="n">
         <v>45986</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="4" t="n">
         <v>95.28927567886736</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="4" t="n">
         <v>95.54353150415614</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="4" t="n">
         <v>95.27949431297284</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="4" t="n">
         <v>95.43595886230467</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136" s="4" t="n">
         <v>9193400</v>
       </c>
     </row>
@@ -3026,19 +3041,19 @@
       <c r="A137" s="6" t="n">
         <v>45987</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="4" t="n">
         <v>95.32839711051984</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="4" t="n">
         <v>95.51419830322266</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="4" t="n">
         <v>95.18170646080978</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="4" t="n">
         <v>95.51419830322266</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137" s="4" t="n">
         <v>7747100</v>
       </c>
     </row>
@@ -3046,19 +3061,19 @@
       <c r="A138" s="6" t="n">
         <v>45989</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="4" t="n">
         <v>95.475074075923</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="4" t="n">
         <v>95.49463680714058</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="4" t="n">
         <v>95.24037352828309</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="4" t="n">
         <v>95.3479461669922</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138" s="4" t="n">
         <v>7798000</v>
       </c>
     </row>
@@ -3066,19 +3081,19 @@
       <c r="A139" s="6" t="n">
         <v>45992</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="4" t="n">
         <v>94.91442069171418</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" s="4" t="n">
         <v>94.98307813424096</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="4" t="n">
         <v>94.82615004407975</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="4" t="n">
         <v>94.83596038818359</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139" s="4" t="n">
         <v>9898100</v>
       </c>
     </row>
@@ -3086,19 +3101,19 @@
       <c r="A140" s="6" t="n">
         <v>45993</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="4" t="n">
         <v>94.8065372283578</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="4" t="n">
         <v>94.96346531916352</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="4" t="n">
         <v>94.74768264659312</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="4" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="4" t="n">
         <v>7317200</v>
       </c>
     </row>
@@ -3106,19 +3121,19 @@
       <c r="A141" s="6" t="n">
         <v>45994</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="4" t="n">
         <v>95.07135418127504</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="4" t="n">
         <v>95.16943517086364</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="4" t="n">
         <v>94.95365250390886</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="4" t="n">
         <v>95.11058807373048</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141" s="4" t="n">
         <v>6855100</v>
       </c>
     </row>
@@ -3126,19 +3141,19 @@
       <c r="A142" s="6" t="n">
         <v>45995</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="4" t="n">
         <v>94.96346281132551</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="4" t="n">
         <v>94.97327315521056</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="4" t="n">
         <v>94.76730083222368</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="4" t="n">
         <v>94.81633758544922</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="4" t="n">
         <v>8928900</v>
       </c>
     </row>
@@ -3146,19 +3161,19 @@
       <c r="A143" s="6" t="n">
         <v>45996</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="4" t="n">
         <v>94.83596089549469</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="4" t="n">
         <v>94.84576375655097</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="4" t="n">
         <v>94.57113398497476</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="4" t="n">
         <v>94.62017822265624</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143" s="4" t="n">
         <v>9118700</v>
       </c>
     </row>
@@ -3166,19 +3181,19 @@
       <c r="A144" s="6" t="n">
         <v>45999</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="4" t="n">
         <v>94.56132596246688</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="4" t="n">
         <v>94.57112882298806</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="4" t="n">
         <v>94.24745483139752</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="4" t="n">
         <v>94.42400360107422</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144" s="4" t="n">
         <v>14728300</v>
       </c>
     </row>
@@ -3186,19 +3201,19 @@
       <c r="A145" s="6" t="n">
         <v>46000</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="4" t="n">
         <v>94.56132700100272</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="4" t="n">
         <v>94.56132700100272</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="4" t="n">
         <v>94.26707655394335</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="4" t="n">
         <v>94.28668975830078</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145" s="4" t="n">
         <v>8509200</v>
       </c>
     </row>
@@ -3206,19 +3221,19 @@
       <c r="A146" s="6" t="n">
         <v>46001</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="4" t="n">
         <v>94.24745696135868</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="4" t="n">
         <v>94.62017519637702</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="4" t="n">
         <v>94.23765410061596</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="4" t="n">
         <v>94.59075164794922</v>
       </c>
-      <c r="F146" t="n">
+      <c r="F146" s="4" t="n">
         <v>13356900</v>
       </c>
     </row>
@@ -3226,19 +3241,19 @@
       <c r="A147" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="4" t="n">
         <v>94.8261484318744</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="4" t="n">
         <v>94.87519266845968</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="4" t="n">
         <v>94.57113187121064</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="4" t="n">
         <v>94.60055541992188</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147" s="4" t="n">
         <v>8672800</v>
       </c>
     </row>
@@ -3246,19 +3261,19 @@
       <c r="A148" s="6" t="n">
         <v>46003</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="4" t="n">
         <v>94.34555053710938</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="4" t="n">
         <v>94.42401084279447</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="4" t="n">
         <v>94.32592984836296</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="4" t="n">
         <v>94.34555053710938</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148" s="4" t="n">
         <v>8348700</v>
       </c>
     </row>
@@ -3266,19 +3281,19 @@
       <c r="A149" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="4" t="n">
         <v>94.56132596246688</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="4" t="n">
         <v>94.65940694937622</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="4" t="n">
         <v>94.4043903969322</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="4" t="n">
         <v>94.42400360107422</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149" s="4" t="n">
         <v>6117000</v>
       </c>
     </row>
@@ -3286,19 +3301,19 @@
       <c r="A150" s="6" t="n">
         <v>46007</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="4" t="n">
         <v>94.39458468577476</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="4" t="n">
         <v>94.7084483491475</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="4" t="n">
         <v>94.3847818247725</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="4" t="n">
         <v>94.68883514404295</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150" s="4" t="n">
         <v>7456400</v>
       </c>
     </row>
@@ -3306,19 +3321,19 @@
       <c r="A151" s="6" t="n">
         <v>46008</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="4" t="n">
         <v>94.5711313517766</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="4" t="n">
         <v>94.71825657762452</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="4" t="n">
         <v>94.55151814711012</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="4" t="n">
         <v>94.66921234130859</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151" s="4" t="n">
         <v>5673200</v>
       </c>
     </row>
@@ -3326,19 +3341,19 @@
       <c r="A152" s="6" t="n">
         <v>46009</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="4" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="4" t="n">
         <v>94.97327566330765</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="4" t="n">
         <v>94.78691654006956</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="4" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152" s="4" t="n">
         <v>7357600</v>
       </c>
     </row>
@@ -3346,19 +3361,19 @@
       <c r="A153" s="6" t="n">
         <v>46010</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="4" t="n">
         <v>94.75992751443634</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="4" t="n">
         <v>94.8484845880067</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="4" t="n">
         <v>94.66152075618268</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="4" t="n">
         <v>94.7008819580078</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153" s="4" t="n">
         <v>5806600</v>
       </c>
     </row>
@@ -3366,19 +3381,19 @@
       <c r="A154" s="6" t="n">
         <v>46013</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="4" t="n">
         <v>94.6221700119554</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="4" t="n">
         <v>94.65168903739922</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="4" t="n">
         <v>94.54344760585064</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="4" t="n">
         <v>94.60248565673828</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154" s="4" t="n">
         <v>4672800</v>
       </c>
     </row>
@@ -3386,19 +3401,19 @@
       <c r="A155" s="6" t="n">
         <v>46014</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="4" t="n">
         <v>94.3958461258692</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="4" t="n">
         <v>94.59264463615646</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="4" t="n">
         <v>94.34664274460644</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="4" t="n">
         <v>94.56312561035156</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155" s="4" t="n">
         <v>5093900</v>
       </c>
     </row>
@@ -3406,19 +3421,19 @@
       <c r="A156" s="6" t="n">
         <v>46015</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" s="4" t="n">
         <v>94.6812095262562</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="4" t="n">
         <v>94.82881216313856</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="4" t="n">
         <v>94.63200614483476</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="4" t="n">
         <v>94.8091278076172</v>
       </c>
-      <c r="F156" t="n">
+      <c r="F156" s="4" t="n">
         <v>3967700</v>
       </c>
     </row>
@@ -3426,19 +3441,19 @@
       <c r="A157" s="6" t="n">
         <v>46017</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="4" t="n">
         <v>94.94688569204136</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="4" t="n">
         <v>94.96657004702892</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="4" t="n">
         <v>94.78944838904955</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="4" t="n">
         <v>94.89768981933594</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157" s="4" t="n">
         <v>3491500</v>
       </c>
     </row>
@@ -3446,19 +3461,19 @@
       <c r="A158" s="6" t="n">
         <v>46020</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="4" t="n">
         <v>95.00594239721801</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="4" t="n">
         <v>95.05513827569588</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="4" t="n">
         <v>94.90753562549702</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="4" t="n">
         <v>95.03546142578124</v>
       </c>
-      <c r="F158" t="n">
+      <c r="F158" s="4" t="n">
         <v>5034600</v>
       </c>
     </row>
@@ -3466,19 +3481,19 @@
       <c r="A159" s="6" t="n">
         <v>46021</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="4" t="n">
         <v>94.89768866360863</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="4" t="n">
         <v>95.01576476256903</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="4" t="n">
         <v>94.8583274614946</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="4" t="n">
         <v>94.93704986572266</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159" s="4" t="n">
         <v>4108600</v>
       </c>
     </row>
@@ -3486,19 +3501,19 @@
       <c r="A160" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="4" t="n">
         <v>94.79929128999878</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="4" t="n">
         <v>94.92721708637974</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="4" t="n">
         <v>94.61233494567512</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="4" t="n">
         <v>94.62217712402344</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160" s="4" t="n">
         <v>6802100</v>
       </c>
     </row>
@@ -3506,19 +3521,19 @@
       <c r="A161" s="6" t="n">
         <v>46024</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="4" t="n">
         <v>94.75009009126956</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="4" t="n">
         <v>94.75009009126956</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="4" t="n">
         <v>94.53360722405996</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="4" t="n">
         <v>94.54344940185548</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F161" s="4" t="n">
         <v>6611800</v>
       </c>
     </row>
@@ -3526,19 +3541,19 @@
       <c r="A162" s="6" t="n">
         <v>46027</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="4" t="n">
         <v>94.69105880544922</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="4" t="n">
         <v>94.83865394601862</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="4" t="n">
         <v>94.63201324183892</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="4" t="n">
         <v>94.82881927490234</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F162" s="4" t="n">
         <v>8693200</v>
       </c>
     </row>
@@ -3546,19 +3561,19 @@
       <c r="A163" s="6" t="n">
         <v>46028</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="4" t="n">
         <v>94.7107300894596</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="4" t="n">
         <v>94.77961032013847</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="4" t="n">
         <v>94.56312745018144</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="4" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163" s="4" t="n">
         <v>12834100</v>
       </c>
     </row>
@@ -3566,19 +3581,19 @@
       <c r="A164" s="6" t="n">
         <v>46029</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" s="4" t="n">
         <v>94.976403560455</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="4" t="n">
         <v>95.0059300925768</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="4" t="n">
         <v>94.79928190463274</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="4" t="n">
         <v>94.93704986572266</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164" s="4" t="n">
         <v>7990900</v>
       </c>
     </row>
@@ -3586,19 +3601,19 @@
       <c r="A165" s="6" t="n">
         <v>46030</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="4" t="n">
         <v>94.69105645710135</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="4" t="n">
         <v>94.76977136099208</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="4" t="n">
         <v>94.64185307321011</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="4" t="n">
         <v>94.65169525146484</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165" s="4" t="n">
         <v>6931700</v>
       </c>
     </row>
@@ -3606,19 +3621,19 @@
       <c r="A166" s="6" t="n">
         <v>46031</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="4" t="n">
         <v>94.62217301032196</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="4" t="n">
         <v>94.83864837289693</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="4" t="n">
         <v>94.53360842380222</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="4" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166" s="4" t="n">
         <v>10277300</v>
       </c>
     </row>
@@ -3626,19 +3641,19 @@
       <c r="A167" s="6" t="n">
         <v>46034</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="4" t="n">
         <v>94.61233430505683</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="4" t="n">
         <v>94.75993694975264</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="4" t="n">
         <v>94.58281527759416</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="4" t="n">
         <v>94.64185333251952</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167" s="4" t="n">
         <v>6360600</v>
       </c>
     </row>
@@ -3646,19 +3661,19 @@
       <c r="A168" s="6" t="n">
         <v>46035</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="4" t="n">
         <v>94.79928716859726</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="4" t="n">
         <v>94.82881370235856</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="4" t="n">
         <v>94.66152670723952</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" s="4" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168" s="4" t="n">
         <v>7622500</v>
       </c>
     </row>
@@ -3666,19 +3681,19 @@
       <c r="A169" s="6" t="n">
         <v>46036</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="4" t="n">
         <v>94.83865770848512</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="4" t="n">
         <v>95.05514059975198</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="4" t="n">
         <v>94.82882303697868</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="4" t="n">
         <v>94.9567413330078</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169" s="4" t="n">
         <v>7331200</v>
       </c>
     </row>
@@ -3686,19 +3701,19 @@
       <c r="A170" s="6" t="n">
         <v>46037</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="4" t="n">
         <v>94.9665741637163</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="4" t="n">
         <v>94.97640883425464</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="4" t="n">
         <v>94.74024911583882</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="4" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170" s="4" t="n">
         <v>6172500</v>
       </c>
     </row>
@@ -3706,19 +3721,19 @@
       <c r="A171" s="6" t="n">
         <v>46038</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="4" t="n">
         <v>94.69105642373262</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="4" t="n">
         <v>94.720575451104</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="4" t="n">
         <v>94.37617428613376</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="4" t="n">
         <v>94.39585113525391</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171" s="4" t="n">
         <v>11979300</v>
       </c>
     </row>
@@ -3726,19 +3741,19 @@
       <c r="A172" s="6" t="n">
         <v>46042</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" s="4" t="n">
         <v>94.07112275424844</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="4" t="n">
         <v>94.18920636601358</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="4" t="n">
         <v>94.00224252423097</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="4" t="n">
         <v>94.0219268798828</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172" s="4" t="n">
         <v>13607700</v>
       </c>
     </row>
@@ -3746,19 +3761,19 @@
       <c r="A173" s="6" t="n">
         <v>46043</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="4" t="n">
         <v>94.13016861667025</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="4" t="n">
         <v>94.30728277381472</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="4" t="n">
         <v>94.03176185285834</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="4" t="n">
         <v>94.26792907714844</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F173" s="4" t="n">
         <v>11969000</v>
       </c>
     </row>
@@ -3766,19 +3781,19 @@
       <c r="A174" s="6" t="n">
         <v>46044</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" s="4" t="n">
         <v>94.16951494977958</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="4" t="n">
         <v>94.32695975366164</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="4" t="n">
         <v>94.12031907910252</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="4" t="n">
         <v>94.25807952880859</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F174" s="4" t="n">
         <v>10209500</v>
       </c>
     </row>
@@ -3786,19 +3801,19 @@
       <c r="A175" s="6" t="n">
         <v>46045</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="4" t="n">
         <v>94.29745123506557</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="4" t="n">
         <v>94.43521170011894</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="4" t="n">
         <v>94.2187288243544</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="4" t="n">
         <v>94.41552734375</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F175" s="4" t="n">
         <v>8147500</v>
       </c>
     </row>
@@ -3806,19 +3821,19 @@
       <c r="A176" s="6" t="n">
         <v>46048</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="4" t="n">
         <v>94.56311823897344</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="4" t="n">
         <v>94.62216379336246</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="4" t="n">
         <v>94.50408019196578</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="4" t="n">
         <v>94.55327606201172</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F176" s="4" t="n">
         <v>6803800</v>
       </c>
     </row>
@@ -3826,19 +3841,19 @@
       <c r="A177" s="6" t="n">
         <v>46049</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="4" t="n">
         <v>94.49424134296994</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="4" t="n">
         <v>94.61232494852536</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="4" t="n">
         <v>94.41551893926632</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="4" t="n">
         <v>94.44504547119141</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F177" s="4" t="n">
         <v>9857200</v>
       </c>
     </row>
@@ -3846,19 +3861,19 @@
       <c r="A178" s="6" t="n">
         <v>46050</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="4" t="n">
         <v>94.38600222613492</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="4" t="n">
         <v>94.41552125140126</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="4" t="n">
         <v>94.19904589698751</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="4" t="n">
         <v>94.36632537841795</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F178" s="4" t="n">
         <v>17032400</v>
       </c>
     </row>
@@ -3866,19 +3881,19 @@
       <c r="A179" s="6" t="n">
         <v>46051</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="4" t="n">
         <v>94.26793079264098</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="4" t="n">
         <v>94.55328638926584</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="4" t="n">
         <v>94.24824643656756</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179" s="4" t="n">
         <v>94.46472930908205</v>
       </c>
-      <c r="F179" t="n">
+      <c r="F179" s="4" t="n">
         <v>11049100</v>
       </c>
     </row>
@@ -3886,19 +3901,19 @@
       <c r="A180" s="6" t="n">
         <v>46052</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="4" t="n">
         <v>94.45488129718537</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="4" t="n">
         <v>94.52376152442363</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="4" t="n">
         <v>94.37616639989994</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180" s="4" t="n">
         <v>94.40568542480467</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F180" s="4" t="n">
         <v>8238500</v>
       </c>
     </row>
@@ -3906,19 +3921,19 @@
       <c r="A181" s="6" t="n">
         <v>46055</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="4" t="n">
         <v>94.44714870629468</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="4" t="n">
         <v>94.47676404259118</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="4" t="n">
         <v>94.2200927734375</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" s="4" t="n">
         <v>94.2200927734375</v>
       </c>
-      <c r="F181" t="n">
+      <c r="F181" s="4" t="n">
         <v>8987100</v>
       </c>
     </row>
@@ -3926,19 +3941,19 @@
       <c r="A182" s="6" t="n">
         <v>46056</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="4" t="n">
         <v>94.17072715129162</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="4" t="n">
         <v>94.3484266977254</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="4" t="n">
         <v>94.15098610474379</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182" s="4" t="n">
         <v>94.30893707275391</v>
       </c>
-      <c r="F182" t="n">
+      <c r="F182" s="4" t="n">
         <v>7313800</v>
       </c>
     </row>
@@ -3946,19 +3961,19 @@
       <c r="A183" s="6" t="n">
         <v>46057</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="4" t="n">
         <v>94.22996162331719</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="4" t="n">
         <v>94.38792012957396</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="4" t="n">
         <v>94.19047952862915</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183" s="4" t="n">
         <v>94.28919982910156</v>
       </c>
-      <c r="F183" t="n">
+      <c r="F183" s="4" t="n">
         <v>7268600</v>
       </c>
     </row>
@@ -3966,19 +3981,19 @@
       <c r="A184" s="6" t="n">
         <v>46058</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="4" t="n">
         <v>94.57549544700704</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="4" t="n">
         <v>94.87165635304076</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="4" t="n">
         <v>94.48664190288356</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184" s="4" t="n">
         <v>94.842041015625</v>
       </c>
-      <c r="F184" t="n">
+      <c r="F184" s="4" t="n">
         <v>12086800</v>
       </c>
     </row>
@@ -3986,19 +4001,19 @@
       <c r="A185" s="6" t="n">
         <v>46059</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185" s="4" t="n">
         <v>94.89140493256876</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C185" s="4" t="n">
         <v>94.9012716904565</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185" s="4" t="n">
         <v>94.69395679667002</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185" s="4" t="n">
         <v>94.842041015625</v>
       </c>
-      <c r="F185" t="n">
+      <c r="F185" s="4" t="n">
         <v>7759900</v>
       </c>
     </row>
@@ -4006,19 +4021,19 @@
       <c r="A186" s="6" t="n">
         <v>46062</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186" s="4" t="n">
         <v>94.7828065399609</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186" s="4" t="n">
         <v>94.90126788487352</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="4" t="n">
         <v>94.70382728876852</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186" s="4" t="n">
         <v>94.86177825927734</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F186" s="4" t="n">
         <v>8165100</v>
       </c>
     </row>
@@ -4026,19 +4041,19 @@
       <c r="A187" s="6" t="n">
         <v>46063</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187" s="4" t="n">
         <v>95.19743371482861</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187" s="4" t="n">
         <v>95.31590258838648</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="4" t="n">
         <v>95.17769266850682</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187" s="4" t="n">
         <v>95.2764129638672</v>
       </c>
-      <c r="F187" t="n">
+      <c r="F187" s="4" t="n">
         <v>9752300</v>
       </c>
     </row>
@@ -4046,19 +4061,19 @@
       <c r="A188" s="6" t="n">
         <v>46064</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188" s="4" t="n">
         <v>94.95063413321699</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188" s="4" t="n">
         <v>95.21717969769664</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="4" t="n">
         <v>94.93089308587176</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188" s="4" t="n">
         <v>95.00986480712891</v>
       </c>
-      <c r="F188" t="n">
+      <c r="F188" s="4" t="n">
         <v>9106600</v>
       </c>
     </row>
@@ -4066,19 +4081,19 @@
       <c r="A189" s="6" t="n">
         <v>46065</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189" s="4" t="n">
         <v>95.16781925059892</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189" s="4" t="n">
         <v>95.61206434972516</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" s="4" t="n">
         <v>95.15794496140975</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189" s="4" t="n">
         <v>95.59232330322266</v>
       </c>
-      <c r="F189" t="n">
+      <c r="F189" s="4" t="n">
         <v>13099900</v>
       </c>
     </row>
@@ -4086,19 +4101,19 @@
       <c r="A190" s="6" t="n">
         <v>46066</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190" s="4" t="n">
         <v>95.87861462785028</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190" s="4" t="n">
         <v>96.01682454494905</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="4" t="n">
         <v>95.84899176115005</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190" s="4" t="n">
         <v>95.96746063232422</v>
       </c>
-      <c r="F190" t="n">
+      <c r="F190" s="4" t="n">
         <v>11681500</v>
       </c>
     </row>
@@ -4106,19 +4121,19 @@
       <c r="A191" s="6" t="n">
         <v>46070</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191" s="4" t="n">
         <v>96.00695210937852</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191" s="4" t="n">
         <v>96.06618278017122</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="4" t="n">
         <v>95.90823181409878</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" s="4" t="n">
         <v>95.95758819580078</v>
       </c>
-      <c r="F191" t="n">
+      <c r="F191" s="4" t="n">
         <v>8623800</v>
       </c>
     </row>
@@ -4126,19 +4141,19 @@
       <c r="A192" s="6" t="n">
         <v>46071</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192" s="4" t="n">
         <v>95.78977006171908</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192" s="4" t="n">
         <v>95.84900073691502</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="4" t="n">
         <v>95.73053938652312</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192" s="4" t="n">
         <v>95.76015472412109</v>
       </c>
-      <c r="F192" t="n">
+      <c r="F192" s="4" t="n">
         <v>7778800</v>
       </c>
     </row>
@@ -4146,19 +4161,19 @@
       <c r="A193" s="6" t="n">
         <v>46072</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193" s="4" t="n">
         <v>95.72066338551508</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193" s="4" t="n">
         <v>95.89836293980252</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="4" t="n">
         <v>95.70092233809476</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193" s="4" t="n">
         <v>95.8489990234375</v>
       </c>
-      <c r="F193" t="n">
+      <c r="F193" s="4" t="n">
         <v>4993000</v>
       </c>
     </row>
@@ -4166,19 +4181,19 @@
       <c r="A194" s="6" t="n">
         <v>46073</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="4" t="n">
         <v>95.88848865015429</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194" s="4" t="n">
         <v>95.89836293980252</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="4" t="n">
         <v>95.65155842172976</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194" s="4" t="n">
         <v>95.8489990234375</v>
       </c>
-      <c r="F194" t="n">
+      <c r="F194" s="4" t="n">
         <v>11200200</v>
       </c>
     </row>
@@ -4186,19 +4201,19 @@
       <c r="A195" s="6" t="n">
         <v>46076</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="4" t="n">
         <v>95.9279659797692</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195" s="4" t="n">
         <v>96.28336504278514</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="4" t="n">
         <v>95.9279659797692</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195" s="4" t="n">
         <v>96.19451904296876</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F195" s="4" t="n">
         <v>9862900</v>
       </c>
     </row>
@@ -4206,19 +4221,19 @@
       <c r="A196" s="6" t="n">
         <v>46077</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="4" t="n">
         <v>96.19453037840844</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196" s="4" t="n">
         <v>96.2340200047164</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="4" t="n">
         <v>96.08593578903051</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196" s="4" t="n">
         <v>96.17478179931641</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F196" s="4" t="n">
         <v>9493300</v>
       </c>
     </row>
@@ -4226,19 +4241,19 @@
       <c r="A197" s="6" t="n">
         <v>46078</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="4" t="n">
         <v>96.02669734423128</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197" s="4" t="n">
         <v>96.17478155954797</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="4" t="n">
         <v>96.02669734423128</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197" s="4" t="n">
         <v>96.09580230712891</v>
       </c>
-      <c r="F197" t="n">
+      <c r="F197" s="4" t="n">
         <v>8762700</v>
       </c>
     </row>
@@ -4246,19 +4261,19 @@
       <c r="A198" s="6" t="n">
         <v>46079</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="4" t="n">
         <v>96.17477848102703</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198" s="4" t="n">
         <v>96.35247802734376</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="4" t="n">
         <v>96.17477848102703</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198" s="4" t="n">
         <v>96.35247802734376</v>
       </c>
-      <c r="F198" t="n">
+      <c r="F198" s="4" t="n">
         <v>8177300</v>
       </c>
     </row>
@@ -4266,19 +4281,19 @@
       <c r="A199" s="6" t="n">
         <v>46080</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199" s="4" t="n">
         <v>96.62890083340191</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199" s="4" t="n">
         <v>96.79673362753606</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199" s="4" t="n">
         <v>96.57954444961332</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199" s="4" t="n">
         <v>96.73749542236328</v>
       </c>
-      <c r="F199" t="n">
+      <c r="F199" s="4" t="n">
         <v>9970300</v>
       </c>
     </row>
@@ -4286,19 +4301,19 @@
       <c r="A200" s="6" t="n">
         <v>46083</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200" s="4" t="n">
         <v>96.41373334683392</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200" s="4" t="n">
         <v>96.42363623574974</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="4" t="n">
         <v>95.98799976774596</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200" s="4" t="n">
         <v>96.15631866455078</v>
       </c>
-      <c r="F200" t="n">
+      <c r="F200" s="4" t="n">
         <v>17709600</v>
       </c>
     </row>
@@ -4306,19 +4321,19 @@
       <c r="A201" s="6" t="n">
         <v>46084</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201" s="4" t="n">
         <v>95.71078642207044</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201" s="4" t="n">
         <v>96.18602692737238</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="4" t="n">
         <v>95.68108530680622</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201" s="4" t="n">
         <v>96.04741668701172</v>
       </c>
-      <c r="F201" t="n">
+      <c r="F201" s="4" t="n">
         <v>13708500</v>
       </c>
     </row>
@@ -4326,19 +4341,19 @@
       <c r="A202" s="6" t="n">
         <v>46085</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="4" t="n">
         <v>96.00781177011282</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202" s="4" t="n">
         <v>96.02760999553703</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="4" t="n">
         <v>95.82959752652891</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202" s="4" t="n">
         <v>95.84939575195312</v>
       </c>
-      <c r="F202" t="n">
+      <c r="F202" s="4" t="n">
         <v>12535500</v>
       </c>
     </row>
@@ -4346,19 +4361,19 @@
       <c r="A203" s="6" t="n">
         <v>46086</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="4" t="n">
         <v>95.49295838593072</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203" s="4" t="n">
         <v>95.62167327714056</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="4" t="n">
         <v>95.43355616148976</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203" s="4" t="n">
         <v>95.5523681640625</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F203" s="4" t="n">
         <v>12599700</v>
       </c>
     </row>
@@ -4366,19 +4381,19 @@
       <c r="A204" s="6" t="n">
         <v>46087</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204" s="4" t="n">
         <v>95.2652521179876</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204" s="4" t="n">
         <v>95.78008906117785</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="4" t="n">
         <v>95.21574522470196</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204" s="4" t="n">
         <v>95.4929656982422</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F204" s="4" t="n">
         <v>12758200</v>
       </c>
     </row>
@@ -4386,19 +4401,19 @@
       <c r="A205" s="6" t="n">
         <v>46090</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205" s="4" t="n">
         <v>95.4038560862932</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205" s="4" t="n">
         <v>95.83949254677108</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="4" t="n">
         <v>95.29494697117374</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E205" s="4" t="n">
         <v>95.78998565673828</v>
       </c>
-      <c r="F205" t="n">
+      <c r="F205" s="4" t="n">
         <v>12134400</v>
       </c>
     </row>
@@ -4406,19 +4421,19 @@
       <c r="A206" s="6" t="n">
         <v>46091</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="4" t="n">
         <v>95.74048506831424</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="4" t="n">
         <v>95.80979018670727</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="4" t="n">
         <v>95.4533692590369</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206" s="4" t="n">
         <v>95.48307037353516</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F206" s="4" t="n">
         <v>10571300</v>
       </c>
     </row>
@@ -4426,19 +4441,19 @@
       <c r="A207" s="6" t="n">
         <v>46092</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207" s="4" t="n">
         <v>95.30484653896325</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="4" t="n">
         <v>95.35434587358031</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="4" t="n">
         <v>95.02762609329754</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" s="4" t="n">
         <v>95.04742431640624</v>
       </c>
-      <c r="F207" t="n">
+      <c r="F207" s="4" t="n">
         <v>12197600</v>
       </c>
     </row>
@@ -4446,19 +4461,19 @@
       <c r="A208" s="6" t="n">
         <v>46093</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208" s="4" t="n">
         <v>94.89891748963493</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="4" t="n">
         <v>95.02763238628256</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="4" t="n">
         <v>94.64149525003074</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" s="4" t="n">
         <v>94.74050903320312</v>
       </c>
-      <c r="F208" t="n">
+      <c r="F208" s="4" t="n">
         <v>11401400</v>
       </c>
     </row>
@@ -4466,19 +4481,19 @@
       <c r="A209" s="6" t="n">
         <v>46094</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209" s="4" t="n">
         <v>94.88902174956804</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="4" t="n">
         <v>94.97813265039862</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="4" t="n">
         <v>94.60190592854828</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="4" t="n">
         <v>94.64150238037109</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F209" s="4" t="n">
         <v>11839700</v>
       </c>
     </row>
@@ -4486,19 +4501,19 @@
       <c r="A210" s="6" t="n">
         <v>46097</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210" s="4" t="n">
         <v>95.02764140140783</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="4" t="n">
         <v>95.10684186029179</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="4" t="n">
         <v>94.91873227253907</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" s="4" t="n">
         <v>95.06723785400391</v>
       </c>
-      <c r="F210" t="n">
+      <c r="F210" s="4" t="n">
         <v>9092100</v>
       </c>
     </row>
@@ -4506,19 +4521,19 @@
       <c r="A211" s="6" t="n">
         <v>46098</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211" s="4" t="n">
         <v>95.21574414819094</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="4" t="n">
         <v>95.3246532692349</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="4" t="n">
         <v>95.17614014474847</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" s="4" t="n">
         <v>95.2355499267578</v>
       </c>
-      <c r="F211" t="n">
+      <c r="F211" s="4" t="n">
         <v>7209700</v>
       </c>
     </row>
@@ -4526,19 +4541,19 @@
       <c r="A212" s="6" t="n">
         <v>46099</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212" s="4" t="n">
         <v>95.09693774190676</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="4" t="n">
         <v>95.1662428580874</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="4" t="n">
         <v>94.78011327455376</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="4" t="n">
         <v>94.79991149902344</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F212" s="4" t="n">
         <v>13048700</v>
       </c>
     </row>
@@ -4546,19 +4561,19 @@
       <c r="A213" s="6" t="n">
         <v>46100</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213" s="4" t="n">
         <v>94.54248158444692</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="4" t="n">
         <v>94.92861113663714</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="4" t="n">
         <v>94.53258624986088</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="4" t="n">
         <v>94.79000091552734</v>
       </c>
-      <c r="F213" t="n">
+      <c r="F213" s="4" t="n">
         <v>18464600</v>
       </c>
     </row>
@@ -4566,19 +4581,19 @@
       <c r="A214" s="6" t="n">
         <v>46101</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214" s="4" t="n">
         <v>94.3642788303888</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C214" s="4" t="n">
         <v>94.39397994513703</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="4" t="n">
         <v>93.90884411230256</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="4" t="n">
         <v>93.93854522705078</v>
       </c>
-      <c r="F214" t="n">
+      <c r="F214" s="4" t="n">
         <v>20761500</v>
       </c>
     </row>
@@ -4586,19 +4601,19 @@
       <c r="A215" s="6" t="n">
         <v>46104</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215" s="4" t="n">
         <v>94.05735095527346</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215" s="4" t="n">
         <v>94.48308453016602</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="4" t="n">
         <v>93.94844183934576</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" s="4" t="n">
         <v>94.23556518554688</v>
       </c>
-      <c r="F215" t="n">
+      <c r="F215" s="4" t="n">
         <v>28336300</v>
       </c>
     </row>
@@ -4606,19 +4621,19 @@
       <c r="A216" s="6" t="n">
         <v>46105</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216" s="4" t="n">
         <v>93.84944182930532</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216" s="4" t="n">
         <v>94.13656519452698</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="4" t="n">
         <v>93.68113047670032</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" s="4" t="n">
         <v>93.9187469482422</v>
       </c>
-      <c r="F216" t="n">
+      <c r="F216" s="4" t="n">
         <v>19785600</v>
       </c>
     </row>
@@ -4626,19 +4641,19 @@
       <c r="A217" s="6" t="n">
         <v>46106</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217" s="4" t="n">
         <v>94.34447509747189</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217" s="4" t="n">
         <v>94.45338421431846</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="4" t="n">
         <v>94.19596197870921</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217" s="4" t="n">
         <v>94.41378021240234</v>
       </c>
-      <c r="F217" t="n">
+      <c r="F217" s="4" t="n">
         <v>15939200</v>
       </c>
     </row>
@@ -4646,19 +4661,19 @@
       <c r="A218" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218" s="4" t="n">
         <v>94.06725119190808</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C218" s="4" t="n">
         <v>94.18605563961344</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="4" t="n">
         <v>93.6514129638672</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" s="4" t="n">
         <v>93.6514129638672</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F218" s="4" t="n">
         <v>12897300</v>
       </c>
     </row>
@@ -4666,19 +4681,19 @@
       <c r="A219" s="6" t="n">
         <v>46108</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219" s="4" t="n">
         <v>93.43360996809255</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219" s="4" t="n">
         <v>93.83953778725363</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="4" t="n">
         <v>93.42370707873994</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" s="4" t="n">
         <v>93.66132354736328</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F219" s="4" t="n">
         <v>11401900</v>
       </c>
     </row>
@@ -4686,19 +4701,19 @@
       <c r="A220" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220" s="4" t="n">
         <v>94.2553637696668</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220" s="4" t="n">
         <v>94.44348088947729</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="4" t="n">
         <v>94.18605865505624</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" s="4" t="n">
         <v>94.32466888427734</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F220" s="4" t="n">
         <v>15430000</v>
       </c>
     </row>
@@ -4706,19 +4721,19 @@
       <c r="A221" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="4" t="n">
         <v>94.59199481475844</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221" s="4" t="n">
         <v>94.73060504516241</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="4" t="n">
         <v>94.40387769334264</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="4" t="n">
         <v>94.49298858642578</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221" s="4" t="n">
         <v>18649700</v>
       </c>
     </row>
@@ -4726,19 +4741,19 @@
       <c r="A222" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B222" s="4" t="n">
         <v>94.45027370360532</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C222" s="4" t="n">
         <v>94.6588819348209</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="4" t="n">
         <v>94.39066593835518</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222" s="4" t="n">
         <v>94.41053771972656</v>
       </c>
-      <c r="F222" t="n">
+      <c r="F222" s="4" t="n">
         <v>13557600</v>
       </c>
     </row>
@@ -4746,19 +4761,19 @@
       <c r="A223" s="6" t="n">
         <v>46114</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="4" t="n">
         <v>94.40060171376628</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C223" s="4" t="n">
         <v>94.75821798937454</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="4" t="n">
         <v>94.38073751128314</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223" s="4" t="n">
         <v>94.62908172607422</v>
       </c>
-      <c r="F223" t="n">
+      <c r="F223" s="4" t="n">
         <v>13171300</v>
       </c>
     </row>
@@ -4766,19 +4781,19 @@
       <c r="A224" s="6" t="n">
         <v>46118</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224" s="4" t="n">
         <v>94.37080141403568</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C224" s="4" t="n">
         <v>94.5496095514484</v>
       </c>
-      <c r="D224" t="n">
+      <c r="D224" s="4" t="n">
         <v>94.2814011347613</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224" s="4" t="n">
         <v>94.3807373046875</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F224" s="4" t="n">
         <v>6104900</v>
       </c>
     </row>
@@ -4786,19 +4801,19 @@
       <c r="A225" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225" s="4" t="n">
         <v>94.44034011201906</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225" s="4" t="n">
         <v>94.65888423924063</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D225" s="4" t="n">
         <v>94.13239570304182</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" s="4" t="n">
         <v>94.61914825439452</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F225" s="4" t="n">
         <v>6737500</v>
       </c>
     </row>
@@ -4806,19 +4821,19 @@
       <c r="A226" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226" s="4" t="n">
         <v>95.08603890739025</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226" s="4" t="n">
         <v>95.09597479855864</v>
       </c>
-      <c r="D226" t="n">
+      <c r="D226" s="4" t="n">
         <v>94.73835850514004</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" s="4" t="n">
         <v>94.8277587890625</v>
       </c>
-      <c r="F226" t="n">
+      <c r="F226" s="4" t="n">
         <v>12107400</v>
       </c>
     </row>
@@ -4826,19 +4841,19 @@
       <c r="A227" s="6" t="n">
         <v>46121</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="4" t="n">
         <v>94.73835818494322</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227" s="4" t="n">
         <v>95.01650250580332</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D227" s="4" t="n">
         <v>94.59928602451318</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="4" t="n">
         <v>94.79795837402344</v>
       </c>
-      <c r="F227" t="n">
+      <c r="F227" s="4" t="n">
         <v>11065900</v>
       </c>
     </row>
@@ -4846,19 +4861,19 @@
       <c r="A228" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228" s="4" t="n">
         <v>94.7979591417408</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228" s="4" t="n">
         <v>94.82775923652224</v>
       </c>
-      <c r="D228" t="n">
+      <c r="D228" s="4" t="n">
         <v>94.62908688540304</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228" s="4" t="n">
         <v>94.63901519775391</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F228" s="4" t="n">
         <v>4404800</v>
       </c>
     </row>
@@ -4866,19 +4881,19 @@
       <c r="A229" s="6" t="n">
         <v>46125</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229" s="4" t="n">
         <v>94.63901753546445</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229" s="4" t="n">
         <v>94.85756167441254</v>
       </c>
-      <c r="D229" t="n">
+      <c r="D229" s="4" t="n">
         <v>94.53968135745112</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="4" t="n">
         <v>94.84763336181641</v>
       </c>
-      <c r="F229" t="n">
+      <c r="F229" s="4" t="n">
         <v>4300200</v>
       </c>
     </row>
@@ -4886,19 +4901,19 @@
       <c r="A230" s="6" t="n">
         <v>46126</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230" s="4" t="n">
         <v>94.80789819778435</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230" s="4" t="n">
         <v>95.1655145048282</v>
       </c>
-      <c r="D230" t="n">
+      <c r="D230" s="4" t="n">
         <v>94.77809810200814</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230" s="4" t="n">
         <v>95.15557861328124</v>
       </c>
-      <c r="F230" t="n">
+      <c r="F230" s="4" t="n">
         <v>5239800</v>
       </c>
     </row>
@@ -4906,19 +4921,19 @@
       <c r="A231" s="6" t="n">
         <v>46127</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231" s="4" t="n">
         <v>95.05624014640566</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C231" s="4" t="n">
         <v>95.06616845884901</v>
       </c>
-      <c r="D231" t="n">
+      <c r="D231" s="4" t="n">
         <v>94.86749610587984</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231" s="4" t="n">
         <v>94.94696807861328</v>
       </c>
-      <c r="F231" t="n">
+      <c r="F231" s="4" t="n">
         <v>5592900</v>
       </c>
     </row>
@@ -4926,19 +4941,19 @@
       <c r="A232" s="6" t="n">
         <v>46128</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232" s="4" t="n">
         <v>95.0363639617881</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C232" s="4" t="n">
         <v>95.06616405546671</v>
       </c>
-      <c r="D232" t="n">
+      <c r="D232" s="4" t="n">
         <v>94.74828375812132</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" s="4" t="n">
         <v>94.77809143066406</v>
       </c>
-      <c r="F232" t="n">
+      <c r="F232" s="4" t="n">
         <v>6618900</v>
       </c>
     </row>
@@ -4946,19 +4961,19 @@
       <c r="A233" s="6" t="n">
         <v>46129</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233" s="4" t="n">
         <v>95.25490360474603</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C233" s="4" t="n">
         <v>95.4138475353712</v>
       </c>
-      <c r="D233" t="n">
+      <c r="D233" s="4" t="n">
         <v>95.20523173170974</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233" s="4" t="n">
         <v>95.29463958740234</v>
       </c>
-      <c r="F233" t="n">
+      <c r="F233" s="4" t="n">
         <v>6912900</v>
       </c>
     </row>
@@ -4966,19 +4981,19 @@
       <c r="A234" s="6" t="n">
         <v>46132</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234" s="4" t="n">
         <v>95.27478200091024</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234" s="4" t="n">
         <v>95.28471031311588</v>
       </c>
-      <c r="D234" t="n">
+      <c r="D234" s="4" t="n">
         <v>95.07610207383344</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234" s="4" t="n">
         <v>95.20523834228516</v>
       </c>
-      <c r="F234" t="n">
+      <c r="F234" s="4" t="n">
         <v>3868800</v>
       </c>
     </row>
@@ -4986,19 +5001,19 @@
       <c r="A235" s="6" t="n">
         <v>46133</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235" s="4" t="n">
         <v>95.05623326679658</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C235" s="4" t="n">
         <v>95.11583345260092</v>
       </c>
-      <c r="D235" t="n">
+      <c r="D235" s="4" t="n">
         <v>94.77808896122444</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235" s="4" t="n">
         <v>94.78801727294922</v>
       </c>
-      <c r="F235" t="n">
+      <c r="F235" s="4" t="n">
         <v>4872900</v>
       </c>
     </row>
@@ -5006,19 +5021,19 @@
       <c r="A236" s="6" t="n">
         <v>46134</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236" s="4" t="n">
         <v>95.04629592127652</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C236" s="4" t="n">
         <v>95.07609601372251</v>
       </c>
-      <c r="D236" t="n">
+      <c r="D236" s="4" t="n">
         <v>94.86748778773668</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" s="4" t="n">
         <v>94.88735198974609</v>
       </c>
-      <c r="F236" t="n">
+      <c r="F236" s="4" t="n">
         <v>4121400</v>
       </c>
     </row>
@@ -5026,19 +5041,19 @@
       <c r="A237" s="6" t="n">
         <v>46135</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237" s="4" t="n">
         <v>94.92709400104378</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C237" s="4" t="n">
         <v>94.99663008078832</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D237" s="4" t="n">
         <v>94.55954939905016</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" s="4" t="n">
         <v>94.73835754394533</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F237" s="4" t="n">
         <v>6795600</v>
       </c>
     </row>
@@ -5046,19 +5061,19 @@
       <c r="A238" s="6" t="n">
         <v>46136</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238" s="4" t="n">
         <v>94.65888507934788</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C238" s="4" t="n">
         <v>94.95689360004241</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D238" s="4" t="n">
         <v>94.57941310895031</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" s="4" t="n">
         <v>94.92709350585938</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F238" s="4" t="n">
         <v>5490000</v>
       </c>
     </row>
@@ -5066,19 +5081,19 @@
       <c r="A239" s="6" t="n">
         <v>46139</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239" s="4" t="n">
         <v>94.78802147001235</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C239" s="4" t="n">
         <v>94.89729353473464</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D239" s="4" t="n">
         <v>94.64894931106838</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" s="4" t="n">
         <v>94.70854949951172</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F239" s="4" t="n">
         <v>4055500</v>
       </c>
     </row>
@@ -5086,19 +5101,19 @@
       <c r="A240" s="6" t="n">
         <v>46140</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240" s="4" t="n">
         <v>94.55954806655744</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C240" s="4" t="n">
         <v>94.6390124573855</v>
       </c>
-      <c r="D240" t="n">
+      <c r="D240" s="4" t="n">
         <v>94.4800760968652</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" s="4" t="n">
         <v>94.61914825439452</v>
       </c>
-      <c r="F240" t="n">
+      <c r="F240" s="4" t="n">
         <v>4867700</v>
       </c>
     </row>
@@ -5106,19 +5121,19 @@
       <c r="A241" s="6" t="n">
         <v>46141</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241" s="4" t="n">
         <v>94.4005991973732</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C241" s="4" t="n">
         <v>94.4005991973732</v>
       </c>
-      <c r="D241" t="n">
+      <c r="D241" s="4" t="n">
         <v>94.07278302366008</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" s="4" t="n">
         <v>94.17212677001952</v>
       </c>
-      <c r="F241" t="n">
+      <c r="F241" s="4" t="n">
         <v>7200300</v>
       </c>
     </row>
@@ -5126,19 +5141,19 @@
       <c r="A242" s="6" t="n">
         <v>46142</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242" s="4" t="n">
         <v>94.410537075628</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C242" s="4" t="n">
         <v>94.46020137098964</v>
       </c>
-      <c r="D242" t="n">
+      <c r="D242" s="4" t="n">
         <v>94.24166482944329</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" s="4" t="n">
         <v>94.35093688964844</v>
       </c>
-      <c r="F242" t="n">
+      <c r="F242" s="4" t="n">
         <v>10382400</v>
       </c>
     </row>
@@ -5146,19 +5161,19 @@
       <c r="A243" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243" s="4" t="n">
         <v>94.37287099463934</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C243" s="4" t="n">
         <v>94.72169726979961</v>
       </c>
-      <c r="D243" t="n">
+      <c r="D243" s="4" t="n">
         <v>94.3031057396073</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243" s="4" t="n">
         <v>94.42269897460938</v>
       </c>
-      <c r="F243" t="n">
+      <c r="F243" s="4" t="n">
         <v>5359200</v>
       </c>
     </row>
@@ -5166,19 +5181,19 @@
       <c r="A244" s="6" t="n">
         <v>46146</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244" s="4" t="n">
         <v>94.273194915031</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C244" s="4" t="n">
         <v>94.28316355204262</v>
       </c>
-      <c r="D244" t="n">
+      <c r="D244" s="4" t="n">
         <v>93.90443898786479</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" s="4" t="n">
         <v>94.07386779785156</v>
       </c>
-      <c r="F244" t="n">
+      <c r="F244" s="4" t="n">
         <v>6593900</v>
       </c>
     </row>
@@ -5186,19 +5201,19 @@
       <c r="A245" s="6" t="n">
         <v>46147</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245" s="4" t="n">
         <v>94.18350348613215</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C245" s="4" t="n">
         <v>94.32303399410053</v>
       </c>
-      <c r="D245" t="n">
+      <c r="D245" s="4" t="n">
         <v>94.1536051778307</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245" s="4" t="n">
         <v>94.21340179443359</v>
       </c>
-      <c r="F245" t="n">
+      <c r="F245" s="4" t="n">
         <v>11281600</v>
       </c>
     </row>
@@ -5206,19 +5221,19 @@
       <c r="A246" s="6" t="n">
         <v>46148</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246" s="4" t="n">
         <v>94.61205848029472</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C246" s="4" t="n">
         <v>94.71172203713732</v>
       </c>
-      <c r="D246" t="n">
+      <c r="D246" s="4" t="n">
         <v>94.54229323012068</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246" s="4" t="n">
         <v>94.68182373046876</v>
       </c>
-      <c r="F246" t="n">
+      <c r="F246" s="4" t="n">
         <v>9031100</v>
       </c>
     </row>
@@ -5226,19 +5241,19 @@
       <c r="A247" s="6" t="n">
         <v>46149</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247" s="4" t="n">
         <v>94.86122648505244</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C247" s="4" t="n">
         <v>94.86122648505244</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D247" s="4" t="n">
         <v>94.37286970649392</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247" s="4" t="n">
         <v>94.39279937744141</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F247" s="4" t="n">
         <v>5610100</v>
       </c>
     </row>
@@ -5246,19 +5261,19 @@
       <c r="A248" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248" s="4" t="n">
         <v>94.72169403388212</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C248" s="4" t="n">
         <v>94.77152201214992</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D248" s="4" t="n">
         <v>94.6020931991234</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" s="4" t="n">
         <v>94.64196014404295</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F248" s="4" t="n">
         <v>3215100</v>
       </c>
     </row>
@@ -5266,19 +5281,19 @@
       <c r="A249" s="6" t="n">
         <v>46153</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249" s="4" t="n">
         <v>94.54230059829504</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C249" s="4" t="n">
         <v>94.56223026968</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D249" s="4" t="n">
         <v>94.32303619384766</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" s="4" t="n">
         <v>94.32303619384766</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F249" s="4" t="n">
         <v>4025400</v>
       </c>
     </row>
@@ -5286,19 +5301,19 @@
       <c r="A250" s="6" t="n">
         <v>46154</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250" s="4" t="n">
         <v>94.10376817503985</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C250" s="4" t="n">
         <v>94.11373681227072</v>
       </c>
-      <c r="D250" t="n">
+      <c r="D250" s="4" t="n">
         <v>93.98417494363832</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="4" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250" s="4" t="n">
         <v>5686700</v>
       </c>
     </row>
@@ -5306,19 +5321,19 @@
       <c r="A251" s="6" t="n">
         <v>46155</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251" s="4" t="n">
         <v>93.98417494363832</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C251" s="4" t="n">
         <v>94.06390122995856</v>
       </c>
-      <c r="D251" t="n">
+      <c r="D251" s="4" t="n">
         <v>93.79480885546288</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="4" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251" s="4" t="n">
         <v>3459200</v>
       </c>
     </row>
@@ -5326,19 +5341,19 @@
       <c r="A252" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252" s="4" t="n">
         <v>94.22336642398864</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C252" s="4" t="n">
         <v>94.24329609406108</v>
       </c>
-      <c r="D252" t="n">
+      <c r="D252" s="4" t="n">
         <v>93.93433678296461</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="4" t="n">
         <v>93.94430541992188</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252" s="4" t="n">
         <v>5167300</v>
       </c>
     </row>
@@ -5346,19 +5361,19 @@
       <c r="A253" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253" s="4" t="n">
         <v>93.40611888617302</v>
       </c>
-      <c r="C253" t="n">
+      <c r="C253" s="4" t="n">
         <v>93.43601719506064</v>
       </c>
-      <c r="D253" t="n">
+      <c r="D253" s="4" t="n">
         <v>93.17688584496376</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="4" t="n">
         <v>93.1968231201172</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253" s="4" t="n">
         <v>12498700</v>
       </c>
     </row>
@@ -5366,19 +5381,19 @@
       <c r="A254" s="6" t="n">
         <v>46160</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254" s="4" t="n">
         <v>93.30645104572598</v>
       </c>
-      <c r="C254" t="n">
+      <c r="C254" s="4" t="n">
         <v>93.43601291291536</v>
       </c>
-      <c r="D254" t="n">
+      <c r="D254" s="4" t="n">
         <v>93.02738243326527</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="4" t="n">
         <v>93.15695190429688</v>
       </c>
-      <c r="F254" t="n">
+      <c r="F254" s="4" t="n">
         <v>8422900</v>
       </c>
     </row>
@@ -5386,19 +5401,19 @@
       <c r="A255" s="6" t="n">
         <v>46161</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255" s="4" t="n">
         <v>92.8180864086212</v>
       </c>
-      <c r="C255" t="n">
+      <c r="C255" s="4" t="n">
         <v>92.95761691252729</v>
       </c>
-      <c r="D255" t="n">
+      <c r="D255" s="4" t="n">
         <v>92.63868896019304</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="4" t="n">
         <v>92.79815673828124</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255" s="4" t="n">
         <v>10069800</v>
       </c>
     </row>
@@ -5406,19 +5421,19 @@
       <c r="A256" s="6" t="n">
         <v>46162</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256" s="4" t="n">
         <v>92.85795760011084</v>
       </c>
-      <c r="C256" t="n">
+      <c r="C256" s="4" t="n">
         <v>93.49581353395244</v>
       </c>
-      <c r="D256" t="n">
+      <c r="D256" s="4" t="n">
         <v>92.8380279288594</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="4" t="n">
         <v>93.42604827880859</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256" s="4" t="n">
         <v>14892500</v>
       </c>
     </row>
@@ -5426,19 +5441,19 @@
       <c r="A257" s="6" t="n">
         <v>46163</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257" s="4" t="n">
         <v>93.15695088636282</v>
       </c>
-      <c r="C257" t="n">
+      <c r="C257" s="4" t="n">
         <v>93.52570681350404</v>
       </c>
-      <c r="D257" t="n">
+      <c r="D257" s="4" t="n">
         <v>92.99748310955638</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="4" t="n">
         <v>93.48584747314452</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257" s="4" t="n">
         <v>7762000</v>
       </c>
     </row>
@@ -5446,19 +5461,19 @@
       <c r="A258" s="6" t="n">
         <v>46164</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258" s="4" t="n">
         <v>93.64530853515627</v>
       </c>
-      <c r="C258" t="n">
+      <c r="C258" s="4" t="n">
         <v>93.6752068426308</v>
       </c>
-      <c r="D258" t="n">
+      <c r="D258" s="4" t="n">
         <v>93.31641194525211</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258" s="4" t="n">
         <v>93.56557464599609</v>
       </c>
-      <c r="F258" t="n">
+      <c r="F258" s="4" t="n">
         <v>6321900</v>
       </c>
     </row>
@@ -5466,19 +5481,19 @@
       <c r="A259" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259" s="4" t="n">
         <v>94.02403764567016</v>
       </c>
-      <c r="C259" t="n">
+      <c r="C259" s="4" t="n">
         <v>94.03400628325736</v>
       </c>
-      <c r="D259" t="n">
+      <c r="D259" s="4" t="n">
         <v>93.81474187939416</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" s="4" t="n">
         <v>93.96424102783205</v>
       </c>
-      <c r="F259" t="n">
+      <c r="F259" s="4" t="n">
         <v>5494400</v>
       </c>
     </row>
@@ -5486,19 +5501,19 @@
       <c r="A260" s="6" t="n">
         <v>46169</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260" s="4" t="n">
         <v>94.0340029221082</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C260" s="4" t="n">
         <v>94.16357239458289</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D260" s="4" t="n">
         <v>93.97420630640744</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260" s="4" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F260" t="n">
+      <c r="F260" s="4" t="n">
         <v>5958800</v>
       </c>
     </row>
@@ -5506,19 +5521,19 @@
       <c r="A261" s="6" t="n">
         <v>46170</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261" s="4" t="n">
         <v>94.03399970200064</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261" s="4" t="n">
         <v>94.35292764788709</v>
       </c>
-      <c r="D261" t="n">
+      <c r="D261" s="4" t="n">
         <v>93.97420308834756</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261" s="4" t="n">
         <v>94.22336578369141</v>
       </c>
-      <c r="F261" t="n">
+      <c r="F261" s="4" t="n">
         <v>5938300</v>
       </c>
     </row>
@@ -5526,19 +5541,19 @@
       <c r="A262" s="6" t="n">
         <v>46171</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262" s="4" t="n">
         <v>94.32303154598291</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C262" s="4" t="n">
         <v>94.42269510568184</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D262" s="4" t="n">
         <v>94.21339934916148</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262" s="4" t="n">
         <v>94.33300018310548</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F262" s="4" t="n">
         <v>9639700</v>
       </c>
     </row>
@@ -5546,19 +5561,19 @@
       <c r="A263" s="6" t="n">
         <v>46174</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263" s="4" t="n">
         <v>93.91000366210938</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C263" s="4" t="n">
         <v>94.1999969482422</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D263" s="4" t="n">
         <v>93.80999755859376</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263" s="4" t="n">
         <v>94.16999816894533</v>
       </c>
-      <c r="F263" t="n">
+      <c r="F263" s="4" t="n">
         <v>8054100</v>
       </c>
     </row>
@@ -5566,19 +5581,19 @@
       <c r="A264" s="6" t="n">
         <v>46175</v>
       </c>
-      <c r="B264" t="n">
+      <c r="B264" s="4" t="n">
         <v>94.33000183105467</v>
       </c>
-      <c r="C264" t="n">
+      <c r="C264" s="4" t="n">
         <v>94.33000183105467</v>
       </c>
-      <c r="D264" t="n">
+      <c r="D264" s="4" t="n">
         <v>94.16000366210938</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264" s="4" t="n">
         <v>94.23999786376952</v>
       </c>
-      <c r="F264" t="n">
+      <c r="F264" s="4" t="n">
         <v>15426600</v>
       </c>
     </row>
@@ -5586,19 +5601,19 @@
       <c r="A265" s="6" t="n">
         <v>46176</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265" s="4" t="n">
         <v>93.98999786376952</v>
       </c>
-      <c r="C265" t="n">
+      <c r="C265" s="4" t="n">
         <v>94.09999847412109</v>
       </c>
-      <c r="D265" t="n">
+      <c r="D265" s="4" t="n">
         <v>93.91000366210938</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="F265" t="n">
+      <c r="F265" s="4" t="n">
         <v>7056500</v>
       </c>
     </row>
@@ -5606,19 +5621,19 @@
       <c r="A266" s="6" t="n">
         <v>46177</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266" s="4" t="n">
         <v>94.1999969482422</v>
       </c>
-      <c r="C266" t="n">
+      <c r="C266" s="4" t="n">
         <v>94.27999877929688</v>
       </c>
-      <c r="D266" t="n">
+      <c r="D266" s="4" t="n">
         <v>94.08999633789062</v>
       </c>
-      <c r="E266" t="n">
+      <c r="E266" s="4" t="n">
         <v>94.12000274658205</v>
       </c>
-      <c r="F266" t="n">
+      <c r="F266" s="4" t="n">
         <v>4417100</v>
       </c>
     </row>

--- a/engine/techniques/kronos_forecast/resources/templates/kronos_forecast_input_template.xlsx
+++ b/engine/techniques/kronos_forecast/resources/templates/kronos_forecast_input_template.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -89,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -99,6 +100,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,11 +470,11 @@
   <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -641,19 +644,19 @@
       <c r="A17" s="6" t="n">
         <v>45814</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="7" t="n">
         <v>90.26361121560964</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="7" t="n">
         <v>90.34061328714786</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="7" t="n">
         <v>89.97486446232391</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="7" t="n">
         <v>90.00373840332031</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="8" t="n">
         <v>7624200</v>
       </c>
     </row>
@@ -661,19 +664,19 @@
       <c r="A18" s="6" t="n">
         <v>45817</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="7" t="n">
         <v>90.01335426202118</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="7" t="n">
         <v>90.28286150074972</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="7" t="n">
         <v>90.00373451098622</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="7" t="n">
         <v>90.1673583984375</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="8" t="n">
         <v>6061200</v>
       </c>
     </row>
@@ -681,19 +684,19 @@
       <c r="A19" s="6" t="n">
         <v>45818</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="7" t="n">
         <v>90.45611502185869</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="7" t="n">
         <v>90.49460871372196</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="7" t="n">
         <v>90.22510881074938</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="7" t="n">
         <v>90.32135772705078</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="8" t="n">
         <v>5579900</v>
       </c>
     </row>
@@ -701,19 +704,19 @@
       <c r="A20" s="6" t="n">
         <v>45819</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="7" t="n">
         <v>90.4945993178188</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="7" t="n">
         <v>90.73522525524936</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="7" t="n">
         <v>90.41760459876488</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="7" t="n">
         <v>90.6967315673828</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="8" t="n">
         <v>6594900</v>
       </c>
     </row>
@@ -721,19 +724,19 @@
       <c r="A21" s="6" t="n">
         <v>45820</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="7" t="n">
         <v>91.04322624525842</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="7" t="n">
         <v>91.1009814637531</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="7" t="n">
         <v>90.87960237005198</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="7" t="n">
         <v>91.0913543701172</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="8" t="n">
         <v>7795400</v>
       </c>
     </row>
@@ -741,19 +744,19 @@
       <c r="A22" s="6" t="n">
         <v>45821</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="7" t="n">
         <v>90.88924367206336</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="7" t="n">
         <v>90.95661865140561</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="7" t="n">
         <v>90.51386773811063</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="7" t="n">
         <v>90.75449371337891</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="8" t="n">
         <v>9195200</v>
       </c>
     </row>
@@ -761,19 +764,19 @@
       <c r="A23" s="6" t="n">
         <v>45824</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="7" t="n">
         <v>90.64861015421847</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="7" t="n">
         <v>90.84110798108718</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="7" t="n">
         <v>90.4753591727081</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="7" t="n">
         <v>90.49460601806641</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="8" t="n">
         <v>7508400</v>
       </c>
     </row>
@@ -781,19 +784,19 @@
       <c r="A24" s="6" t="n">
         <v>45825</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="7" t="n">
         <v>90.72561827062786</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="7" t="n">
         <v>90.97586399357584</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="7" t="n">
         <v>90.5812412191906</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="7" t="n">
         <v>90.93737030029295</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="8" t="n">
         <v>5285000</v>
       </c>
     </row>
@@ -801,19 +804,19 @@
       <c r="A25" s="6" t="n">
         <v>45826</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="7" t="n">
         <v>91.09136610629736</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="7" t="n">
         <v>91.28386394389206</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="7" t="n">
         <v>90.84111304276681</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="7" t="n">
         <v>90.9951171875</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="8" t="n">
         <v>6732400</v>
       </c>
     </row>
@@ -821,19 +824,19 @@
       <c r="A26" s="6" t="n">
         <v>45828</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="7" t="n">
         <v>90.81223810868332</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="7" t="n">
         <v>91.18761402821455</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="7" t="n">
         <v>90.75449022670058</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="7" t="n">
         <v>91.05286407470705</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="8" t="n">
         <v>6261700</v>
       </c>
     </row>
@@ -841,19 +844,19 @@
       <c r="A27" s="6" t="n">
         <v>45831</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="7" t="n">
         <v>91.31274314653469</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="7" t="n">
         <v>91.66886487229723</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="7" t="n">
         <v>91.24536817058052</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="7" t="n">
         <v>91.37049102783205</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="8" t="n">
         <v>9310300</v>
       </c>
     </row>
@@ -861,19 +864,19 @@
       <c r="A28" s="6" t="n">
         <v>45832</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="7" t="n">
         <v>91.28386078667523</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="7" t="n">
         <v>91.73623876703049</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="7" t="n">
         <v>91.24536709514511</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="7" t="n">
         <v>91.68811798095705</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="8" t="n">
         <v>7694500</v>
       </c>
     </row>
@@ -881,19 +884,19 @@
       <c r="A29" s="6" t="n">
         <v>45833</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="7" t="n">
         <v>91.51486389291787</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="7" t="n">
         <v>91.76510959598669</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="7" t="n">
         <v>91.41861498071285</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="7" t="n">
         <v>91.72661590576172</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="8" t="n">
         <v>6393300</v>
       </c>
     </row>
@@ -901,19 +904,19 @@
       <c r="A30" s="6" t="n">
         <v>45834</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="7" t="n">
         <v>91.89987435141001</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="7" t="n">
         <v>92.0634982497842</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="7" t="n">
         <v>91.77474414638814</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="7" t="n">
         <v>92.05387115478516</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="8" t="n">
         <v>7131900</v>
       </c>
     </row>
@@ -921,19 +924,19 @@
       <c r="A31" s="6" t="n">
         <v>45835</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="7" t="n">
         <v>91.81324005126952</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="7" t="n">
         <v>92.09236704406506</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="7" t="n">
         <v>91.75549217114684</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="7" t="n">
         <v>91.81324005126952</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="8" t="n">
         <v>8402400</v>
       </c>
     </row>
@@ -941,19 +944,19 @@
       <c r="A32" s="6" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="7" t="n">
         <v>92.01536171227636</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="7" t="n">
         <v>92.21748662886024</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="7" t="n">
         <v>91.88061176788712</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="7" t="n">
         <v>92.17898559570312</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="8" t="n">
         <v>10542300</v>
       </c>
     </row>
@@ -961,19 +964,19 @@
       <c r="A33" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="7" t="n">
         <v>92.13359949434631</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="7" t="n">
         <v>92.2205035986628</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="7" t="n">
         <v>91.84393633542214</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="7" t="n">
         <v>92.00807952880859</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="8" t="n">
         <v>10659800</v>
       </c>
     </row>
@@ -981,19 +984,19 @@
       <c r="A34" s="6" t="n">
         <v>45840</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="7" t="n">
         <v>91.71841752854527</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="7" t="n">
         <v>91.86325280478364</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="7" t="n">
         <v>91.6604863647012</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="7" t="n">
         <v>91.81497192382812</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="8" t="n">
         <v>6026200</v>
       </c>
     </row>
@@ -1001,19 +1004,19 @@
       <c r="A35" s="6" t="n">
         <v>45841</v>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="7" t="n">
         <v>91.53496875245619</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="7" t="n">
         <v>91.59289991779704</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="7" t="n">
         <v>91.38047582270951</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="7" t="n">
         <v>91.49634552001952</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="8" t="n">
         <v>7398900</v>
       </c>
     </row>
@@ -1021,19 +1024,19 @@
       <c r="A36" s="6" t="n">
         <v>45845</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="7" t="n">
         <v>91.35150030328847</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="7" t="n">
         <v>91.36115795200422</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="7" t="n">
         <v>91.12941858259164</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="7" t="n">
         <v>91.2066650390625</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="8" t="n">
         <v>8518600</v>
       </c>
     </row>
@@ -1041,19 +1044,19 @@
       <c r="A37" s="6" t="n">
         <v>45846</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="7" t="n">
         <v>90.96528301126028</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="7" t="n">
         <v>91.08115270567748</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="7" t="n">
         <v>90.9170094968909</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="7" t="n">
         <v>91.07149505615234</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="8" t="n">
         <v>5282800</v>
       </c>
     </row>
@@ -1061,19 +1064,19 @@
       <c r="A38" s="6" t="n">
         <v>45847</v>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="7" t="n">
         <v>91.2066650310782</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="7" t="n">
         <v>91.55426671853913</v>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="7" t="n">
         <v>91.2066650310782</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="7" t="n">
         <v>91.54460906982422</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="8" t="n">
         <v>6900800</v>
       </c>
     </row>
@@ -1081,19 +1084,19 @@
       <c r="A39" s="6" t="n">
         <v>45848</v>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="7" t="n">
         <v>91.47703022048702</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="7" t="n">
         <v>91.5156534529237</v>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="7" t="n">
         <v>91.31288700760244</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="7" t="n">
         <v>91.49634552001952</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="8" t="n">
         <v>4451900</v>
       </c>
     </row>
@@ -1101,19 +1104,19 @@
       <c r="A40" s="6" t="n">
         <v>45849</v>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="7" t="n">
         <v>91.18736475056954</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="7" t="n">
         <v>91.2163303325168</v>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="7" t="n">
         <v>91.02321417515481</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="7" t="n">
         <v>91.07149505615234</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="8" t="n">
         <v>6004300</v>
       </c>
     </row>
@@ -1121,19 +1124,19 @@
       <c r="A41" s="6" t="n">
         <v>45852</v>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="7" t="n">
         <v>91.07148302861764</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="7" t="n">
         <v>91.20666063760449</v>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="7" t="n">
         <v>90.92664777138113</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="7" t="n">
         <v>91.03285980224609</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="8" t="n">
         <v>5101600</v>
       </c>
     </row>
@@ -1141,19 +1144,19 @@
       <c r="A42" s="6" t="n">
         <v>45853</v>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="7" t="n">
         <v>91.13908508329943</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="7" t="n">
         <v>91.14874273295318</v>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="7" t="n">
         <v>90.62734015107434</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="7" t="n">
         <v>90.67562103271484</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="8" t="n">
         <v>5628100</v>
       </c>
     </row>
@@ -1161,19 +1164,19 @@
       <c r="A43" s="6" t="n">
         <v>45854</v>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="7" t="n">
         <v>90.82044658682167</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="7" t="n">
         <v>90.99424744293636</v>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="7" t="n">
         <v>90.69492661109422</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="7" t="n">
         <v>90.92665863037109</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="8" t="n">
         <v>12786300</v>
       </c>
     </row>
@@ -1181,19 +1184,19 @@
       <c r="A44" s="6" t="n">
         <v>45855</v>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="7" t="n">
         <v>90.97494391443792</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="7" t="n">
         <v>91.08115596312859</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="7" t="n">
         <v>90.82045098302299</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="7" t="n">
         <v>90.89769744873048</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="8" t="n">
         <v>4747200</v>
       </c>
     </row>
@@ -1201,19 +1204,19 @@
       <c r="A45" s="6" t="n">
         <v>45856</v>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="7" t="n">
         <v>91.15838506502314</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="7" t="n">
         <v>91.2259738679858</v>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="7" t="n">
         <v>91.0521730365637</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="7" t="n">
         <v>91.1487274169922</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="8" t="n">
         <v>4035000</v>
       </c>
     </row>
@@ -1221,19 +1224,19 @@
       <c r="A46" s="6" t="n">
         <v>45859</v>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="7" t="n">
         <v>91.53495788667372</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="7" t="n">
         <v>91.63151227298958</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="7" t="n">
         <v>91.41908820311816</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="7" t="n">
         <v>91.46736907958984</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="8" t="n">
         <v>5232300</v>
       </c>
     </row>
@@ -1241,19 +1244,19 @@
       <c r="A47" s="6" t="n">
         <v>45860</v>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="7" t="n">
         <v>91.5639375308982</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="7" t="n">
         <v>91.78601191687449</v>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D47" s="7" t="n">
         <v>91.54462223069154</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="7" t="n">
         <v>91.72808074951172</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="8" t="n">
         <v>6098000</v>
       </c>
     </row>
@@ -1261,19 +1264,19 @@
       <c r="A48" s="6" t="n">
         <v>45861</v>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="7" t="n">
         <v>91.51563495130084</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="7" t="n">
         <v>91.5735661049298</v>
       </c>
-      <c r="D48" s="4" t="n">
+      <c r="D48" s="7" t="n">
         <v>91.35149177160092</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="7" t="n">
         <v>91.39977264404295</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="8" t="n">
         <v>5074000</v>
       </c>
     </row>
@@ -1281,19 +1284,19 @@
       <c r="A49" s="6" t="n">
         <v>45862</v>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="7" t="n">
         <v>91.08115152230759</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="7" t="n">
         <v>91.36116442187333</v>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D49" s="7" t="n">
         <v>91.07149387290794</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="7" t="n">
         <v>91.2646026611328</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="8" t="n">
         <v>5867400</v>
       </c>
     </row>
@@ -1301,19 +1304,19 @@
       <c r="A50" s="6" t="n">
         <v>45863</v>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="7" t="n">
         <v>91.235630612188</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="7" t="n">
         <v>91.47702026367188</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="7" t="n">
         <v>91.19700738395528</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="7" t="n">
         <v>91.47702026367188</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="8" t="n">
         <v>3614000</v>
       </c>
     </row>
@@ -1321,19 +1324,19 @@
       <c r="A51" s="6" t="n">
         <v>45866</v>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="7" t="n">
         <v>91.31288470607257</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="7" t="n">
         <v>91.38047351947608</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="7" t="n">
         <v>91.2356382431462</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="7" t="n">
         <v>91.27426147460938</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="8" t="n">
         <v>5073200</v>
       </c>
     </row>
@@ -1341,19 +1344,19 @@
       <c r="A52" s="6" t="n">
         <v>45867</v>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="7" t="n">
         <v>91.40944573075043</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="7" t="n">
         <v>91.87291717529295</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="7" t="n">
         <v>91.39013779693266</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="7" t="n">
         <v>91.87291717529295</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="8" t="n">
         <v>7864000</v>
       </c>
     </row>
@@ -1361,19 +1364,19 @@
       <c r="A53" s="6" t="n">
         <v>45868</v>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="7" t="n">
         <v>91.55427551269533</v>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="C53" s="7" t="n">
         <v>91.80532283700396</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="7" t="n">
         <v>91.48668669845394</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="7" t="n">
         <v>91.55427551269533</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="8" t="n">
         <v>7425600</v>
       </c>
     </row>
@@ -1381,19 +1384,19 @@
       <c r="A54" s="6" t="n">
         <v>45869</v>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="7" t="n">
         <v>91.699104312396</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="7" t="n">
         <v>91.8535898626214</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="7" t="n">
         <v>91.5928922737164</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="7" t="n">
         <v>91.63151550292967</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="8" t="n">
         <v>10411800</v>
       </c>
     </row>
@@ -1401,19 +1404,19 @@
       <c r="A55" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="7" t="n">
         <v>92.37647453039052</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C55" s="7" t="n">
         <v>92.73490100980582</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="7" t="n">
         <v>92.35709613112816</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="7" t="n">
         <v>92.68646240234376</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="8" t="n">
         <v>11870100</v>
       </c>
     </row>
@@ -1421,19 +1424,19 @@
       <c r="A56" s="6" t="n">
         <v>45873</v>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="7" t="n">
         <v>92.77363615412176</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="7" t="n">
         <v>92.8511349640423</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="7" t="n">
         <v>92.54114711505346</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="7" t="n">
         <v>92.81238555908205</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="8" t="n">
         <v>8449500</v>
       </c>
     </row>
@@ -1441,19 +1444,19 @@
       <c r="A57" s="6" t="n">
         <v>45874</v>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="7" t="n">
         <v>92.64770568390176</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="7" t="n">
         <v>92.86082371480806</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="7" t="n">
         <v>92.62833467686175</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="7" t="n">
         <v>92.74457550048828</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="8" t="n">
         <v>8218700</v>
       </c>
     </row>
@@ -1461,19 +1464,19 @@
       <c r="A58" s="6" t="n">
         <v>45875</v>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="7" t="n">
         <v>92.60894820773012</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="7" t="n">
         <v>92.7251964119182</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="7" t="n">
         <v>92.27958938190278</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="7" t="n">
         <v>92.6767578125</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="8" t="n">
         <v>10107500</v>
       </c>
     </row>
@@ -1481,19 +1484,19 @@
       <c r="A59" s="6" t="n">
         <v>45876</v>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="7" t="n">
         <v>92.67676499332474</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="7" t="n">
         <v>92.77363480897422</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="7" t="n">
         <v>92.54114577327684</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="7" t="n">
         <v>92.60895538330078</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="8" t="n">
         <v>5725900</v>
       </c>
     </row>
@@ -1501,19 +1504,19 @@
       <c r="A60" s="6" t="n">
         <v>45877</v>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="7" t="n">
         <v>92.48302388263993</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="7" t="n">
         <v>92.48302388263993</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="7" t="n">
         <v>92.3474046647614</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="7" t="n">
         <v>92.39583587646484</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="8" t="n">
         <v>5623800</v>
       </c>
     </row>
@@ -1521,19 +1524,19 @@
       <c r="A61" s="6" t="n">
         <v>45880</v>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="7" t="n">
         <v>92.4636382502884</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="7" t="n">
         <v>92.55082624964116</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="7" t="n">
         <v>92.37645764162812</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="7" t="n">
         <v>92.42489624023438</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="8" t="n">
         <v>4920200</v>
       </c>
     </row>
@@ -1541,19 +1544,19 @@
       <c r="A62" s="6" t="n">
         <v>45881</v>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="7" t="n">
         <v>92.30864777188422</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="7" t="n">
         <v>92.405517578125</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="7" t="n">
         <v>92.20208876781165</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="7" t="n">
         <v>92.405517578125</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="8" t="n">
         <v>6724600</v>
       </c>
     </row>
@@ -1561,19 +1564,19 @@
       <c r="A63" s="6" t="n">
         <v>45882</v>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="7" t="n">
         <v>92.6670765642546</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="7" t="n">
         <v>92.83175597816179</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="7" t="n">
         <v>92.64769816809334</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="7" t="n">
         <v>92.73488616943359</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="8" t="n">
         <v>5925200</v>
       </c>
     </row>
@@ -1581,19 +1584,19 @@
       <c r="A64" s="6" t="n">
         <v>45883</v>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="7" t="n">
         <v>92.57988634685496</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="7" t="n">
         <v>92.60894654970856</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="7" t="n">
         <v>92.36676833833866</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="7" t="n">
         <v>92.43457794189452</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="8" t="n">
         <v>5527500</v>
       </c>
     </row>
@@ -1601,19 +1604,19 @@
       <c r="A65" s="6" t="n">
         <v>45884</v>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="7" t="n">
         <v>92.39582744076009</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="7" t="n">
         <v>92.45395523646744</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="7" t="n">
         <v>92.19239863251528</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="7" t="n">
         <v>92.25052642822266</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="8" t="n">
         <v>7428500</v>
       </c>
     </row>
@@ -1621,19 +1624,19 @@
       <c r="A66" s="6" t="n">
         <v>45887</v>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="7" t="n">
         <v>92.3183505917184</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="7" t="n">
         <v>92.32803240028636</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="7" t="n">
         <v>92.07617234503572</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="7" t="n">
         <v>92.16335296630859</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="8" t="n">
         <v>9669600</v>
       </c>
     </row>
@@ -1641,19 +1644,19 @@
       <c r="A67" s="6" t="n">
         <v>45888</v>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="7" t="n">
         <v>92.29896606236493</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="7" t="n">
         <v>92.43458528024344</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="7" t="n">
         <v>92.28927686374701</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="7" t="n">
         <v>92.39583587646484</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="F67" s="8" t="n">
         <v>6499300</v>
       </c>
     </row>
@@ -1661,19 +1664,19 @@
       <c r="A68" s="6" t="n">
         <v>45889</v>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="7" t="n">
         <v>92.39582915624329</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="7" t="n">
         <v>92.61863636409146</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="7" t="n">
         <v>92.37645815110946</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="7" t="n">
         <v>92.5314483642578</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="8" t="n">
         <v>6270700</v>
       </c>
     </row>
@@ -1681,19 +1684,19 @@
       <c r="A69" s="6" t="n">
         <v>45890</v>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="7" t="n">
         <v>92.40551653294666</v>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="C69" s="7" t="n">
         <v>92.4539551308654</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="7" t="n">
         <v>92.13427812226342</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="7" t="n">
         <v>92.2602081298828</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="8" t="n">
         <v>5351300</v>
       </c>
     </row>
@@ -1701,19 +1704,19 @@
       <c r="A70" s="6" t="n">
         <v>45891</v>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="7" t="n">
         <v>92.41519400345044</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="7" t="n">
         <v>92.88017196541952</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="7" t="n">
         <v>92.3861338046638</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="7" t="n">
         <v>92.77361297607422</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="8" t="n">
         <v>10867700</v>
       </c>
     </row>
@@ -1721,19 +1724,19 @@
       <c r="A71" s="6" t="n">
         <v>45894</v>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="7" t="n">
         <v>92.60894772644244</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C71" s="7" t="n">
         <v>92.71550673205458</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="7" t="n">
         <v>92.54113812202496</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="7" t="n">
         <v>92.58957672119141</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="8" t="n">
         <v>9936400</v>
       </c>
     </row>
@@ -1741,19 +1744,19 @@
       <c r="A72" s="6" t="n">
         <v>45895</v>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="7" t="n">
         <v>92.66707717680109</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="7" t="n">
         <v>92.86081679553816</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="7" t="n">
         <v>92.60894937862579</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="7" t="n">
         <v>92.83175659179688</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="8" t="n">
         <v>5871200</v>
       </c>
     </row>
@@ -1761,19 +1764,19 @@
       <c r="A73" s="6" t="n">
         <v>45896</v>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="7" t="n">
         <v>92.7058279877547</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="7" t="n">
         <v>93.00613403320312</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="7" t="n">
         <v>92.64770757475526</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="7" t="n">
         <v>93.00613403320312</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="8" t="n">
         <v>5222800</v>
       </c>
     </row>
@@ -1781,19 +1784,19 @@
       <c r="A74" s="6" t="n">
         <v>45897</v>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="7" t="n">
         <v>92.97706768488661</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="7" t="n">
         <v>93.21924591064452</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="7" t="n">
         <v>92.9383182818822</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="7" t="n">
         <v>93.21924591064452</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="8" t="n">
         <v>6544700</v>
       </c>
     </row>
@@ -1801,19 +1804,19 @@
       <c r="A75" s="6" t="n">
         <v>45898</v>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="7" t="n">
         <v>93.11268631659811</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="7" t="n">
         <v>93.21924532651931</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="7" t="n">
         <v>93.02549831271126</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="7" t="n">
         <v>93.14174652099609</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="8" t="n">
         <v>6818900</v>
       </c>
     </row>
@@ -1821,19 +1824,19 @@
       <c r="A76" s="6" t="n">
         <v>45902</v>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="7" t="n">
         <v>92.77632636850764</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="7" t="n">
         <v>92.94154536866878</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="7" t="n">
         <v>92.7471709467038</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="7" t="n">
         <v>92.86380004882812</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="8" t="n">
         <v>8623200</v>
       </c>
     </row>
@@ -1841,19 +1844,19 @@
       <c r="A77" s="6" t="n">
         <v>45903</v>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="7" t="n">
         <v>92.87349817544307</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="7" t="n">
         <v>93.32056520373892</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="7" t="n">
         <v>92.87349817544307</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="7" t="n">
         <v>93.18450164794922</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="8" t="n">
         <v>7586100</v>
       </c>
     </row>
@@ -1861,19 +1864,19 @@
       <c r="A78" s="6" t="n">
         <v>45904</v>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="7" t="n">
         <v>93.41776353905608</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="7" t="n">
         <v>93.6024169921875</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="7" t="n">
         <v>93.30113445162468</v>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="7" t="n">
         <v>93.6024169921875</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="8" t="n">
         <v>6395300</v>
       </c>
     </row>
@@ -1881,19 +1884,19 @@
       <c r="A79" s="6" t="n">
         <v>45905</v>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="7" t="n">
         <v>94.1855541321566</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="7" t="n">
         <v>94.29245485933237</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="7" t="n">
         <v>94.0592041015625</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="7" t="n">
         <v>94.0592041015625</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="8" t="n">
         <v>9566300</v>
       </c>
     </row>
@@ -1901,19 +1904,19 @@
       <c r="A80" s="6" t="n">
         <v>45908</v>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="7" t="n">
         <v>94.29245079485916</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="7" t="n">
         <v>94.36048257189736</v>
       </c>
-      <c r="D80" s="4" t="n">
+      <c r="D80" s="7" t="n">
         <v>94.19526360121996</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="7" t="n">
         <v>94.35076904296876</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="8" t="n">
         <v>7599600</v>
       </c>
     </row>
@@ -1921,19 +1924,19 @@
       <c r="A81" s="6" t="n">
         <v>45909</v>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="7" t="n">
         <v>94.30217533378048</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="7" t="n">
         <v>94.40908347533154</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="D81" s="7" t="n">
         <v>94.03976915946016</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="7" t="n">
         <v>94.12723541259766</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="8" t="n">
         <v>8223100</v>
       </c>
     </row>
@@ -1941,19 +1944,19 @@
       <c r="A82" s="6" t="n">
         <v>45910</v>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="7" t="n">
         <v>94.32161775311396</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C82" s="7" t="n">
         <v>94.49655767528152</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="D82" s="7" t="n">
         <v>94.23414408457624</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="7" t="n">
         <v>94.3799285888672</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="8" t="n">
         <v>8864500</v>
       </c>
     </row>
@@ -1961,19 +1964,19 @@
       <c r="A83" s="6" t="n">
         <v>45911</v>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="7" t="n">
         <v>94.50626917146556</v>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C83" s="7" t="n">
         <v>94.72008545117126</v>
       </c>
-      <c r="D83" s="4" t="n">
+      <c r="D83" s="7" t="n">
         <v>94.49655564232094</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="7" t="n">
         <v>94.52571105957033</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="8" t="n">
         <v>8554300</v>
       </c>
     </row>
@@ -1981,19 +1984,19 @@
       <c r="A84" s="6" t="n">
         <v>45912</v>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="7" t="n">
         <v>94.30218334016776</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="7" t="n">
         <v>94.31190428519989</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="D84" s="7" t="n">
         <v>94.1175224591002</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="7" t="n">
         <v>94.25359344482422</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="8" t="n">
         <v>36502700</v>
       </c>
     </row>
@@ -2001,19 +2004,19 @@
       <c r="A85" s="6" t="n">
         <v>45915</v>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="7" t="n">
         <v>94.41880907945216</v>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C85" s="7" t="n">
         <v>94.48684086244155</v>
       </c>
-      <c r="D85" s="4" t="n">
+      <c r="D85" s="7" t="n">
         <v>94.37021177092764</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="7" t="n">
         <v>94.40908813476562</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="8" t="n">
         <v>4990100</v>
       </c>
     </row>
@@ -2021,19 +2024,19 @@
       <c r="A86" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="7" t="n">
         <v>94.41880207776036</v>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C86" s="7" t="n">
         <v>94.55486563364929</v>
       </c>
-      <c r="D86" s="4" t="n">
+      <c r="D86" s="7" t="n">
         <v>94.3799257168053</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="7" t="n">
         <v>94.46739196777344</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="8" t="n">
         <v>5847700</v>
       </c>
     </row>
@@ -2041,19 +2044,19 @@
       <c r="A87" s="6" t="n">
         <v>45917</v>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="7" t="n">
         <v>94.56459563659998</v>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="7" t="n">
         <v>94.77840451997352</v>
       </c>
-      <c r="D87" s="4" t="n">
+      <c r="D87" s="7" t="n">
         <v>94.14668398493301</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="7" t="n">
         <v>94.2633056640625</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="8" t="n">
         <v>10701700</v>
       </c>
     </row>
@@ -2061,19 +2064,19 @@
       <c r="A88" s="6" t="n">
         <v>45918</v>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="7" t="n">
         <v>93.93285129510748</v>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="7" t="n">
         <v>94.08834931178146</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="D88" s="7" t="n">
         <v>93.7967877499276</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="7" t="n">
         <v>93.95228576660156</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="8" t="n">
         <v>7589200</v>
       </c>
     </row>
@@ -2081,19 +2084,19 @@
       <c r="A89" s="6" t="n">
         <v>45919</v>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="7" t="n">
         <v>93.90371572990716</v>
       </c>
-      <c r="C89" s="4" t="n">
+      <c r="C89" s="7" t="n">
         <v>93.9814610472245</v>
       </c>
-      <c r="D89" s="4" t="n">
+      <c r="D89" s="7" t="n">
         <v>93.78708663156814</v>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="7" t="n">
         <v>93.91342926025391</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="8" t="n">
         <v>5528800</v>
       </c>
     </row>
@@ -2101,19 +2104,19 @@
       <c r="A90" s="6" t="n">
         <v>45922</v>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="7" t="n">
         <v>93.91341734133194</v>
       </c>
-      <c r="C90" s="4" t="n">
+      <c r="C90" s="7" t="n">
         <v>93.94258017339702</v>
       </c>
-      <c r="D90" s="4" t="n">
+      <c r="D90" s="7" t="n">
         <v>93.74819836750174</v>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="7" t="n">
         <v>93.75791931152344</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="8" t="n">
         <v>5282700</v>
       </c>
     </row>
@@ -2121,19 +2124,19 @@
       <c r="A91" s="6" t="n">
         <v>45923</v>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="7" t="n">
         <v>93.89398209541996</v>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C91" s="7" t="n">
         <v>94.03004565097294</v>
       </c>
-      <c r="D91" s="4" t="n">
+      <c r="D91" s="7" t="n">
         <v>93.7773530128427</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="7" t="n">
         <v>94.02032470703124</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="8" t="n">
         <v>7077500</v>
       </c>
     </row>
@@ -2141,19 +2144,19 @@
       <c r="A92" s="6" t="n">
         <v>45924</v>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="7" t="n">
         <v>93.9037027152396</v>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C92" s="7" t="n">
         <v>93.9134162442401</v>
       </c>
-      <c r="D92" s="4" t="n">
+      <c r="D92" s="7" t="n">
         <v>93.72876279943137</v>
       </c>
-      <c r="E92" s="4" t="n">
+      <c r="E92" s="7" t="n">
         <v>93.76763916015624</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="F92" s="8" t="n">
         <v>5419700</v>
       </c>
     </row>
@@ -2161,19 +2164,19 @@
       <c r="A93" s="6" t="n">
         <v>45925</v>
       </c>
-      <c r="B93" s="4" t="n">
+      <c r="B93" s="7" t="n">
         <v>93.55383169713518</v>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C93" s="7" t="n">
         <v>93.61214253626208</v>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="D93" s="7" t="n">
         <v>93.39832623958571</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="7" t="n">
         <v>93.56354522705078</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="8" t="n">
         <v>6517500</v>
       </c>
     </row>
@@ -2181,19 +2184,19 @@
       <c r="A94" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="7" t="n">
         <v>93.5441090323086</v>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="7" t="n">
         <v>93.71904896138092</v>
       </c>
-      <c r="D94" s="4" t="n">
+      <c r="D94" s="7" t="n">
         <v>93.42747994129098</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="7" t="n">
         <v>93.51495361328124</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="8" t="n">
         <v>7295300</v>
       </c>
     </row>
@@ -2201,19 +2204,19 @@
       <c r="A95" s="6" t="n">
         <v>45929</v>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="7" t="n">
         <v>93.63158102260439</v>
       </c>
-      <c r="C95" s="4" t="n">
+      <c r="C95" s="7" t="n">
         <v>93.83568379810984</v>
       </c>
-      <c r="D95" s="4" t="n">
+      <c r="D95" s="7" t="n">
         <v>93.62186749227264</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="7" t="n">
         <v>93.78708648681641</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="8" t="n">
         <v>6357500</v>
       </c>
     </row>
@@ -2221,19 +2224,19 @@
       <c r="A96" s="6" t="n">
         <v>45930</v>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="7" t="n">
         <v>93.86482854779052</v>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C96" s="7" t="n">
         <v>94.03976846768649</v>
       </c>
-      <c r="D96" s="4" t="n">
+      <c r="D96" s="7" t="n">
         <v>93.70932310125733</v>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="7" t="n">
         <v>93.74819946289062</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="8" t="n">
         <v>9257800</v>
       </c>
     </row>
@@ -2241,19 +2244,19 @@
       <c r="A97" s="6" t="n">
         <v>45931</v>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="7" t="n">
         <v>94.13229616627872</v>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C97" s="7" t="n">
         <v>94.20053593607309</v>
       </c>
-      <c r="D97" s="4" t="n">
+      <c r="D97" s="7" t="n">
         <v>93.91782619333158</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="7" t="n">
         <v>94.06405639648438</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="8" t="n">
         <v>8347000</v>
       </c>
     </row>
@@ -2261,19 +2264,19 @@
       <c r="A98" s="6" t="n">
         <v>45932</v>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="7" t="n">
         <v>94.02505001762906</v>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="7" t="n">
         <v>94.2200260778786</v>
       </c>
-      <c r="D98" s="4" t="n">
+      <c r="D98" s="7" t="n">
         <v>93.9665609183423</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="7" t="n">
         <v>94.16152954101562</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="8" t="n">
         <v>9420600</v>
       </c>
     </row>
@@ -2281,19 +2284,19 @@
       <c r="A99" s="6" t="n">
         <v>45933</v>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="7" t="n">
         <v>94.17127170566584</v>
       </c>
-      <c r="C99" s="4" t="n">
+      <c r="C99" s="7" t="n">
         <v>94.21026691419692</v>
       </c>
-      <c r="D99" s="4" t="n">
+      <c r="D99" s="7" t="n">
         <v>93.95680177753262</v>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="7" t="n">
         <v>93.97630310058594</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="8" t="n">
         <v>5154300</v>
       </c>
     </row>
@@ -2301,19 +2304,19 @@
       <c r="A100" s="6" t="n">
         <v>45936</v>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="7" t="n">
         <v>93.75210758614294</v>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C100" s="7" t="n">
         <v>93.91783168854346</v>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D100" s="7" t="n">
         <v>93.6936184764904</v>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="7" t="n">
         <v>93.703369140625</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="8" t="n">
         <v>6319600</v>
       </c>
     </row>
@@ -2321,19 +2324,19 @@
       <c r="A101" s="6" t="n">
         <v>45937</v>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="7" t="n">
         <v>93.82033887761988</v>
       </c>
-      <c r="C101" s="4" t="n">
+      <c r="C101" s="7" t="n">
         <v>94.06405339590786</v>
       </c>
-      <c r="D101" s="4" t="n">
+      <c r="D101" s="7" t="n">
         <v>93.76184977325536</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="7" t="n">
         <v>93.93732452392578</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="8" t="n">
         <v>5119900</v>
       </c>
     </row>
@@ -2341,19 +2344,19 @@
       <c r="A102" s="6" t="n">
         <v>45938</v>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="7" t="n">
         <v>94.11280612944996</v>
       </c>
-      <c r="C102" s="4" t="n">
+      <c r="C102" s="7" t="n">
         <v>94.13230001979906</v>
       </c>
-      <c r="D102" s="4" t="n">
+      <c r="D102" s="7" t="n">
         <v>93.898336147723</v>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="7" t="n">
         <v>93.95682525634766</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="8" t="n">
         <v>5141900</v>
       </c>
     </row>
@@ -2361,19 +2364,19 @@
       <c r="A103" s="6" t="n">
         <v>45939</v>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="7" t="n">
         <v>93.8690864329882</v>
       </c>
-      <c r="C103" s="4" t="n">
+      <c r="C103" s="7" t="n">
         <v>93.93732620182466</v>
       </c>
-      <c r="D103" s="4" t="n">
+      <c r="D103" s="7" t="n">
         <v>93.81059732757896</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="7" t="n">
         <v>93.88858032226562</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="8" t="n">
         <v>7130600</v>
       </c>
     </row>
@@ -2381,19 +2384,19 @@
       <c r="A104" s="6" t="n">
         <v>45940</v>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="7" t="n">
         <v>94.22003792139596</v>
       </c>
-      <c r="C104" s="4" t="n">
+      <c r="C104" s="7" t="n">
         <v>94.58073066243853</v>
       </c>
-      <c r="D104" s="4" t="n">
+      <c r="D104" s="7" t="n">
         <v>94.1420474874927</v>
       </c>
-      <c r="E104" s="4" t="n">
+      <c r="E104" s="7" t="n">
         <v>94.47350311279295</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="8" t="n">
         <v>10417700</v>
       </c>
     </row>
@@ -2401,19 +2404,19 @@
       <c r="A105" s="6" t="n">
         <v>45943</v>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="7" t="n">
         <v>94.46374295490376</v>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C105" s="7" t="n">
         <v>94.55147660604422</v>
       </c>
-      <c r="D105" s="4" t="n">
+      <c r="D105" s="7" t="n">
         <v>94.34675731580673</v>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="7" t="n">
         <v>94.52223205566406</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="8" t="n">
         <v>5607600</v>
       </c>
     </row>
@@ -2421,19 +2424,19 @@
       <c r="A106" s="6" t="n">
         <v>45944</v>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="7" t="n">
         <v>94.61970762920625</v>
       </c>
-      <c r="C106" s="4" t="n">
+      <c r="C106" s="7" t="n">
         <v>94.79518235285455</v>
       </c>
-      <c r="D106" s="4" t="n">
+      <c r="D106" s="7" t="n">
         <v>94.54172464792144</v>
       </c>
-      <c r="E106" s="4" t="n">
+      <c r="E106" s="7" t="n">
         <v>94.76593780517578</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="8" t="n">
         <v>7650600</v>
       </c>
     </row>
@@ -2441,19 +2444,19 @@
       <c r="A107" s="6" t="n">
         <v>45945</v>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="7" t="n">
         <v>94.76594927395068</v>
       </c>
-      <c r="C107" s="4" t="n">
+      <c r="C107" s="7" t="n">
         <v>94.88293491639932</v>
       </c>
-      <c r="D107" s="4" t="n">
+      <c r="D107" s="7" t="n">
         <v>94.58072386613452</v>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="7" t="n">
         <v>94.65871429443359</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="8" t="n">
         <v>7769300</v>
       </c>
     </row>
@@ -2461,19 +2464,19 @@
       <c r="A108" s="6" t="n">
         <v>45946</v>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="7" t="n">
         <v>94.58072347283004</v>
       </c>
-      <c r="C108" s="4" t="n">
+      <c r="C108" s="7" t="n">
         <v>95.13639225639128</v>
       </c>
-      <c r="D108" s="4" t="n">
+      <c r="D108" s="7" t="n">
         <v>94.56122958462464</v>
       </c>
-      <c r="E108" s="4" t="n">
+      <c r="E108" s="7" t="n">
         <v>95.09740447998048</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="8" t="n">
         <v>11627200</v>
       </c>
     </row>
@@ -2481,19 +2484,19 @@
       <c r="A109" s="6" t="n">
         <v>45947</v>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="7" t="n">
         <v>95.00966127235247</v>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C109" s="7" t="n">
         <v>95.02916259769999</v>
       </c>
-      <c r="D109" s="4" t="n">
+      <c r="D109" s="7" t="n">
         <v>94.82443586943327</v>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="7" t="n">
         <v>94.94142150878906</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="8" t="n">
         <v>12491000</v>
       </c>
     </row>
@@ -2501,19 +2504,19 @@
       <c r="A110" s="6" t="n">
         <v>45950</v>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="7" t="n">
         <v>94.999913615625</v>
       </c>
-      <c r="C110" s="4" t="n">
+      <c r="C110" s="7" t="n">
         <v>95.07790404432993</v>
       </c>
-      <c r="D110" s="4" t="n">
+      <c r="D110" s="7" t="n">
         <v>94.92193062449672</v>
       </c>
-      <c r="E110" s="4" t="n">
+      <c r="E110" s="7" t="n">
         <v>95.06815338134766</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="F110" s="8" t="n">
         <v>10437800</v>
       </c>
     </row>
@@ -2521,19 +2524,19 @@
       <c r="A111" s="6" t="n">
         <v>45951</v>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="7" t="n">
         <v>95.23388623002488</v>
       </c>
-      <c r="C111" s="4" t="n">
+      <c r="C111" s="7" t="n">
         <v>95.31186922224084</v>
       </c>
-      <c r="D111" s="4" t="n">
+      <c r="D111" s="7" t="n">
         <v>95.17538968889198</v>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="7" t="n">
         <v>95.24362945556641</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="8" t="n">
         <v>7642000</v>
       </c>
     </row>
@@ -2541,19 +2544,19 @@
       <c r="A112" s="6" t="n">
         <v>45952</v>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="7" t="n">
         <v>95.19489042173922</v>
       </c>
-      <c r="C112" s="4" t="n">
+      <c r="C112" s="7" t="n">
         <v>95.31186862812235</v>
       </c>
-      <c r="D112" s="4" t="n">
+      <c r="D112" s="7" t="n">
         <v>95.10714932937516</v>
       </c>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="7" t="n">
         <v>95.26313018798828</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="8" t="n">
         <v>6523500</v>
       </c>
     </row>
@@ -2561,19 +2564,19 @@
       <c r="A113" s="6" t="n">
         <v>45953</v>
       </c>
-      <c r="B113" s="4" t="n">
+      <c r="B113" s="7" t="n">
         <v>95.06815771520796</v>
       </c>
-      <c r="C113" s="4" t="n">
+      <c r="C113" s="7" t="n">
         <v>95.12665425819164</v>
       </c>
-      <c r="D113" s="4" t="n">
+      <c r="D113" s="7" t="n">
         <v>94.93167817754096</v>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="7" t="n">
         <v>94.95117950439452</v>
       </c>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="8" t="n">
         <v>6138300</v>
       </c>
     </row>
@@ -2581,19 +2584,19 @@
       <c r="A114" s="6" t="n">
         <v>45954</v>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="7" t="n">
         <v>95.06816209555473</v>
       </c>
-      <c r="C114" s="4" t="n">
+      <c r="C114" s="7" t="n">
         <v>95.08766342330682</v>
       </c>
-      <c r="D114" s="4" t="n">
+      <c r="D114" s="7" t="n">
         <v>94.88294410737376</v>
       </c>
-      <c r="E114" s="4" t="n">
+      <c r="E114" s="7" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="8" t="n">
         <v>7555200</v>
       </c>
     </row>
@@ -2601,19 +2604,19 @@
       <c r="A115" s="6" t="n">
         <v>45957</v>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="7" t="n">
         <v>94.89268733367248</v>
       </c>
-      <c r="C115" s="4" t="n">
+      <c r="C115" s="7" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="D115" s="4" t="n">
+      <c r="D115" s="7" t="n">
         <v>94.76595845359311</v>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="7" t="n">
         <v>95.03891754150391</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="8" t="n">
         <v>7272300</v>
       </c>
     </row>
@@ -2621,19 +2624,19 @@
       <c r="A116" s="6" t="n">
         <v>45958</v>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="7" t="n">
         <v>94.98041775782325</v>
       </c>
-      <c r="C116" s="4" t="n">
+      <c r="C116" s="7" t="n">
         <v>95.17538638796626</v>
       </c>
-      <c r="D116" s="4" t="n">
+      <c r="D116" s="7" t="n">
         <v>94.98041775782325</v>
       </c>
-      <c r="E116" s="4" t="n">
+      <c r="E116" s="7" t="n">
         <v>95.12664794921876</v>
       </c>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="8" t="n">
         <v>5539600</v>
       </c>
     </row>
@@ -2641,19 +2644,19 @@
       <c r="A117" s="6" t="n">
         <v>45959</v>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="7" t="n">
         <v>95.07790112383094</v>
       </c>
-      <c r="C117" s="4" t="n">
+      <c r="C117" s="7" t="n">
         <v>95.07790112383094</v>
       </c>
-      <c r="D117" s="4" t="n">
+      <c r="D117" s="7" t="n">
         <v>94.46374325119211</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="7" t="n">
         <v>94.51248168945312</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="8" t="n">
         <v>11223300</v>
       </c>
     </row>
@@ -2661,19 +2664,19 @@
       <c r="A118" s="6" t="n">
         <v>45960</v>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="7" t="n">
         <v>94.23953516407464</v>
       </c>
-      <c r="C118" s="4" t="n">
+      <c r="C118" s="7" t="n">
         <v>94.52224491884976</v>
       </c>
-      <c r="D118" s="4" t="n">
+      <c r="D118" s="7" t="n">
         <v>94.22004127369384</v>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="7" t="n">
         <v>94.37601470947266</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="8" t="n">
         <v>8958800</v>
       </c>
     </row>
@@ -2681,19 +2684,19 @@
       <c r="A119" s="6" t="n">
         <v>45961</v>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B119" s="7" t="n">
         <v>94.43450987259448</v>
       </c>
-      <c r="C119" s="4" t="n">
+      <c r="C119" s="7" t="n">
         <v>94.51249287055298</v>
       </c>
-      <c r="D119" s="4" t="n">
+      <c r="D119" s="7" t="n">
         <v>94.35651943705868</v>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="7" t="n">
         <v>94.41500854492188</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="8" t="n">
         <v>9739900</v>
       </c>
     </row>
@@ -2701,19 +2704,19 @@
       <c r="A120" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="7" t="n">
         <v>94.29178200291418</v>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C120" s="7" t="n">
         <v>94.42869127671588</v>
       </c>
-      <c r="D120" s="4" t="n">
+      <c r="D120" s="7" t="n">
         <v>94.24289009712548</v>
       </c>
-      <c r="E120" s="4" t="n">
+      <c r="E120" s="7" t="n">
         <v>94.37001800537109</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="8" t="n">
         <v>8012500</v>
       </c>
     </row>
@@ -2721,19 +2724,19 @@
       <c r="A121" s="6" t="n">
         <v>45965</v>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="7" t="n">
         <v>94.43846635912506</v>
       </c>
-      <c r="C121" s="4" t="n">
+      <c r="C121" s="7" t="n">
         <v>94.53625762519208</v>
       </c>
-      <c r="D121" s="4" t="n">
+      <c r="D121" s="7" t="n">
         <v>94.41891109030981</v>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="7" t="n">
         <v>94.48736572265624</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="8" t="n">
         <v>6119000</v>
       </c>
     </row>
@@ -2741,19 +2744,19 @@
       <c r="A122" s="6" t="n">
         <v>45966</v>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="7" t="n">
         <v>94.32112145232284</v>
       </c>
-      <c r="C122" s="4" t="n">
+      <c r="C122" s="7" t="n">
         <v>94.34068418401856</v>
       </c>
-      <c r="D122" s="4" t="n">
+      <c r="D122" s="7" t="n">
         <v>94.0081848941556</v>
       </c>
-      <c r="E122" s="4" t="n">
+      <c r="E122" s="7" t="n">
         <v>94.03752899169922</v>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="8" t="n">
         <v>11749200</v>
       </c>
     </row>
@@ -2761,19 +2764,19 @@
       <c r="A123" s="6" t="n">
         <v>45967</v>
       </c>
-      <c r="B123" s="4" t="n">
+      <c r="B123" s="7" t="n">
         <v>94.38957300514608</v>
       </c>
-      <c r="C123" s="4" t="n">
+      <c r="C123" s="7" t="n">
         <v>94.58516301072822</v>
       </c>
-      <c r="D123" s="4" t="n">
+      <c r="D123" s="7" t="n">
         <v>94.37979910061384</v>
       </c>
-      <c r="E123" s="4" t="n">
+      <c r="E123" s="7" t="n">
         <v>94.51670837402344</v>
       </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="8" t="n">
         <v>7665000</v>
       </c>
     </row>
@@ -2781,19 +2784,19 @@
       <c r="A124" s="6" t="n">
         <v>45968</v>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="7" t="n">
         <v>94.42868891372514</v>
       </c>
-      <c r="C124" s="4" t="n">
+      <c r="C124" s="7" t="n">
         <v>94.7220701850991</v>
       </c>
-      <c r="D124" s="4" t="n">
+      <c r="D124" s="7" t="n">
         <v>94.41891500940947</v>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="7" t="n">
         <v>94.55582427978516</v>
       </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="8" t="n">
         <v>11460300</v>
       </c>
     </row>
@@ -2801,19 +2804,19 @@
       <c r="A125" s="6" t="n">
         <v>45971</v>
       </c>
-      <c r="B125" s="4" t="n">
+      <c r="B125" s="7" t="n">
         <v>94.43846941453818</v>
       </c>
-      <c r="C125" s="4" t="n">
+      <c r="C125" s="7" t="n">
         <v>94.51670541432114</v>
       </c>
-      <c r="D125" s="4" t="n">
+      <c r="D125" s="7" t="n">
         <v>94.37979614519874</v>
       </c>
-      <c r="E125" s="4" t="n">
+      <c r="E125" s="7" t="n">
         <v>94.42868804931641</v>
       </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="8" t="n">
         <v>9097300</v>
       </c>
     </row>
@@ -2821,19 +2824,19 @@
       <c r="A126" s="6" t="n">
         <v>45972</v>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="7" t="n">
         <v>94.6731770472381</v>
       </c>
-      <c r="C126" s="4" t="n">
+      <c r="C126" s="7" t="n">
         <v>94.75141305288368</v>
       </c>
-      <c r="D126" s="4" t="n">
+      <c r="D126" s="7" t="n">
         <v>94.59494850258864</v>
       </c>
-      <c r="E126" s="4" t="n">
+      <c r="E126" s="7" t="n">
         <v>94.72207641601562</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="8" t="n">
         <v>4937700</v>
       </c>
     </row>
@@ -2841,19 +2844,19 @@
       <c r="A127" s="6" t="n">
         <v>45973</v>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="7" t="n">
         <v>94.67317591532679</v>
       </c>
-      <c r="C127" s="4" t="n">
+      <c r="C127" s="7" t="n">
         <v>94.81008519307164</v>
       </c>
-      <c r="D127" s="4" t="n">
+      <c r="D127" s="7" t="n">
         <v>94.64383927880949</v>
       </c>
-      <c r="E127" s="4" t="n">
+      <c r="E127" s="7" t="n">
         <v>94.74163055419922</v>
       </c>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="8" t="n">
         <v>7188200</v>
       </c>
     </row>
@@ -2861,19 +2864,19 @@
       <c r="A128" s="6" t="n">
         <v>45974</v>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="7" t="n">
         <v>94.51671095245112</v>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C128" s="7" t="n">
         <v>94.66340159539052</v>
       </c>
-      <c r="D128" s="4" t="n">
+      <c r="D128" s="7" t="n">
         <v>94.46781158447266</v>
       </c>
-      <c r="E128" s="4" t="n">
+      <c r="E128" s="7" t="n">
         <v>94.46781158447266</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="8" t="n">
         <v>46965300</v>
       </c>
     </row>
@@ -2881,19 +2884,19 @@
       <c r="A129" s="6" t="n">
         <v>45975</v>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="7" t="n">
         <v>94.7416387318744</v>
       </c>
-      <c r="C129" s="4" t="n">
+      <c r="C129" s="7" t="n">
         <v>94.79053810428807</v>
       </c>
-      <c r="D129" s="4" t="n">
+      <c r="D129" s="7" t="n">
         <v>94.29179285745616</v>
       </c>
-      <c r="E129" s="4" t="n">
+      <c r="E129" s="7" t="n">
         <v>94.31135559082033</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="F129" s="8" t="n">
         <v>11288500</v>
       </c>
     </row>
@@ -2901,19 +2904,19 @@
       <c r="A130" s="6" t="n">
         <v>45978</v>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="7" t="n">
         <v>94.4091334296328</v>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C130" s="7" t="n">
         <v>94.4873694299542</v>
       </c>
-      <c r="D130" s="4" t="n">
+      <c r="D130" s="7" t="n">
         <v>94.360234064183</v>
       </c>
-      <c r="E130" s="4" t="n">
+      <c r="E130" s="7" t="n">
         <v>94.41891479492188</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="8" t="n">
         <v>6648500</v>
       </c>
     </row>
@@ -2921,19 +2924,19 @@
       <c r="A131" s="6" t="n">
         <v>45979</v>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="7" t="n">
         <v>94.7025216008121</v>
       </c>
-      <c r="C131" s="4" t="n">
+      <c r="C131" s="7" t="n">
         <v>94.79053897977028</v>
       </c>
-      <c r="D131" s="4" t="n">
+      <c r="D131" s="7" t="n">
         <v>94.4384843859311</v>
       </c>
-      <c r="E131" s="4" t="n">
+      <c r="E131" s="7" t="n">
         <v>94.5753936767578</v>
       </c>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="8" t="n">
         <v>8769000</v>
       </c>
     </row>
@@ -2941,19 +2944,19 @@
       <c r="A132" s="6" t="n">
         <v>45980</v>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="7" t="n">
         <v>94.67318104289504</v>
       </c>
-      <c r="C132" s="4" t="n">
+      <c r="C132" s="7" t="n">
         <v>94.72208041373636</v>
       </c>
-      <c r="D132" s="4" t="n">
+      <c r="D132" s="7" t="n">
         <v>94.46781711515514</v>
       </c>
-      <c r="E132" s="4" t="n">
+      <c r="E132" s="7" t="n">
         <v>94.50693511962891</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="8" t="n">
         <v>13075900</v>
       </c>
     </row>
@@ -2961,19 +2964,19 @@
       <c r="A133" s="6" t="n">
         <v>45981</v>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="7" t="n">
         <v>94.60471430687321</v>
       </c>
-      <c r="C133" s="4" t="n">
+      <c r="C133" s="7" t="n">
         <v>94.81007820836116</v>
       </c>
-      <c r="D133" s="4" t="n">
+      <c r="D133" s="7" t="n">
         <v>94.56559630739994</v>
       </c>
-      <c r="E133" s="4" t="n">
+      <c r="E133" s="7" t="n">
         <v>94.73184967041016</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="8" t="n">
         <v>9076400</v>
       </c>
     </row>
@@ -2981,19 +2984,19 @@
       <c r="A134" s="6" t="n">
         <v>45982</v>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="7" t="n">
         <v>95.04479217529295</v>
       </c>
-      <c r="C134" s="4" t="n">
+      <c r="C134" s="7" t="n">
         <v>95.08391017722336</v>
       </c>
-      <c r="D134" s="4" t="n">
+      <c r="D134" s="7" t="n">
         <v>94.8589835313726</v>
       </c>
-      <c r="E134" s="4" t="n">
+      <c r="E134" s="7" t="n">
         <v>95.04479217529295</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="8" t="n">
         <v>12551100</v>
       </c>
     </row>
@@ -3001,19 +3004,19 @@
       <c r="A135" s="6" t="n">
         <v>45985</v>
       </c>
-      <c r="B135" s="4" t="n">
+      <c r="B135" s="7" t="n">
         <v>95.14258300811166</v>
       </c>
-      <c r="C135" s="4" t="n">
+      <c r="C135" s="7" t="n">
         <v>95.21103764592318</v>
       </c>
-      <c r="D135" s="4" t="n">
+      <c r="D135" s="7" t="n">
         <v>95.03501036855128</v>
       </c>
-      <c r="E135" s="4" t="n">
+      <c r="E135" s="7" t="n">
         <v>95.19147491455078</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="8" t="n">
         <v>6903900</v>
       </c>
     </row>
@@ -3021,19 +3024,19 @@
       <c r="A136" s="6" t="n">
         <v>45986</v>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="7" t="n">
         <v>95.28927567886736</v>
       </c>
-      <c r="C136" s="4" t="n">
+      <c r="C136" s="7" t="n">
         <v>95.54353150415614</v>
       </c>
-      <c r="D136" s="4" t="n">
+      <c r="D136" s="7" t="n">
         <v>95.27949431297284</v>
       </c>
-      <c r="E136" s="4" t="n">
+      <c r="E136" s="7" t="n">
         <v>95.43595886230467</v>
       </c>
-      <c r="F136" s="4" t="n">
+      <c r="F136" s="8" t="n">
         <v>9193400</v>
       </c>
     </row>
@@ -3041,19 +3044,19 @@
       <c r="A137" s="6" t="n">
         <v>45987</v>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="7" t="n">
         <v>95.32839711051984</v>
       </c>
-      <c r="C137" s="4" t="n">
+      <c r="C137" s="7" t="n">
         <v>95.51419830322266</v>
       </c>
-      <c r="D137" s="4" t="n">
+      <c r="D137" s="7" t="n">
         <v>95.18170646080978</v>
       </c>
-      <c r="E137" s="4" t="n">
+      <c r="E137" s="7" t="n">
         <v>95.51419830322266</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="8" t="n">
         <v>7747100</v>
       </c>
     </row>
@@ -3061,19 +3064,19 @@
       <c r="A138" s="6" t="n">
         <v>45989</v>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="7" t="n">
         <v>95.475074075923</v>
       </c>
-      <c r="C138" s="4" t="n">
+      <c r="C138" s="7" t="n">
         <v>95.49463680714058</v>
       </c>
-      <c r="D138" s="4" t="n">
+      <c r="D138" s="7" t="n">
         <v>95.24037352828309</v>
       </c>
-      <c r="E138" s="4" t="n">
+      <c r="E138" s="7" t="n">
         <v>95.3479461669922</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="8" t="n">
         <v>7798000</v>
       </c>
     </row>
@@ -3081,19 +3084,19 @@
       <c r="A139" s="6" t="n">
         <v>45992</v>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="7" t="n">
         <v>94.91442069171418</v>
       </c>
-      <c r="C139" s="4" t="n">
+      <c r="C139" s="7" t="n">
         <v>94.98307813424096</v>
       </c>
-      <c r="D139" s="4" t="n">
+      <c r="D139" s="7" t="n">
         <v>94.82615004407975</v>
       </c>
-      <c r="E139" s="4" t="n">
+      <c r="E139" s="7" t="n">
         <v>94.83596038818359</v>
       </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="8" t="n">
         <v>9898100</v>
       </c>
     </row>
@@ -3101,19 +3104,19 @@
       <c r="A140" s="6" t="n">
         <v>45993</v>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="7" t="n">
         <v>94.8065372283578</v>
       </c>
-      <c r="C140" s="4" t="n">
+      <c r="C140" s="7" t="n">
         <v>94.96346531916352</v>
       </c>
-      <c r="D140" s="4" t="n">
+      <c r="D140" s="7" t="n">
         <v>94.74768264659312</v>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E140" s="7" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="8" t="n">
         <v>7317200</v>
       </c>
     </row>
@@ -3121,19 +3124,19 @@
       <c r="A141" s="6" t="n">
         <v>45994</v>
       </c>
-      <c r="B141" s="4" t="n">
+      <c r="B141" s="7" t="n">
         <v>95.07135418127504</v>
       </c>
-      <c r="C141" s="4" t="n">
+      <c r="C141" s="7" t="n">
         <v>95.16943517086364</v>
       </c>
-      <c r="D141" s="4" t="n">
+      <c r="D141" s="7" t="n">
         <v>94.95365250390886</v>
       </c>
-      <c r="E141" s="4" t="n">
+      <c r="E141" s="7" t="n">
         <v>95.11058807373048</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="8" t="n">
         <v>6855100</v>
       </c>
     </row>
@@ -3141,19 +3144,19 @@
       <c r="A142" s="6" t="n">
         <v>45995</v>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="7" t="n">
         <v>94.96346281132551</v>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C142" s="7" t="n">
         <v>94.97327315521056</v>
       </c>
-      <c r="D142" s="4" t="n">
+      <c r="D142" s="7" t="n">
         <v>94.76730083222368</v>
       </c>
-      <c r="E142" s="4" t="n">
+      <c r="E142" s="7" t="n">
         <v>94.81633758544922</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="8" t="n">
         <v>8928900</v>
       </c>
     </row>
@@ -3161,19 +3164,19 @@
       <c r="A143" s="6" t="n">
         <v>45996</v>
       </c>
-      <c r="B143" s="4" t="n">
+      <c r="B143" s="7" t="n">
         <v>94.83596089549469</v>
       </c>
-      <c r="C143" s="4" t="n">
+      <c r="C143" s="7" t="n">
         <v>94.84576375655097</v>
       </c>
-      <c r="D143" s="4" t="n">
+      <c r="D143" s="7" t="n">
         <v>94.57113398497476</v>
       </c>
-      <c r="E143" s="4" t="n">
+      <c r="E143" s="7" t="n">
         <v>94.62017822265624</v>
       </c>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="8" t="n">
         <v>9118700</v>
       </c>
     </row>
@@ -3181,19 +3184,19 @@
       <c r="A144" s="6" t="n">
         <v>45999</v>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="7" t="n">
         <v>94.56132596246688</v>
       </c>
-      <c r="C144" s="4" t="n">
+      <c r="C144" s="7" t="n">
         <v>94.57112882298806</v>
       </c>
-      <c r="D144" s="4" t="n">
+      <c r="D144" s="7" t="n">
         <v>94.24745483139752</v>
       </c>
-      <c r="E144" s="4" t="n">
+      <c r="E144" s="7" t="n">
         <v>94.42400360107422</v>
       </c>
-      <c r="F144" s="4" t="n">
+      <c r="F144" s="8" t="n">
         <v>14728300</v>
       </c>
     </row>
@@ -3201,19 +3204,19 @@
       <c r="A145" s="6" t="n">
         <v>46000</v>
       </c>
-      <c r="B145" s="4" t="n">
+      <c r="B145" s="7" t="n">
         <v>94.56132700100272</v>
       </c>
-      <c r="C145" s="4" t="n">
+      <c r="C145" s="7" t="n">
         <v>94.56132700100272</v>
       </c>
-      <c r="D145" s="4" t="n">
+      <c r="D145" s="7" t="n">
         <v>94.26707655394335</v>
       </c>
-      <c r="E145" s="4" t="n">
+      <c r="E145" s="7" t="n">
         <v>94.28668975830078</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="8" t="n">
         <v>8509200</v>
       </c>
     </row>
@@ -3221,19 +3224,19 @@
       <c r="A146" s="6" t="n">
         <v>46001</v>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="7" t="n">
         <v>94.24745696135868</v>
       </c>
-      <c r="C146" s="4" t="n">
+      <c r="C146" s="7" t="n">
         <v>94.62017519637702</v>
       </c>
-      <c r="D146" s="4" t="n">
+      <c r="D146" s="7" t="n">
         <v>94.23765410061596</v>
       </c>
-      <c r="E146" s="4" t="n">
+      <c r="E146" s="7" t="n">
         <v>94.59075164794922</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="8" t="n">
         <v>13356900</v>
       </c>
     </row>
@@ -3241,19 +3244,19 @@
       <c r="A147" s="6" t="n">
         <v>46002</v>
       </c>
-      <c r="B147" s="4" t="n">
+      <c r="B147" s="7" t="n">
         <v>94.8261484318744</v>
       </c>
-      <c r="C147" s="4" t="n">
+      <c r="C147" s="7" t="n">
         <v>94.87519266845968</v>
       </c>
-      <c r="D147" s="4" t="n">
+      <c r="D147" s="7" t="n">
         <v>94.57113187121064</v>
       </c>
-      <c r="E147" s="4" t="n">
+      <c r="E147" s="7" t="n">
         <v>94.60055541992188</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="8" t="n">
         <v>8672800</v>
       </c>
     </row>
@@ -3261,19 +3264,19 @@
       <c r="A148" s="6" t="n">
         <v>46003</v>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="7" t="n">
         <v>94.34555053710938</v>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C148" s="7" t="n">
         <v>94.42401084279447</v>
       </c>
-      <c r="D148" s="4" t="n">
+      <c r="D148" s="7" t="n">
         <v>94.32592984836296</v>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="7" t="n">
         <v>94.34555053710938</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="8" t="n">
         <v>8348700</v>
       </c>
     </row>
@@ -3281,19 +3284,19 @@
       <c r="A149" s="6" t="n">
         <v>46006</v>
       </c>
-      <c r="B149" s="4" t="n">
+      <c r="B149" s="7" t="n">
         <v>94.56132596246688</v>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C149" s="7" t="n">
         <v>94.65940694937622</v>
       </c>
-      <c r="D149" s="4" t="n">
+      <c r="D149" s="7" t="n">
         <v>94.4043903969322</v>
       </c>
-      <c r="E149" s="4" t="n">
+      <c r="E149" s="7" t="n">
         <v>94.42400360107422</v>
       </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="8" t="n">
         <v>6117000</v>
       </c>
     </row>
@@ -3301,19 +3304,19 @@
       <c r="A150" s="6" t="n">
         <v>46007</v>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="7" t="n">
         <v>94.39458468577476</v>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C150" s="7" t="n">
         <v>94.7084483491475</v>
       </c>
-      <c r="D150" s="4" t="n">
+      <c r="D150" s="7" t="n">
         <v>94.3847818247725</v>
       </c>
-      <c r="E150" s="4" t="n">
+      <c r="E150" s="7" t="n">
         <v>94.68883514404295</v>
       </c>
-      <c r="F150" s="4" t="n">
+      <c r="F150" s="8" t="n">
         <v>7456400</v>
       </c>
     </row>
@@ -3321,19 +3324,19 @@
       <c r="A151" s="6" t="n">
         <v>46008</v>
       </c>
-      <c r="B151" s="4" t="n">
+      <c r="B151" s="7" t="n">
         <v>94.5711313517766</v>
       </c>
-      <c r="C151" s="4" t="n">
+      <c r="C151" s="7" t="n">
         <v>94.71825657762452</v>
       </c>
-      <c r="D151" s="4" t="n">
+      <c r="D151" s="7" t="n">
         <v>94.55151814711012</v>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="7" t="n">
         <v>94.66921234130859</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="8" t="n">
         <v>5673200</v>
       </c>
     </row>
@@ -3341,19 +3344,19 @@
       <c r="A152" s="6" t="n">
         <v>46009</v>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="7" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="C152" s="4" t="n">
+      <c r="C152" s="7" t="n">
         <v>94.97327566330765</v>
       </c>
-      <c r="D152" s="4" t="n">
+      <c r="D152" s="7" t="n">
         <v>94.78691654006956</v>
       </c>
-      <c r="E152" s="4" t="n">
+      <c r="E152" s="7" t="n">
         <v>94.91442108154295</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="8" t="n">
         <v>7357600</v>
       </c>
     </row>
@@ -3361,19 +3364,19 @@
       <c r="A153" s="6" t="n">
         <v>46010</v>
       </c>
-      <c r="B153" s="4" t="n">
+      <c r="B153" s="7" t="n">
         <v>94.75992751443634</v>
       </c>
-      <c r="C153" s="4" t="n">
+      <c r="C153" s="7" t="n">
         <v>94.8484845880067</v>
       </c>
-      <c r="D153" s="4" t="n">
+      <c r="D153" s="7" t="n">
         <v>94.66152075618268</v>
       </c>
-      <c r="E153" s="4" t="n">
+      <c r="E153" s="7" t="n">
         <v>94.7008819580078</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="8" t="n">
         <v>5806600</v>
       </c>
     </row>
@@ -3381,19 +3384,19 @@
       <c r="A154" s="6" t="n">
         <v>46013</v>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="7" t="n">
         <v>94.6221700119554</v>
       </c>
-      <c r="C154" s="4" t="n">
+      <c r="C154" s="7" t="n">
         <v>94.65168903739922</v>
       </c>
-      <c r="D154" s="4" t="n">
+      <c r="D154" s="7" t="n">
         <v>94.54344760585064</v>
       </c>
-      <c r="E154" s="4" t="n">
+      <c r="E154" s="7" t="n">
         <v>94.60248565673828</v>
       </c>
-      <c r="F154" s="4" t="n">
+      <c r="F154" s="8" t="n">
         <v>4672800</v>
       </c>
     </row>
@@ -3401,19 +3404,19 @@
       <c r="A155" s="6" t="n">
         <v>46014</v>
       </c>
-      <c r="B155" s="4" t="n">
+      <c r="B155" s="7" t="n">
         <v>94.3958461258692</v>
       </c>
-      <c r="C155" s="4" t="n">
+      <c r="C155" s="7" t="n">
         <v>94.59264463615646</v>
       </c>
-      <c r="D155" s="4" t="n">
+      <c r="D155" s="7" t="n">
         <v>94.34664274460644</v>
       </c>
-      <c r="E155" s="4" t="n">
+      <c r="E155" s="7" t="n">
         <v>94.56312561035156</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="8" t="n">
         <v>5093900</v>
       </c>
     </row>
@@ -3421,19 +3424,19 @@
       <c r="A156" s="6" t="n">
         <v>46015</v>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="7" t="n">
         <v>94.6812095262562</v>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C156" s="7" t="n">
         <v>94.82881216313856</v>
       </c>
-      <c r="D156" s="4" t="n">
+      <c r="D156" s="7" t="n">
         <v>94.63200614483476</v>
       </c>
-      <c r="E156" s="4" t="n">
+      <c r="E156" s="7" t="n">
         <v>94.8091278076172</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="8" t="n">
         <v>3967700</v>
       </c>
     </row>
@@ -3441,19 +3444,19 @@
       <c r="A157" s="6" t="n">
         <v>46017</v>
       </c>
-      <c r="B157" s="4" t="n">
+      <c r="B157" s="7" t="n">
         <v>94.94688569204136</v>
       </c>
-      <c r="C157" s="4" t="n">
+      <c r="C157" s="7" t="n">
         <v>94.96657004702892</v>
       </c>
-      <c r="D157" s="4" t="n">
+      <c r="D157" s="7" t="n">
         <v>94.78944838904955</v>
       </c>
-      <c r="E157" s="4" t="n">
+      <c r="E157" s="7" t="n">
         <v>94.89768981933594</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="8" t="n">
         <v>3491500</v>
       </c>
     </row>
@@ -3461,19 +3464,19 @@
       <c r="A158" s="6" t="n">
         <v>46020</v>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="7" t="n">
         <v>95.00594239721801</v>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C158" s="7" t="n">
         <v>95.05513827569588</v>
       </c>
-      <c r="D158" s="4" t="n">
+      <c r="D158" s="7" t="n">
         <v>94.90753562549702</v>
       </c>
-      <c r="E158" s="4" t="n">
+      <c r="E158" s="7" t="n">
         <v>95.03546142578124</v>
       </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="8" t="n">
         <v>5034600</v>
       </c>
     </row>
@@ -3481,19 +3484,19 @@
       <c r="A159" s="6" t="n">
         <v>46021</v>
       </c>
-      <c r="B159" s="4" t="n">
+      <c r="B159" s="7" t="n">
         <v>94.89768866360863</v>
       </c>
-      <c r="C159" s="4" t="n">
+      <c r="C159" s="7" t="n">
         <v>95.01576476256903</v>
       </c>
-      <c r="D159" s="4" t="n">
+      <c r="D159" s="7" t="n">
         <v>94.8583274614946</v>
       </c>
-      <c r="E159" s="4" t="n">
+      <c r="E159" s="7" t="n">
         <v>94.93704986572266</v>
       </c>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="8" t="n">
         <v>4108600</v>
       </c>
     </row>
@@ -3501,19 +3504,19 @@
       <c r="A160" s="6" t="n">
         <v>46022</v>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="7" t="n">
         <v>94.79929128999878</v>
       </c>
-      <c r="C160" s="4" t="n">
+      <c r="C160" s="7" t="n">
         <v>94.92721708637974</v>
       </c>
-      <c r="D160" s="4" t="n">
+      <c r="D160" s="7" t="n">
         <v>94.61233494567512</v>
       </c>
-      <c r="E160" s="4" t="n">
+      <c r="E160" s="7" t="n">
         <v>94.62217712402344</v>
       </c>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="8" t="n">
         <v>6802100</v>
       </c>
     </row>
@@ -3521,19 +3524,19 @@
       <c r="A161" s="6" t="n">
         <v>46024</v>
       </c>
-      <c r="B161" s="4" t="n">
+      <c r="B161" s="7" t="n">
         <v>94.75009009126956</v>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C161" s="7" t="n">
         <v>94.75009009126956</v>
       </c>
-      <c r="D161" s="4" t="n">
+      <c r="D161" s="7" t="n">
         <v>94.53360722405996</v>
       </c>
-      <c r="E161" s="4" t="n">
+      <c r="E161" s="7" t="n">
         <v>94.54344940185548</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="8" t="n">
         <v>6611800</v>
       </c>
     </row>
@@ -3541,19 +3544,19 @@
       <c r="A162" s="6" t="n">
         <v>46027</v>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="7" t="n">
         <v>94.69105880544922</v>
       </c>
-      <c r="C162" s="4" t="n">
+      <c r="C162" s="7" t="n">
         <v>94.83865394601862</v>
       </c>
-      <c r="D162" s="4" t="n">
+      <c r="D162" s="7" t="n">
         <v>94.63201324183892</v>
       </c>
-      <c r="E162" s="4" t="n">
+      <c r="E162" s="7" t="n">
         <v>94.82881927490234</v>
       </c>
-      <c r="F162" s="4" t="n">
+      <c r="F162" s="8" t="n">
         <v>8693200</v>
       </c>
     </row>
@@ -3561,19 +3564,19 @@
       <c r="A163" s="6" t="n">
         <v>46028</v>
       </c>
-      <c r="B163" s="4" t="n">
+      <c r="B163" s="7" t="n">
         <v>94.7107300894596</v>
       </c>
-      <c r="C163" s="4" t="n">
+      <c r="C163" s="7" t="n">
         <v>94.77961032013847</v>
       </c>
-      <c r="D163" s="4" t="n">
+      <c r="D163" s="7" t="n">
         <v>94.56312745018144</v>
       </c>
-      <c r="E163" s="4" t="n">
+      <c r="E163" s="7" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="8" t="n">
         <v>12834100</v>
       </c>
     </row>
@@ -3581,19 +3584,19 @@
       <c r="A164" s="6" t="n">
         <v>46029</v>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="7" t="n">
         <v>94.976403560455</v>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C164" s="7" t="n">
         <v>95.0059300925768</v>
       </c>
-      <c r="D164" s="4" t="n">
+      <c r="D164" s="7" t="n">
         <v>94.79928190463274</v>
       </c>
-      <c r="E164" s="4" t="n">
+      <c r="E164" s="7" t="n">
         <v>94.93704986572266</v>
       </c>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="8" t="n">
         <v>7990900</v>
       </c>
     </row>
@@ -3601,19 +3604,19 @@
       <c r="A165" s="6" t="n">
         <v>46030</v>
       </c>
-      <c r="B165" s="4" t="n">
+      <c r="B165" s="7" t="n">
         <v>94.69105645710135</v>
       </c>
-      <c r="C165" s="4" t="n">
+      <c r="C165" s="7" t="n">
         <v>94.76977136099208</v>
       </c>
-      <c r="D165" s="4" t="n">
+      <c r="D165" s="7" t="n">
         <v>94.64185307321011</v>
       </c>
-      <c r="E165" s="4" t="n">
+      <c r="E165" s="7" t="n">
         <v>94.65169525146484</v>
       </c>
-      <c r="F165" s="4" t="n">
+      <c r="F165" s="8" t="n">
         <v>6931700</v>
       </c>
     </row>
@@ -3621,19 +3624,19 @@
       <c r="A166" s="6" t="n">
         <v>46031</v>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="7" t="n">
         <v>94.62217301032196</v>
       </c>
-      <c r="C166" s="4" t="n">
+      <c r="C166" s="7" t="n">
         <v>94.83864837289693</v>
       </c>
-      <c r="D166" s="4" t="n">
+      <c r="D166" s="7" t="n">
         <v>94.53360842380222</v>
       </c>
-      <c r="E166" s="4" t="n">
+      <c r="E166" s="7" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F166" s="4" t="n">
+      <c r="F166" s="8" t="n">
         <v>10277300</v>
       </c>
     </row>
@@ -3641,19 +3644,19 @@
       <c r="A167" s="6" t="n">
         <v>46034</v>
       </c>
-      <c r="B167" s="4" t="n">
+      <c r="B167" s="7" t="n">
         <v>94.61233430505683</v>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C167" s="7" t="n">
         <v>94.75993694975264</v>
       </c>
-      <c r="D167" s="4" t="n">
+      <c r="D167" s="7" t="n">
         <v>94.58281527759416</v>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E167" s="7" t="n">
         <v>94.64185333251952</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="8" t="n">
         <v>6360600</v>
       </c>
     </row>
@@ -3661,19 +3664,19 @@
       <c r="A168" s="6" t="n">
         <v>46035</v>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="7" t="n">
         <v>94.79928716859726</v>
       </c>
-      <c r="C168" s="4" t="n">
+      <c r="C168" s="7" t="n">
         <v>94.82881370235856</v>
       </c>
-      <c r="D168" s="4" t="n">
+      <c r="D168" s="7" t="n">
         <v>94.66152670723952</v>
       </c>
-      <c r="E168" s="4" t="n">
+      <c r="E168" s="7" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="8" t="n">
         <v>7622500</v>
       </c>
     </row>
@@ -3681,19 +3684,19 @@
       <c r="A169" s="6" t="n">
         <v>46036</v>
       </c>
-      <c r="B169" s="4" t="n">
+      <c r="B169" s="7" t="n">
         <v>94.83865770848512</v>
       </c>
-      <c r="C169" s="4" t="n">
+      <c r="C169" s="7" t="n">
         <v>95.05514059975198</v>
       </c>
-      <c r="D169" s="4" t="n">
+      <c r="D169" s="7" t="n">
         <v>94.82882303697868</v>
       </c>
-      <c r="E169" s="4" t="n">
+      <c r="E169" s="7" t="n">
         <v>94.9567413330078</v>
       </c>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="8" t="n">
         <v>7331200</v>
       </c>
     </row>
@@ -3701,19 +3704,19 @@
       <c r="A170" s="6" t="n">
         <v>46037</v>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="7" t="n">
         <v>94.9665741637163</v>
       </c>
-      <c r="C170" s="4" t="n">
+      <c r="C170" s="7" t="n">
         <v>94.97640883425464</v>
       </c>
-      <c r="D170" s="4" t="n">
+      <c r="D170" s="7" t="n">
         <v>94.74024911583882</v>
       </c>
-      <c r="E170" s="4" t="n">
+      <c r="E170" s="7" t="n">
         <v>94.75993347167967</v>
       </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="8" t="n">
         <v>6172500</v>
       </c>
     </row>
@@ -3721,19 +3724,19 @@
       <c r="A171" s="6" t="n">
         <v>46038</v>
       </c>
-      <c r="B171" s="4" t="n">
+      <c r="B171" s="7" t="n">
         <v>94.69105642373262</v>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C171" s="7" t="n">
         <v>94.720575451104</v>
       </c>
-      <c r="D171" s="4" t="n">
+      <c r="D171" s="7" t="n">
         <v>94.37617428613376</v>
       </c>
-      <c r="E171" s="4" t="n">
+      <c r="E171" s="7" t="n">
         <v>94.39585113525391</v>
       </c>
-      <c r="F171" s="4" t="n">
+      <c r="F171" s="8" t="n">
         <v>11979300</v>
       </c>
     </row>
@@ -3741,19 +3744,19 @@
       <c r="A172" s="6" t="n">
         <v>46042</v>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="7" t="n">
         <v>94.07112275424844</v>
       </c>
-      <c r="C172" s="4" t="n">
+      <c r="C172" s="7" t="n">
         <v>94.18920636601358</v>
       </c>
-      <c r="D172" s="4" t="n">
+      <c r="D172" s="7" t="n">
         <v>94.00224252423097</v>
       </c>
-      <c r="E172" s="4" t="n">
+      <c r="E172" s="7" t="n">
         <v>94.0219268798828</v>
       </c>
-      <c r="F172" s="4" t="n">
+      <c r="F172" s="8" t="n">
         <v>13607700</v>
       </c>
     </row>
@@ -3761,19 +3764,19 @@
       <c r="A173" s="6" t="n">
         <v>46043</v>
       </c>
-      <c r="B173" s="4" t="n">
+      <c r="B173" s="7" t="n">
         <v>94.13016861667025</v>
       </c>
-      <c r="C173" s="4" t="n">
+      <c r="C173" s="7" t="n">
         <v>94.30728277381472</v>
       </c>
-      <c r="D173" s="4" t="n">
+      <c r="D173" s="7" t="n">
         <v>94.03176185285834</v>
       </c>
-      <c r="E173" s="4" t="n">
+      <c r="E173" s="7" t="n">
         <v>94.26792907714844</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="8" t="n">
         <v>11969000</v>
       </c>
     </row>
@@ -3781,19 +3784,19 @@
       <c r="A174" s="6" t="n">
         <v>46044</v>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="7" t="n">
         <v>94.16951494977958</v>
       </c>
-      <c r="C174" s="4" t="n">
+      <c r="C174" s="7" t="n">
         <v>94.32695975366164</v>
       </c>
-      <c r="D174" s="4" t="n">
+      <c r="D174" s="7" t="n">
         <v>94.12031907910252</v>
       </c>
-      <c r="E174" s="4" t="n">
+      <c r="E174" s="7" t="n">
         <v>94.25807952880859</v>
       </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="8" t="n">
         <v>10209500</v>
       </c>
     </row>
@@ -3801,19 +3804,19 @@
       <c r="A175" s="6" t="n">
         <v>46045</v>
       </c>
-      <c r="B175" s="4" t="n">
+      <c r="B175" s="7" t="n">
         <v>94.29745123506557</v>
       </c>
-      <c r="C175" s="4" t="n">
+      <c r="C175" s="7" t="n">
         <v>94.43521170011894</v>
       </c>
-      <c r="D175" s="4" t="n">
+      <c r="D175" s="7" t="n">
         <v>94.2187288243544</v>
       </c>
-      <c r="E175" s="4" t="n">
+      <c r="E175" s="7" t="n">
         <v>94.41552734375</v>
       </c>
-      <c r="F175" s="4" t="n">
+      <c r="F175" s="8" t="n">
         <v>8147500</v>
       </c>
     </row>
@@ -3821,19 +3824,19 @@
       <c r="A176" s="6" t="n">
         <v>46048</v>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="7" t="n">
         <v>94.56311823897344</v>
       </c>
-      <c r="C176" s="4" t="n">
+      <c r="C176" s="7" t="n">
         <v>94.62216379336246</v>
       </c>
-      <c r="D176" s="4" t="n">
+      <c r="D176" s="7" t="n">
         <v>94.50408019196578</v>
       </c>
-      <c r="E176" s="4" t="n">
+      <c r="E176" s="7" t="n">
         <v>94.55327606201172</v>
       </c>
-      <c r="F176" s="4" t="n">
+      <c r="F176" s="8" t="n">
         <v>6803800</v>
       </c>
     </row>
@@ -3841,19 +3844,19 @@
       <c r="A177" s="6" t="n">
         <v>46049</v>
       </c>
-      <c r="B177" s="4" t="n">
+      <c r="B177" s="7" t="n">
         <v>94.49424134296994</v>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C177" s="7" t="n">
         <v>94.61232494852536</v>
       </c>
-      <c r="D177" s="4" t="n">
+      <c r="D177" s="7" t="n">
         <v>94.41551893926632</v>
       </c>
-      <c r="E177" s="4" t="n">
+      <c r="E177" s="7" t="n">
         <v>94.44504547119141</v>
       </c>
-      <c r="F177" s="4" t="n">
+      <c r="F177" s="8" t="n">
         <v>9857200</v>
       </c>
     </row>
@@ -3861,19 +3864,19 @@
       <c r="A178" s="6" t="n">
         <v>46050</v>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="7" t="n">
         <v>94.38600222613492</v>
       </c>
-      <c r="C178" s="4" t="n">
+      <c r="C178" s="7" t="n">
         <v>94.41552125140126</v>
       </c>
-      <c r="D178" s="4" t="n">
+      <c r="D178" s="7" t="n">
         <v>94.19904589698751</v>
       </c>
-      <c r="E178" s="4" t="n">
+      <c r="E178" s="7" t="n">
         <v>94.36632537841795</v>
       </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="8" t="n">
         <v>17032400</v>
       </c>
     </row>
@@ -3881,19 +3884,19 @@
       <c r="A179" s="6" t="n">
         <v>46051</v>
       </c>
-      <c r="B179" s="4" t="n">
+      <c r="B179" s="7" t="n">
         <v>94.26793079264098</v>
       </c>
-      <c r="C179" s="4" t="n">
+      <c r="C179" s="7" t="n">
         <v>94.55328638926584</v>
       </c>
-      <c r="D179" s="4" t="n">
+      <c r="D179" s="7" t="n">
         <v>94.24824643656756</v>
       </c>
-      <c r="E179" s="4" t="n">
+      <c r="E179" s="7" t="n">
         <v>94.46472930908205</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="F179" s="8" t="n">
         <v>11049100</v>
       </c>
     </row>
@@ -3901,19 +3904,19 @@
       <c r="A180" s="6" t="n">
         <v>46052</v>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="7" t="n">
         <v>94.45488129718537</v>
       </c>
-      <c r="C180" s="4" t="n">
+      <c r="C180" s="7" t="n">
         <v>94.52376152442363</v>
       </c>
-      <c r="D180" s="4" t="n">
+      <c r="D180" s="7" t="n">
         <v>94.37616639989994</v>
       </c>
-      <c r="E180" s="4" t="n">
+      <c r="E180" s="7" t="n">
         <v>94.40568542480467</v>
       </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" s="8" t="n">
         <v>8238500</v>
       </c>
     </row>
@@ -3921,19 +3924,19 @@
       <c r="A181" s="6" t="n">
         <v>46055</v>
       </c>
-      <c r="B181" s="4" t="n">
+      <c r="B181" s="7" t="n">
         <v>94.44714870629468</v>
       </c>
-      <c r="C181" s="4" t="n">
+      <c r="C181" s="7" t="n">
         <v>94.47676404259118</v>
       </c>
-      <c r="D181" s="4" t="n">
+      <c r="D181" s="7" t="n">
         <v>94.2200927734375</v>
       </c>
-      <c r="E181" s="4" t="n">
+      <c r="E181" s="7" t="n">
         <v>94.2200927734375</v>
       </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="8" t="n">
         <v>8987100</v>
       </c>
     </row>
@@ -3941,19 +3944,19 @@
       <c r="A182" s="6" t="n">
         <v>46056</v>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="7" t="n">
         <v>94.17072715129162</v>
       </c>
-      <c r="C182" s="4" t="n">
+      <c r="C182" s="7" t="n">
         <v>94.3484266977254</v>
       </c>
-      <c r="D182" s="4" t="n">
+      <c r="D182" s="7" t="n">
         <v>94.15098610474379</v>
       </c>
-      <c r="E182" s="4" t="n">
+      <c r="E182" s="7" t="n">
         <v>94.30893707275391</v>
       </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="8" t="n">
         <v>7313800</v>
       </c>
     </row>
@@ -3961,19 +3964,19 @@
       <c r="A183" s="6" t="n">
         <v>46057</v>
       </c>
-      <c r="B183" s="4" t="n">
+      <c r="B183" s="7" t="n">
         <v>94.22996162331719</v>
       </c>
-      <c r="C183" s="4" t="n">
+      <c r="C183" s="7" t="n">
         <v>94.38792012957396</v>
       </c>
-      <c r="D183" s="4" t="n">
+      <c r="D183" s="7" t="n">
         <v>94.19047952862915</v>
       </c>
-      <c r="E183" s="4" t="n">
+      <c r="E183" s="7" t="n">
         <v>94.28919982910156</v>
       </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="8" t="n">
         <v>7268600</v>
       </c>
     </row>
@@ -3981,19 +3984,19 @@
       <c r="A184" s="6" t="n">
         <v>46058</v>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="7" t="n">
         <v>94.57549544700704</v>
       </c>
-      <c r="C184" s="4" t="n">
+      <c r="C184" s="7" t="n">
         <v>94.87165635304076</v>
       </c>
-      <c r="D184" s="4" t="n">
+      <c r="D184" s="7" t="n">
         <v>94.48664190288356</v>
       </c>
-      <c r="E184" s="4" t="n">
+      <c r="E184" s="7" t="n">
         <v>94.842041015625</v>
       </c>
-      <c r="F184" s="4" t="n">
+      <c r="F184" s="8" t="n">
         <v>12086800</v>
       </c>
     </row>
@@ -4001,19 +4004,19 @@
       <c r="A185" s="6" t="n">
         <v>46059</v>
       </c>
-      <c r="B185" s="4" t="n">
+      <c r="B185" s="7" t="n">
         <v>94.89140493256876</v>
       </c>
-      <c r="C185" s="4" t="n">
+      <c r="C185" s="7" t="n">
         <v>94.9012716904565</v>
       </c>
-      <c r="D185" s="4" t="n">
+      <c r="D185" s="7" t="n">
         <v>94.69395679667002</v>
       </c>
-      <c r="E185" s="4" t="n">
+      <c r="E185" s="7" t="n">
         <v>94.842041015625</v>
       </c>
-      <c r="F185" s="4" t="n">
+      <c r="F185" s="8" t="n">
         <v>7759900</v>
       </c>
     </row>
@@ -4021,19 +4024,19 @@
       <c r="A186" s="6" t="n">
         <v>46062</v>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="7" t="n">
         <v>94.7828065399609</v>
       </c>
-      <c r="C186" s="4" t="n">
+      <c r="C186" s="7" t="n">
         <v>94.90126788487352</v>
       </c>
-      <c r="D186" s="4" t="n">
+      <c r="D186" s="7" t="n">
         <v>94.70382728876852</v>
       </c>
-      <c r="E186" s="4" t="n">
+      <c r="E186" s="7" t="n">
         <v>94.86177825927734</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="F186" s="8" t="n">
         <v>8165100</v>
       </c>
     </row>
@@ -4041,19 +4044,19 @@
       <c r="A187" s="6" t="n">
         <v>46063</v>
       </c>
-      <c r="B187" s="4" t="n">
+      <c r="B187" s="7" t="n">
         <v>95.19743371482861</v>
       </c>
-      <c r="C187" s="4" t="n">
+      <c r="C187" s="7" t="n">
         <v>95.31590258838648</v>
       </c>
-      <c r="D187" s="4" t="n">
+      <c r="D187" s="7" t="n">
         <v>95.17769266850682</v>
       </c>
-      <c r="E187" s="4" t="n">
+      <c r="E187" s="7" t="n">
         <v>95.2764129638672</v>
       </c>
-      <c r="F187" s="4" t="n">
+      <c r="F187" s="8" t="n">
         <v>9752300</v>
       </c>
     </row>
@@ -4061,19 +4064,19 @@
       <c r="A188" s="6" t="n">
         <v>46064</v>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="7" t="n">
         <v>94.95063413321699</v>
       </c>
-      <c r="C188" s="4" t="n">
+      <c r="C188" s="7" t="n">
         <v>95.21717969769664</v>
       </c>
-      <c r="D188" s="4" t="n">
+      <c r="D188" s="7" t="n">
         <v>94.93089308587176</v>
       </c>
-      <c r="E188" s="4" t="n">
+      <c r="E188" s="7" t="n">
         <v>95.00986480712891</v>
       </c>
-      <c r="F188" s="4" t="n">
+      <c r="F188" s="8" t="n">
         <v>9106600</v>
       </c>
     </row>
@@ -4081,19 +4084,19 @@
       <c r="A189" s="6" t="n">
         <v>46065</v>
       </c>
-      <c r="B189" s="4" t="n">
+      <c r="B189" s="7" t="n">
         <v>95.16781925059892</v>
       </c>
-      <c r="C189" s="4" t="n">
+      <c r="C189" s="7" t="n">
         <v>95.61206434972516</v>
       </c>
-      <c r="D189" s="4" t="n">
+      <c r="D189" s="7" t="n">
         <v>95.15794496140975</v>
       </c>
-      <c r="E189" s="4" t="n">
+      <c r="E189" s="7" t="n">
         <v>95.59232330322266</v>
       </c>
-      <c r="F189" s="4" t="n">
+      <c r="F189" s="8" t="n">
         <v>13099900</v>
       </c>
     </row>
@@ -4101,19 +4104,19 @@
       <c r="A190" s="6" t="n">
         <v>46066</v>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B190" s="7" t="n">
         <v>95.87861462785028</v>
       </c>
-      <c r="C190" s="4" t="n">
+      <c r="C190" s="7" t="n">
         <v>96.01682454494905</v>
       </c>
-      <c r="D190" s="4" t="n">
+      <c r="D190" s="7" t="n">
         <v>95.84899176115005</v>
       </c>
-      <c r="E190" s="4" t="n">
+      <c r="E190" s="7" t="n">
         <v>95.96746063232422</v>
       </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="8" t="n">
         <v>11681500</v>
       </c>
     </row>
@@ -4121,19 +4124,19 @@
       <c r="A191" s="6" t="n">
         <v>46070</v>
       </c>
-      <c r="B191" s="4" t="n">
+      <c r="B191" s="7" t="n">
         <v>96.00695210937852</v>
       </c>
-      <c r="C191" s="4" t="n">
+      <c r="C191" s="7" t="n">
         <v>96.06618278017122</v>
       </c>
-      <c r="D191" s="4" t="n">
+      <c r="D191" s="7" t="n">
         <v>95.90823181409878</v>
       </c>
-      <c r="E191" s="4" t="n">
+      <c r="E191" s="7" t="n">
         <v>95.95758819580078</v>
       </c>
-      <c r="F191" s="4" t="n">
+      <c r="F191" s="8" t="n">
         <v>8623800</v>
       </c>
     </row>
@@ -4141,19 +4144,19 @@
       <c r="A192" s="6" t="n">
         <v>46071</v>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="7" t="n">
         <v>95.78977006171908</v>
       </c>
-      <c r="C192" s="4" t="n">
+      <c r="C192" s="7" t="n">
         <v>95.84900073691502</v>
       </c>
-      <c r="D192" s="4" t="n">
+      <c r="D192" s="7" t="n">
         <v>95.73053938652312</v>
       </c>
-      <c r="E192" s="4" t="n">
+      <c r="E192" s="7" t="n">
         <v>95.76015472412109</v>
       </c>
-      <c r="F192" s="4" t="n">
+      <c r="F192" s="8" t="n">
         <v>7778800</v>
       </c>
     </row>
@@ -4161,19 +4164,19 @@
       <c r="A193" s="6" t="n">
         <v>46072</v>
       </c>
-      <c r="B193" s="4" t="n">
+      <c r="B193" s="7" t="n">
         <v>95.72066338551508</v>
       </c>
-      <c r="C193" s="4" t="n">
+      <c r="C193" s="7" t="n">
         <v>95.89836293980252</v>
       </c>
-      <c r="D193" s="4" t="n">
+      <c r="D193" s="7" t="n">
         <v>95.70092233809476</v>
       </c>
-      <c r="E193" s="4" t="n">
+      <c r="E193" s="7" t="n">
         <v>95.8489990234375</v>
       </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="8" t="n">
         <v>4993000</v>
       </c>
     </row>
@@ -4181,19 +4184,19 @@
       <c r="A194" s="6" t="n">
         <v>46073</v>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="7" t="n">
         <v>95.88848865015429</v>
       </c>
-      <c r="C194" s="4" t="n">
+      <c r="C194" s="7" t="n">
         <v>95.89836293980252</v>
       </c>
-      <c r="D194" s="4" t="n">
+      <c r="D194" s="7" t="n">
         <v>95.65155842172976</v>
       </c>
-      <c r="E194" s="4" t="n">
+      <c r="E194" s="7" t="n">
         <v>95.8489990234375</v>
       </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="8" t="n">
         <v>11200200</v>
       </c>
     </row>
@@ -4201,19 +4204,19 @@
       <c r="A195" s="6" t="n">
         <v>46076</v>
       </c>
-      <c r="B195" s="4" t="n">
+      <c r="B195" s="7" t="n">
         <v>95.9279659797692</v>
       </c>
-      <c r="C195" s="4" t="n">
+      <c r="C195" s="7" t="n">
         <v>96.28336504278514</v>
       </c>
-      <c r="D195" s="4" t="n">
+      <c r="D195" s="7" t="n">
         <v>95.9279659797692</v>
       </c>
-      <c r="E195" s="4" t="n">
+      <c r="E195" s="7" t="n">
         <v>96.19451904296876</v>
       </c>
-      <c r="F195" s="4" t="n">
+      <c r="F195" s="8" t="n">
         <v>9862900</v>
       </c>
     </row>
@@ -4221,19 +4224,19 @@
       <c r="A196" s="6" t="n">
         <v>46077</v>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="7" t="n">
         <v>96.19453037840844</v>
       </c>
-      <c r="C196" s="4" t="n">
+      <c r="C196" s="7" t="n">
         <v>96.2340200047164</v>
       </c>
-      <c r="D196" s="4" t="n">
+      <c r="D196" s="7" t="n">
         <v>96.08593578903051</v>
       </c>
-      <c r="E196" s="4" t="n">
+      <c r="E196" s="7" t="n">
         <v>96.17478179931641</v>
       </c>
-      <c r="F196" s="4" t="n">
+      <c r="F196" s="8" t="n">
         <v>9493300</v>
       </c>
     </row>
@@ -4241,19 +4244,19 @@
       <c r="A197" s="6" t="n">
         <v>46078</v>
       </c>
-      <c r="B197" s="4" t="n">
+      <c r="B197" s="7" t="n">
         <v>96.02669734423128</v>
       </c>
-      <c r="C197" s="4" t="n">
+      <c r="C197" s="7" t="n">
         <v>96.17478155954797</v>
       </c>
-      <c r="D197" s="4" t="n">
+      <c r="D197" s="7" t="n">
         <v>96.02669734423128</v>
       </c>
-      <c r="E197" s="4" t="n">
+      <c r="E197" s="7" t="n">
         <v>96.09580230712891</v>
       </c>
-      <c r="F197" s="4" t="n">
+      <c r="F197" s="8" t="n">
         <v>8762700</v>
       </c>
     </row>
@@ -4261,19 +4264,19 @@
       <c r="A198" s="6" t="n">
         <v>46079</v>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="7" t="n">
         <v>96.17477848102703</v>
       </c>
-      <c r="C198" s="4" t="n">
+      <c r="C198" s="7" t="n">
         <v>96.35247802734376</v>
       </c>
-      <c r="D198" s="4" t="n">
+      <c r="D198" s="7" t="n">
         <v>96.17477848102703</v>
       </c>
-      <c r="E198" s="4" t="n">
+      <c r="E198" s="7" t="n">
         <v>96.35247802734376</v>
       </c>
-      <c r="F198" s="4" t="n">
+      <c r="F198" s="8" t="n">
         <v>8177300</v>
       </c>
     </row>
@@ -4281,19 +4284,19 @@
       <c r="A199" s="6" t="n">
         <v>46080</v>
       </c>
-      <c r="B199" s="4" t="n">
+      <c r="B199" s="7" t="n">
         <v>96.62890083340191</v>
       </c>
-      <c r="C199" s="4" t="n">
+      <c r="C199" s="7" t="n">
         <v>96.79673362753606</v>
       </c>
-      <c r="D199" s="4" t="n">
+      <c r="D199" s="7" t="n">
         <v>96.57954444961332</v>
       </c>
-      <c r="E199" s="4" t="n">
+      <c r="E199" s="7" t="n">
         <v>96.73749542236328</v>
       </c>
-      <c r="F199" s="4" t="n">
+      <c r="F199" s="8" t="n">
         <v>9970300</v>
       </c>
     </row>
@@ -4301,19 +4304,19 @@
       <c r="A200" s="6" t="n">
         <v>46083</v>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="7" t="n">
         <v>96.41373334683392</v>
       </c>
-      <c r="C200" s="4" t="n">
+      <c r="C200" s="7" t="n">
         <v>96.42363623574974</v>
       </c>
-      <c r="D200" s="4" t="n">
+      <c r="D200" s="7" t="n">
         <v>95.98799976774596</v>
       </c>
-      <c r="E200" s="4" t="n">
+      <c r="E200" s="7" t="n">
         <v>96.15631866455078</v>
       </c>
-      <c r="F200" s="4" t="n">
+      <c r="F200" s="8" t="n">
         <v>17709600</v>
       </c>
     </row>
@@ -4321,19 +4324,19 @@
       <c r="A201" s="6" t="n">
         <v>46084</v>
       </c>
-      <c r="B201" s="4" t="n">
+      <c r="B201" s="7" t="n">
         <v>95.71078642207044</v>
       </c>
-      <c r="C201" s="4" t="n">
+      <c r="C201" s="7" t="n">
         <v>96.18602692737238</v>
       </c>
-      <c r="D201" s="4" t="n">
+      <c r="D201" s="7" t="n">
         <v>95.68108530680622</v>
       </c>
-      <c r="E201" s="4" t="n">
+      <c r="E201" s="7" t="n">
         <v>96.04741668701172</v>
       </c>
-      <c r="F201" s="4" t="n">
+      <c r="F201" s="8" t="n">
         <v>13708500</v>
       </c>
     </row>
@@ -4341,19 +4344,19 @@
       <c r="A202" s="6" t="n">
         <v>46085</v>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="7" t="n">
         <v>96.00781177011282</v>
       </c>
-      <c r="C202" s="4" t="n">
+      <c r="C202" s="7" t="n">
         <v>96.02760999553703</v>
       </c>
-      <c r="D202" s="4" t="n">
+      <c r="D202" s="7" t="n">
         <v>95.82959752652891</v>
       </c>
-      <c r="E202" s="4" t="n">
+      <c r="E202" s="7" t="n">
         <v>95.84939575195312</v>
       </c>
-      <c r="F202" s="4" t="n">
+      <c r="F202" s="8" t="n">
         <v>12535500</v>
       </c>
     </row>
@@ -4361,19 +4364,19 @@
       <c r="A203" s="6" t="n">
         <v>46086</v>
       </c>
-      <c r="B203" s="4" t="n">
+      <c r="B203" s="7" t="n">
         <v>95.49295838593072</v>
       </c>
-      <c r="C203" s="4" t="n">
+      <c r="C203" s="7" t="n">
         <v>95.62167327714056</v>
       </c>
-      <c r="D203" s="4" t="n">
+      <c r="D203" s="7" t="n">
         <v>95.43355616148976</v>
       </c>
-      <c r="E203" s="4" t="n">
+      <c r="E203" s="7" t="n">
         <v>95.5523681640625</v>
       </c>
-      <c r="F203" s="4" t="n">
+      <c r="F203" s="8" t="n">
         <v>12599700</v>
       </c>
     </row>
@@ -4381,19 +4384,19 @@
       <c r="A204" s="6" t="n">
         <v>46087</v>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="7" t="n">
         <v>95.2652521179876</v>
       </c>
-      <c r="C204" s="4" t="n">
+      <c r="C204" s="7" t="n">
         <v>95.78008906117785</v>
       </c>
-      <c r="D204" s="4" t="n">
+      <c r="D204" s="7" t="n">
         <v>95.21574522470196</v>
       </c>
-      <c r="E204" s="4" t="n">
+      <c r="E204" s="7" t="n">
         <v>95.4929656982422</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="F204" s="8" t="n">
         <v>12758200</v>
       </c>
     </row>
@@ -4401,19 +4404,19 @@
       <c r="A205" s="6" t="n">
         <v>46090</v>
       </c>
-      <c r="B205" s="4" t="n">
+      <c r="B205" s="7" t="n">
         <v>95.4038560862932</v>
       </c>
-      <c r="C205" s="4" t="n">
+      <c r="C205" s="7" t="n">
         <v>95.83949254677108</v>
       </c>
-      <c r="D205" s="4" t="n">
+      <c r="D205" s="7" t="n">
         <v>95.29494697117374</v>
       </c>
-      <c r="E205" s="4" t="n">
+      <c r="E205" s="7" t="n">
         <v>95.78998565673828</v>
       </c>
-      <c r="F205" s="4" t="n">
+      <c r="F205" s="8" t="n">
         <v>12134400</v>
       </c>
     </row>
@@ -4421,19 +4424,19 @@
       <c r="A206" s="6" t="n">
         <v>46091</v>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="7" t="n">
         <v>95.74048506831424</v>
       </c>
-      <c r="C206" s="4" t="n">
+      <c r="C206" s="7" t="n">
         <v>95.80979018670727</v>
       </c>
-      <c r="D206" s="4" t="n">
+      <c r="D206" s="7" t="n">
         <v>95.4533692590369</v>
       </c>
-      <c r="E206" s="4" t="n">
+      <c r="E206" s="7" t="n">
         <v>95.48307037353516</v>
       </c>
-      <c r="F206" s="4" t="n">
+      <c r="F206" s="8" t="n">
         <v>10571300</v>
       </c>
     </row>
@@ -4441,19 +4444,19 @@
       <c r="A207" s="6" t="n">
         <v>46092</v>
       </c>
-      <c r="B207" s="4" t="n">
+      <c r="B207" s="7" t="n">
         <v>95.30484653896325</v>
       </c>
-      <c r="C207" s="4" t="n">
+      <c r="C207" s="7" t="n">
         <v>95.35434587358031</v>
       </c>
-      <c r="D207" s="4" t="n">
+      <c r="D207" s="7" t="n">
         <v>95.02762609329754</v>
       </c>
-      <c r="E207" s="4" t="n">
+      <c r="E207" s="7" t="n">
         <v>95.04742431640624</v>
       </c>
-      <c r="F207" s="4" t="n">
+      <c r="F207" s="8" t="n">
         <v>12197600</v>
       </c>
     </row>
@@ -4461,19 +4464,19 @@
       <c r="A208" s="6" t="n">
         <v>46093</v>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="7" t="n">
         <v>94.89891748963493</v>
       </c>
-      <c r="C208" s="4" t="n">
+      <c r="C208" s="7" t="n">
         <v>95.02763238628256</v>
       </c>
-      <c r="D208" s="4" t="n">
+      <c r="D208" s="7" t="n">
         <v>94.64149525003074</v>
       </c>
-      <c r="E208" s="4" t="n">
+      <c r="E208" s="7" t="n">
         <v>94.74050903320312</v>
       </c>
-      <c r="F208" s="4" t="n">
+      <c r="F208" s="8" t="n">
         <v>11401400</v>
       </c>
     </row>
@@ -4481,19 +4484,19 @@
       <c r="A209" s="6" t="n">
         <v>46094</v>
       </c>
-      <c r="B209" s="4" t="n">
+      <c r="B209" s="7" t="n">
         <v>94.88902174956804</v>
       </c>
-      <c r="C209" s="4" t="n">
+      <c r="C209" s="7" t="n">
         <v>94.97813265039862</v>
       </c>
-      <c r="D209" s="4" t="n">
+      <c r="D209" s="7" t="n">
         <v>94.60190592854828</v>
       </c>
-      <c r="E209" s="4" t="n">
+      <c r="E209" s="7" t="n">
         <v>94.64150238037109</v>
       </c>
-      <c r="F209" s="4" t="n">
+      <c r="F209" s="8" t="n">
         <v>11839700</v>
       </c>
     </row>
@@ -4501,19 +4504,19 @@
       <c r="A210" s="6" t="n">
         <v>46097</v>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="7" t="n">
         <v>95.02764140140783</v>
       </c>
-      <c r="C210" s="4" t="n">
+      <c r="C210" s="7" t="n">
         <v>95.10684186029179</v>
       </c>
-      <c r="D210" s="4" t="n">
+      <c r="D210" s="7" t="n">
         <v>94.91873227253907</v>
       </c>
-      <c r="E210" s="4" t="n">
+      <c r="E210" s="7" t="n">
         <v>95.06723785400391</v>
       </c>
-      <c r="F210" s="4" t="n">
+      <c r="F210" s="8" t="n">
         <v>9092100</v>
       </c>
     </row>
@@ -4521,19 +4524,19 @@
       <c r="A211" s="6" t="n">
         <v>46098</v>
       </c>
-      <c r="B211" s="4" t="n">
+      <c r="B211" s="7" t="n">
         <v>95.21574414819094</v>
       </c>
-      <c r="C211" s="4" t="n">
+      <c r="C211" s="7" t="n">
         <v>95.3246532692349</v>
       </c>
-      <c r="D211" s="4" t="n">
+      <c r="D211" s="7" t="n">
         <v>95.17614014474847</v>
       </c>
-      <c r="E211" s="4" t="n">
+      <c r="E211" s="7" t="n">
         <v>95.2355499267578</v>
       </c>
-      <c r="F211" s="4" t="n">
+      <c r="F211" s="8" t="n">
         <v>7209700</v>
       </c>
     </row>
@@ -4541,19 +4544,19 @@
       <c r="A212" s="6" t="n">
         <v>46099</v>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="7" t="n">
         <v>95.09693774190676</v>
       </c>
-      <c r="C212" s="4" t="n">
+      <c r="C212" s="7" t="n">
         <v>95.1662428580874</v>
       </c>
-      <c r="D212" s="4" t="n">
+      <c r="D212" s="7" t="n">
         <v>94.78011327455376</v>
       </c>
-      <c r="E212" s="4" t="n">
+      <c r="E212" s="7" t="n">
         <v>94.79991149902344</v>
       </c>
-      <c r="F212" s="4" t="n">
+      <c r="F212" s="8" t="n">
         <v>13048700</v>
       </c>
     </row>
@@ -4561,19 +4564,19 @@
       <c r="A213" s="6" t="n">
         <v>46100</v>
       </c>
-      <c r="B213" s="4" t="n">
+      <c r="B213" s="7" t="n">
         <v>94.54248158444692</v>
       </c>
-      <c r="C213" s="4" t="n">
+      <c r="C213" s="7" t="n">
         <v>94.92861113663714</v>
       </c>
-      <c r="D213" s="4" t="n">
+      <c r="D213" s="7" t="n">
         <v>94.53258624986088</v>
       </c>
-      <c r="E213" s="4" t="n">
+      <c r="E213" s="7" t="n">
         <v>94.79000091552734</v>
       </c>
-      <c r="F213" s="4" t="n">
+      <c r="F213" s="8" t="n">
         <v>18464600</v>
       </c>
     </row>
@@ -4581,19 +4584,19 @@
       <c r="A214" s="6" t="n">
         <v>46101</v>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="7" t="n">
         <v>94.3642788303888</v>
       </c>
-      <c r="C214" s="4" t="n">
+      <c r="C214" s="7" t="n">
         <v>94.39397994513703</v>
       </c>
-      <c r="D214" s="4" t="n">
+      <c r="D214" s="7" t="n">
         <v>93.90884411230256</v>
       </c>
-      <c r="E214" s="4" t="n">
+      <c r="E214" s="7" t="n">
         <v>93.93854522705078</v>
       </c>
-      <c r="F214" s="4" t="n">
+      <c r="F214" s="8" t="n">
         <v>20761500</v>
       </c>
     </row>
@@ -4601,19 +4604,19 @@
       <c r="A215" s="6" t="n">
         <v>46104</v>
       </c>
-      <c r="B215" s="4" t="n">
+      <c r="B215" s="7" t="n">
         <v>94.05735095527346</v>
       </c>
-      <c r="C215" s="4" t="n">
+      <c r="C215" s="7" t="n">
         <v>94.48308453016602</v>
       </c>
-      <c r="D215" s="4" t="n">
+      <c r="D215" s="7" t="n">
         <v>93.94844183934576</v>
       </c>
-      <c r="E215" s="4" t="n">
+      <c r="E215" s="7" t="n">
         <v>94.23556518554688</v>
       </c>
-      <c r="F215" s="4" t="n">
+      <c r="F215" s="8" t="n">
         <v>28336300</v>
       </c>
     </row>
@@ -4621,19 +4624,19 @@
       <c r="A216" s="6" t="n">
         <v>46105</v>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="7" t="n">
         <v>93.84944182930532</v>
       </c>
-      <c r="C216" s="4" t="n">
+      <c r="C216" s="7" t="n">
         <v>94.13656519452698</v>
       </c>
-      <c r="D216" s="4" t="n">
+      <c r="D216" s="7" t="n">
         <v>93.68113047670032</v>
       </c>
-      <c r="E216" s="4" t="n">
+      <c r="E216" s="7" t="n">
         <v>93.9187469482422</v>
       </c>
-      <c r="F216" s="4" t="n">
+      <c r="F216" s="8" t="n">
         <v>19785600</v>
       </c>
     </row>
@@ -4641,19 +4644,19 @@
       <c r="A217" s="6" t="n">
         <v>46106</v>
       </c>
-      <c r="B217" s="4" t="n">
+      <c r="B217" s="7" t="n">
         <v>94.34447509747189</v>
       </c>
-      <c r="C217" s="4" t="n">
+      <c r="C217" s="7" t="n">
         <v>94.45338421431846</v>
       </c>
-      <c r="D217" s="4" t="n">
+      <c r="D217" s="7" t="n">
         <v>94.19596197870921</v>
       </c>
-      <c r="E217" s="4" t="n">
+      <c r="E217" s="7" t="n">
         <v>94.41378021240234</v>
       </c>
-      <c r="F217" s="4" t="n">
+      <c r="F217" s="8" t="n">
         <v>15939200</v>
       </c>
     </row>
@@ -4661,19 +4664,19 @@
       <c r="A218" s="6" t="n">
         <v>46107</v>
       </c>
-      <c r="B218" s="4" t="n">
+      <c r="B218" s="7" t="n">
         <v>94.06725119190808</v>
       </c>
-      <c r="C218" s="4" t="n">
+      <c r="C218" s="7" t="n">
         <v>94.18605563961344</v>
       </c>
-      <c r="D218" s="4" t="n">
+      <c r="D218" s="7" t="n">
         <v>93.6514129638672</v>
       </c>
-      <c r="E218" s="4" t="n">
+      <c r="E218" s="7" t="n">
         <v>93.6514129638672</v>
       </c>
-      <c r="F218" s="4" t="n">
+      <c r="F218" s="8" t="n">
         <v>12897300</v>
       </c>
     </row>
@@ -4681,19 +4684,19 @@
       <c r="A219" s="6" t="n">
         <v>46108</v>
       </c>
-      <c r="B219" s="4" t="n">
+      <c r="B219" s="7" t="n">
         <v>93.43360996809255</v>
       </c>
-      <c r="C219" s="4" t="n">
+      <c r="C219" s="7" t="n">
         <v>93.83953778725363</v>
       </c>
-      <c r="D219" s="4" t="n">
+      <c r="D219" s="7" t="n">
         <v>93.42370707873994</v>
       </c>
-      <c r="E219" s="4" t="n">
+      <c r="E219" s="7" t="n">
         <v>93.66132354736328</v>
       </c>
-      <c r="F219" s="4" t="n">
+      <c r="F219" s="8" t="n">
         <v>11401900</v>
       </c>
     </row>
@@ -4701,19 +4704,19 @@
       <c r="A220" s="6" t="n">
         <v>46111</v>
       </c>
-      <c r="B220" s="4" t="n">
+      <c r="B220" s="7" t="n">
         <v>94.2553637696668</v>
       </c>
-      <c r="C220" s="4" t="n">
+      <c r="C220" s="7" t="n">
         <v>94.44348088947729</v>
       </c>
-      <c r="D220" s="4" t="n">
+      <c r="D220" s="7" t="n">
         <v>94.18605865505624</v>
       </c>
-      <c r="E220" s="4" t="n">
+      <c r="E220" s="7" t="n">
         <v>94.32466888427734</v>
       </c>
-      <c r="F220" s="4" t="n">
+      <c r="F220" s="8" t="n">
         <v>15430000</v>
       </c>
     </row>
@@ -4721,19 +4724,19 @@
       <c r="A221" s="6" t="n">
         <v>46112</v>
       </c>
-      <c r="B221" s="4" t="n">
+      <c r="B221" s="7" t="n">
         <v>94.59199481475844</v>
       </c>
-      <c r="C221" s="4" t="n">
+      <c r="C221" s="7" t="n">
         <v>94.73060504516241</v>
       </c>
-      <c r="D221" s="4" t="n">
+      <c r="D221" s="7" t="n">
         <v>94.40387769334264</v>
       </c>
-      <c r="E221" s="4" t="n">
+      <c r="E221" s="7" t="n">
         <v>94.49298858642578</v>
       </c>
-      <c r="F221" s="4" t="n">
+      <c r="F221" s="8" t="n">
         <v>18649700</v>
       </c>
     </row>
@@ -4741,19 +4744,19 @@
       <c r="A222" s="6" t="n">
         <v>46113</v>
       </c>
-      <c r="B222" s="4" t="n">
+      <c r="B222" s="7" t="n">
         <v>94.45027370360532</v>
       </c>
-      <c r="C222" s="4" t="n">
+      <c r="C222" s="7" t="n">
         <v>94.6588819348209</v>
       </c>
-      <c r="D222" s="4" t="n">
+      <c r="D222" s="7" t="n">
         <v>94.39066593835518</v>
       </c>
-      <c r="E222" s="4" t="n">
+      <c r="E222" s="7" t="n">
         <v>94.41053771972656</v>
       </c>
-      <c r="F222" s="4" t="n">
+      <c r="F222" s="8" t="n">
         <v>13557600</v>
       </c>
     </row>
@@ -4761,19 +4764,19 @@
       <c r="A223" s="6" t="n">
         <v>46114</v>
       </c>
-      <c r="B223" s="4" t="n">
+      <c r="B223" s="7" t="n">
         <v>94.40060171376628</v>
       </c>
-      <c r="C223" s="4" t="n">
+      <c r="C223" s="7" t="n">
         <v>94.75821798937454</v>
       </c>
-      <c r="D223" s="4" t="n">
+      <c r="D223" s="7" t="n">
         <v>94.38073751128314</v>
       </c>
-      <c r="E223" s="4" t="n">
+      <c r="E223" s="7" t="n">
         <v>94.62908172607422</v>
       </c>
-      <c r="F223" s="4" t="n">
+      <c r="F223" s="8" t="n">
         <v>13171300</v>
       </c>
     </row>
@@ -4781,19 +4784,19 @@
       <c r="A224" s="6" t="n">
         <v>46118</v>
       </c>
-      <c r="B224" s="4" t="n">
+      <c r="B224" s="7" t="n">
         <v>94.37080141403568</v>
       </c>
-      <c r="C224" s="4" t="n">
+      <c r="C224" s="7" t="n">
         <v>94.5496095514484</v>
       </c>
-      <c r="D224" s="4" t="n">
+      <c r="D224" s="7" t="n">
         <v>94.2814011347613</v>
       </c>
-      <c r="E224" s="4" t="n">
+      <c r="E224" s="7" t="n">
         <v>94.3807373046875</v>
       </c>
-      <c r="F224" s="4" t="n">
+      <c r="F224" s="8" t="n">
         <v>6104900</v>
       </c>
     </row>
@@ -4801,19 +4804,19 @@
       <c r="A225" s="6" t="n">
         <v>46119</v>
       </c>
-      <c r="B225" s="4" t="n">
+      <c r="B225" s="7" t="n">
         <v>94.44034011201906</v>
       </c>
-      <c r="C225" s="4" t="n">
+      <c r="C225" s="7" t="n">
         <v>94.65888423924063</v>
       </c>
-      <c r="D225" s="4" t="n">
+      <c r="D225" s="7" t="n">
         <v>94.13239570304182</v>
       </c>
-      <c r="E225" s="4" t="n">
+      <c r="E225" s="7" t="n">
         <v>94.61914825439452</v>
       </c>
-      <c r="F225" s="4" t="n">
+      <c r="F225" s="8" t="n">
         <v>6737500</v>
       </c>
     </row>
@@ -4821,19 +4824,19 @@
       <c r="A226" s="6" t="n">
         <v>46120</v>
       </c>
-      <c r="B226" s="4" t="n">
+      <c r="B226" s="7" t="n">
         <v>95.08603890739025</v>
       </c>
-      <c r="C226" s="4" t="n">
+      <c r="C226" s="7" t="n">
         <v>95.09597479855864</v>
       </c>
-      <c r="D226" s="4" t="n">
+      <c r="D226" s="7" t="n">
         <v>94.73835850514004</v>
       </c>
-      <c r="E226" s="4" t="n">
+      <c r="E226" s="7" t="n">
         <v>94.8277587890625</v>
       </c>
-      <c r="F226" s="4" t="n">
+      <c r="F226" s="8" t="n">
         <v>12107400</v>
       </c>
     </row>
@@ -4841,19 +4844,19 @@
       <c r="A227" s="6" t="n">
         <v>46121</v>
       </c>
-      <c r="B227" s="4" t="n">
+      <c r="B227" s="7" t="n">
         <v>94.73835818494322</v>
       </c>
-      <c r="C227" s="4" t="n">
+      <c r="C227" s="7" t="n">
         <v>95.01650250580332</v>
       </c>
-      <c r="D227" s="4" t="n">
+      <c r="D227" s="7" t="n">
         <v>94.59928602451318</v>
       </c>
-      <c r="E227" s="4" t="n">
+      <c r="E227" s="7" t="n">
         <v>94.79795837402344</v>
       </c>
-      <c r="F227" s="4" t="n">
+      <c r="F227" s="8" t="n">
         <v>11065900</v>
       </c>
     </row>
@@ -4861,19 +4864,19 @@
       <c r="A228" s="6" t="n">
         <v>46122</v>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="7" t="n">
         <v>94.7979591417408</v>
       </c>
-      <c r="C228" s="4" t="n">
+      <c r="C228" s="7" t="n">
         <v>94.82775923652224</v>
       </c>
-      <c r="D228" s="4" t="n">
+      <c r="D228" s="7" t="n">
         <v>94.62908688540304</v>
       </c>
-      <c r="E228" s="4" t="n">
+      <c r="E228" s="7" t="n">
         <v>94.63901519775391</v>
       </c>
-      <c r="F228" s="4" t="n">
+      <c r="F228" s="8" t="n">
         <v>4404800</v>
       </c>
     </row>
@@ -4881,19 +4884,19 @@
       <c r="A229" s="6" t="n">
         <v>46125</v>
       </c>
-      <c r="B229" s="4" t="n">
+      <c r="B229" s="7" t="n">
         <v>94.63901753546445</v>
       </c>
-      <c r="C229" s="4" t="n">
+      <c r="C229" s="7" t="n">
         <v>94.85756167441254</v>
       </c>
-      <c r="D229" s="4" t="n">
+      <c r="D229" s="7" t="n">
         <v>94.53968135745112</v>
       </c>
-      <c r="E229" s="4" t="n">
+      <c r="E229" s="7" t="n">
         <v>94.84763336181641</v>
       </c>
-      <c r="F229" s="4" t="n">
+      <c r="F229" s="8" t="n">
         <v>4300200</v>
       </c>
     </row>
@@ -4901,19 +4904,19 @@
       <c r="A230" s="6" t="n">
         <v>46126</v>
       </c>
-      <c r="B230" s="4" t="n">
+      <c r="B230" s="7" t="n">
         <v>94.80789819778435</v>
       </c>
-      <c r="C230" s="4" t="n">
+      <c r="C230" s="7" t="n">
         <v>95.1655145048282</v>
       </c>
-      <c r="D230" s="4" t="n">
+      <c r="D230" s="7" t="n">
         <v>94.77809810200814</v>
       </c>
-      <c r="E230" s="4" t="n">
+      <c r="E230" s="7" t="n">
         <v>95.15557861328124</v>
       </c>
-      <c r="F230" s="4" t="n">
+      <c r="F230" s="8" t="n">
         <v>5239800</v>
       </c>
     </row>
@@ -4921,19 +4924,19 @@
       <c r="A231" s="6" t="n">
         <v>46127</v>
       </c>
-      <c r="B231" s="4" t="n">
+      <c r="B231" s="7" t="n">
         <v>95.05624014640566</v>
       </c>
-      <c r="C231" s="4" t="n">
+      <c r="C231" s="7" t="n">
         <v>95.06616845884901</v>
       </c>
-      <c r="D231" s="4" t="n">
+      <c r="D231" s="7" t="n">
         <v>94.86749610587984</v>
       </c>
-      <c r="E231" s="4" t="n">
+      <c r="E231" s="7" t="n">
         <v>94.94696807861328</v>
       </c>
-      <c r="F231" s="4" t="n">
+      <c r="F231" s="8" t="n">
         <v>5592900</v>
       </c>
     </row>
@@ -4941,19 +4944,19 @@
       <c r="A232" s="6" t="n">
         <v>46128</v>
       </c>
-      <c r="B232" s="4" t="n">
+      <c r="B232" s="7" t="n">
         <v>95.0363639617881</v>
       </c>
-      <c r="C232" s="4" t="n">
+      <c r="C232" s="7" t="n">
         <v>95.06616405546671</v>
       </c>
-      <c r="D232" s="4" t="n">
+      <c r="D232" s="7" t="n">
         <v>94.74828375812132</v>
       </c>
-      <c r="E232" s="4" t="n">
+      <c r="E232" s="7" t="n">
         <v>94.77809143066406</v>
       </c>
-      <c r="F232" s="4" t="n">
+      <c r="F232" s="8" t="n">
         <v>6618900</v>
       </c>
     </row>
@@ -4961,19 +4964,19 @@
       <c r="A233" s="6" t="n">
         <v>46129</v>
       </c>
-      <c r="B233" s="4" t="n">
+      <c r="B233" s="7" t="n">
         <v>95.25490360474603</v>
       </c>
-      <c r="C233" s="4" t="n">
+      <c r="C233" s="7" t="n">
         <v>95.4138475353712</v>
       </c>
-      <c r="D233" s="4" t="n">
+      <c r="D233" s="7" t="n">
         <v>95.20523173170974</v>
       </c>
-      <c r="E233" s="4" t="n">
+      <c r="E233" s="7" t="n">
         <v>95.29463958740234</v>
       </c>
-      <c r="F233" s="4" t="n">
+      <c r="F233" s="8" t="n">
         <v>6912900</v>
       </c>
     </row>
@@ -4981,19 +4984,19 @@
       <c r="A234" s="6" t="n">
         <v>46132</v>
       </c>
-      <c r="B234" s="4" t="n">
+      <c r="B234" s="7" t="n">
         <v>95.27478200091024</v>
       </c>
-      <c r="C234" s="4" t="n">
+      <c r="C234" s="7" t="n">
         <v>95.28471031311588</v>
       </c>
-      <c r="D234" s="4" t="n">
+      <c r="D234" s="7" t="n">
         <v>95.07610207383344</v>
       </c>
-      <c r="E234" s="4" t="n">
+      <c r="E234" s="7" t="n">
         <v>95.20523834228516</v>
       </c>
-      <c r="F234" s="4" t="n">
+      <c r="F234" s="8" t="n">
         <v>3868800</v>
       </c>
     </row>
@@ -5001,19 +5004,19 @@
       <c r="A235" s="6" t="n">
         <v>46133</v>
       </c>
-      <c r="B235" s="4" t="n">
+      <c r="B235" s="7" t="n">
         <v>95.05623326679658</v>
       </c>
-      <c r="C235" s="4" t="n">
+      <c r="C235" s="7" t="n">
         <v>95.11583345260092</v>
       </c>
-      <c r="D235" s="4" t="n">
+      <c r="D235" s="7" t="n">
         <v>94.77808896122444</v>
       </c>
-      <c r="E235" s="4" t="n">
+      <c r="E235" s="7" t="n">
         <v>94.78801727294922</v>
       </c>
-      <c r="F235" s="4" t="n">
+      <c r="F235" s="8" t="n">
         <v>4872900</v>
       </c>
     </row>
@@ -5021,19 +5024,19 @@
       <c r="A236" s="6" t="n">
         <v>46134</v>
       </c>
-      <c r="B236" s="4" t="n">
+      <c r="B236" s="7" t="n">
         <v>95.04629592127652</v>
       </c>
-      <c r="C236" s="4" t="n">
+      <c r="C236" s="7" t="n">
         <v>95.07609601372251</v>
       </c>
-      <c r="D236" s="4" t="n">
+      <c r="D236" s="7" t="n">
         <v>94.86748778773668</v>
       </c>
-      <c r="E236" s="4" t="n">
+      <c r="E236" s="7" t="n">
         <v>94.88735198974609</v>
       </c>
-      <c r="F236" s="4" t="n">
+      <c r="F236" s="8" t="n">
         <v>4121400</v>
       </c>
     </row>
@@ -5041,19 +5044,19 @@
       <c r="A237" s="6" t="n">
         <v>46135</v>
       </c>
-      <c r="B237" s="4" t="n">
+      <c r="B237" s="7" t="n">
         <v>94.92709400104378</v>
       </c>
-      <c r="C237" s="4" t="n">
+      <c r="C237" s="7" t="n">
         <v>94.99663008078832</v>
       </c>
-      <c r="D237" s="4" t="n">
+      <c r="D237" s="7" t="n">
         <v>94.55954939905016</v>
       </c>
-      <c r="E237" s="4" t="n">
+      <c r="E237" s="7" t="n">
         <v>94.73835754394533</v>
       </c>
-      <c r="F237" s="4" t="n">
+      <c r="F237" s="8" t="n">
         <v>6795600</v>
       </c>
     </row>
@@ -5061,19 +5064,19 @@
       <c r="A238" s="6" t="n">
         <v>46136</v>
       </c>
-      <c r="B238" s="4" t="n">
+      <c r="B238" s="7" t="n">
         <v>94.65888507934788</v>
       </c>
-      <c r="C238" s="4" t="n">
+      <c r="C238" s="7" t="n">
         <v>94.95689360004241</v>
       </c>
-      <c r="D238" s="4" t="n">
+      <c r="D238" s="7" t="n">
         <v>94.57941310895031</v>
       </c>
-      <c r="E238" s="4" t="n">
+      <c r="E238" s="7" t="n">
         <v>94.92709350585938</v>
       </c>
-      <c r="F238" s="4" t="n">
+      <c r="F238" s="8" t="n">
         <v>5490000</v>
       </c>
     </row>
@@ -5081,19 +5084,19 @@
       <c r="A239" s="6" t="n">
         <v>46139</v>
       </c>
-      <c r="B239" s="4" t="n">
+      <c r="B239" s="7" t="n">
         <v>94.78802147001235</v>
       </c>
-      <c r="C239" s="4" t="n">
+      <c r="C239" s="7" t="n">
         <v>94.89729353473464</v>
       </c>
-      <c r="D239" s="4" t="n">
+      <c r="D239" s="7" t="n">
         <v>94.64894931106838</v>
       </c>
-      <c r="E239" s="4" t="n">
+      <c r="E239" s="7" t="n">
         <v>94.70854949951172</v>
       </c>
-      <c r="F239" s="4" t="n">
+      <c r="F239" s="8" t="n">
         <v>4055500</v>
       </c>
     </row>
@@ -5101,19 +5104,19 @@
       <c r="A240" s="6" t="n">
         <v>46140</v>
       </c>
-      <c r="B240" s="4" t="n">
+      <c r="B240" s="7" t="n">
         <v>94.55954806655744</v>
       </c>
-      <c r="C240" s="4" t="n">
+      <c r="C240" s="7" t="n">
         <v>94.6390124573855</v>
       </c>
-      <c r="D240" s="4" t="n">
+      <c r="D240" s="7" t="n">
         <v>94.4800760968652</v>
       </c>
-      <c r="E240" s="4" t="n">
+      <c r="E240" s="7" t="n">
         <v>94.61914825439452</v>
       </c>
-      <c r="F240" s="4" t="n">
+      <c r="F240" s="8" t="n">
         <v>4867700</v>
       </c>
     </row>
@@ -5121,19 +5124,19 @@
       <c r="A241" s="6" t="n">
         <v>46141</v>
       </c>
-      <c r="B241" s="4" t="n">
+      <c r="B241" s="7" t="n">
         <v>94.4005991973732</v>
       </c>
-      <c r="C241" s="4" t="n">
+      <c r="C241" s="7" t="n">
         <v>94.4005991973732</v>
       </c>
-      <c r="D241" s="4" t="n">
+      <c r="D241" s="7" t="n">
         <v>94.07278302366008</v>
       </c>
-      <c r="E241" s="4" t="n">
+      <c r="E241" s="7" t="n">
         <v>94.17212677001952</v>
       </c>
-      <c r="F241" s="4" t="n">
+      <c r="F241" s="8" t="n">
         <v>7200300</v>
       </c>
     </row>
@@ -5141,19 +5144,19 @@
       <c r="A242" s="6" t="n">
         <v>46142</v>
       </c>
-      <c r="B242" s="4" t="n">
+      <c r="B242" s="7" t="n">
         <v>94.410537075628</v>
       </c>
-      <c r="C242" s="4" t="n">
+      <c r="C242" s="7" t="n">
         <v>94.46020137098964</v>
       </c>
-      <c r="D242" s="4" t="n">
+      <c r="D242" s="7" t="n">
         <v>94.24166482944329</v>
       </c>
-      <c r="E242" s="4" t="n">
+      <c r="E242" s="7" t="n">
         <v>94.35093688964844</v>
       </c>
-      <c r="F242" s="4" t="n">
+      <c r="F242" s="8" t="n">
         <v>10382400</v>
       </c>
     </row>
@@ -5161,19 +5164,19 @@
       <c r="A243" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="B243" s="4" t="n">
+      <c r="B243" s="7" t="n">
         <v>94.37287099463934</v>
       </c>
-      <c r="C243" s="4" t="n">
+      <c r="C243" s="7" t="n">
         <v>94.72169726979961</v>
       </c>
-      <c r="D243" s="4" t="n">
+      <c r="D243" s="7" t="n">
         <v>94.3031057396073</v>
       </c>
-      <c r="E243" s="4" t="n">
+      <c r="E243" s="7" t="n">
         <v>94.42269897460938</v>
       </c>
-      <c r="F243" s="4" t="n">
+      <c r="F243" s="8" t="n">
         <v>5359200</v>
       </c>
     </row>
@@ -5181,19 +5184,19 @@
       <c r="A244" s="6" t="n">
         <v>46146</v>
       </c>
-      <c r="B244" s="4" t="n">
+      <c r="B244" s="7" t="n">
         <v>94.273194915031</v>
       </c>
-      <c r="C244" s="4" t="n">
+      <c r="C244" s="7" t="n">
         <v>94.28316355204262</v>
       </c>
-      <c r="D244" s="4" t="n">
+      <c r="D244" s="7" t="n">
         <v>93.90443898786479</v>
       </c>
-      <c r="E244" s="4" t="n">
+      <c r="E244" s="7" t="n">
         <v>94.07386779785156</v>
       </c>
-      <c r="F244" s="4" t="n">
+      <c r="F244" s="8" t="n">
         <v>6593900</v>
       </c>
     </row>
@@ -5201,19 +5204,19 @@
       <c r="A245" s="6" t="n">
         <v>46147</v>
       </c>
-      <c r="B245" s="4" t="n">
+      <c r="B245" s="7" t="n">
         <v>94.18350348613215</v>
       </c>
-      <c r="C245" s="4" t="n">
+      <c r="C245" s="7" t="n">
         <v>94.32303399410053</v>
       </c>
-      <c r="D245" s="4" t="n">
+      <c r="D245" s="7" t="n">
         <v>94.1536051778307</v>
       </c>
-      <c r="E245" s="4" t="n">
+      <c r="E245" s="7" t="n">
         <v>94.21340179443359</v>
       </c>
-      <c r="F245" s="4" t="n">
+      <c r="F245" s="8" t="n">
         <v>11281600</v>
       </c>
     </row>
@@ -5221,19 +5224,19 @@
       <c r="A246" s="6" t="n">
         <v>46148</v>
       </c>
-      <c r="B246" s="4" t="n">
+      <c r="B246" s="7" t="n">
         <v>94.61205848029472</v>
       </c>
-      <c r="C246" s="4" t="n">
+      <c r="C246" s="7" t="n">
         <v>94.71172203713732</v>
       </c>
-      <c r="D246" s="4" t="n">
+      <c r="D246" s="7" t="n">
         <v>94.54229323012068</v>
       </c>
-      <c r="E246" s="4" t="n">
+      <c r="E246" s="7" t="n">
         <v>94.68182373046876</v>
       </c>
-      <c r="F246" s="4" t="n">
+      <c r="F246" s="8" t="n">
         <v>9031100</v>
       </c>
     </row>
@@ -5241,19 +5244,19 @@
       <c r="A247" s="6" t="n">
         <v>46149</v>
       </c>
-      <c r="B247" s="4" t="n">
+      <c r="B247" s="7" t="n">
         <v>94.86122648505244</v>
       </c>
-      <c r="C247" s="4" t="n">
+      <c r="C247" s="7" t="n">
         <v>94.86122648505244</v>
       </c>
-      <c r="D247" s="4" t="n">
+      <c r="D247" s="7" t="n">
         <v>94.37286970649392</v>
       </c>
-      <c r="E247" s="4" t="n">
+      <c r="E247" s="7" t="n">
         <v>94.39279937744141</v>
       </c>
-      <c r="F247" s="4" t="n">
+      <c r="F247" s="8" t="n">
         <v>5610100</v>
       </c>
     </row>
@@ -5261,19 +5264,19 @@
       <c r="A248" s="6" t="n">
         <v>46150</v>
       </c>
-      <c r="B248" s="4" t="n">
+      <c r="B248" s="7" t="n">
         <v>94.72169403388212</v>
       </c>
-      <c r="C248" s="4" t="n">
+      <c r="C248" s="7" t="n">
         <v>94.77152201214992</v>
       </c>
-      <c r="D248" s="4" t="n">
+      <c r="D248" s="7" t="n">
         <v>94.6020931991234</v>
       </c>
-      <c r="E248" s="4" t="n">
+      <c r="E248" s="7" t="n">
         <v>94.64196014404295</v>
       </c>
-      <c r="F248" s="4" t="n">
+      <c r="F248" s="8" t="n">
         <v>3215100</v>
       </c>
     </row>
@@ -5281,19 +5284,19 @@
       <c r="A249" s="6" t="n">
         <v>46153</v>
       </c>
-      <c r="B249" s="4" t="n">
+      <c r="B249" s="7" t="n">
         <v>94.54230059829504</v>
       </c>
-      <c r="C249" s="4" t="n">
+      <c r="C249" s="7" t="n">
         <v>94.56223026968</v>
       </c>
-      <c r="D249" s="4" t="n">
+      <c r="D249" s="7" t="n">
         <v>94.32303619384766</v>
       </c>
-      <c r="E249" s="4" t="n">
+      <c r="E249" s="7" t="n">
         <v>94.32303619384766</v>
       </c>
-      <c r="F249" s="4" t="n">
+      <c r="F249" s="8" t="n">
         <v>4025400</v>
       </c>
     </row>
@@ -5301,19 +5304,19 @@
       <c r="A250" s="6" t="n">
         <v>46154</v>
       </c>
-      <c r="B250" s="4" t="n">
+      <c r="B250" s="7" t="n">
         <v>94.10376817503985</v>
       </c>
-      <c r="C250" s="4" t="n">
+      <c r="C250" s="7" t="n">
         <v>94.11373681227072</v>
       </c>
-      <c r="D250" s="4" t="n">
+      <c r="D250" s="7" t="n">
         <v>93.98417494363832</v>
       </c>
-      <c r="E250" s="4" t="n">
+      <c r="E250" s="7" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F250" s="4" t="n">
+      <c r="F250" s="8" t="n">
         <v>5686700</v>
       </c>
     </row>
@@ -5321,19 +5324,19 @@
       <c r="A251" s="6" t="n">
         <v>46155</v>
       </c>
-      <c r="B251" s="4" t="n">
+      <c r="B251" s="7" t="n">
         <v>93.98417494363832</v>
       </c>
-      <c r="C251" s="4" t="n">
+      <c r="C251" s="7" t="n">
         <v>94.06390122995856</v>
       </c>
-      <c r="D251" s="4" t="n">
+      <c r="D251" s="7" t="n">
         <v>93.79480885546288</v>
       </c>
-      <c r="E251" s="4" t="n">
+      <c r="E251" s="7" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F251" s="4" t="n">
+      <c r="F251" s="8" t="n">
         <v>3459200</v>
       </c>
     </row>
@@ -5341,19 +5344,19 @@
       <c r="A252" s="6" t="n">
         <v>46156</v>
       </c>
-      <c r="B252" s="4" t="n">
+      <c r="B252" s="7" t="n">
         <v>94.22336642398864</v>
       </c>
-      <c r="C252" s="4" t="n">
+      <c r="C252" s="7" t="n">
         <v>94.24329609406108</v>
       </c>
-      <c r="D252" s="4" t="n">
+      <c r="D252" s="7" t="n">
         <v>93.93433678296461</v>
       </c>
-      <c r="E252" s="4" t="n">
+      <c r="E252" s="7" t="n">
         <v>93.94430541992188</v>
       </c>
-      <c r="F252" s="4" t="n">
+      <c r="F252" s="8" t="n">
         <v>5167300</v>
       </c>
     </row>
@@ -5361,19 +5364,19 @@
       <c r="A253" s="6" t="n">
         <v>46157</v>
       </c>
-      <c r="B253" s="4" t="n">
+      <c r="B253" s="7" t="n">
         <v>93.40611888617302</v>
       </c>
-      <c r="C253" s="4" t="n">
+      <c r="C253" s="7" t="n">
         <v>93.43601719506064</v>
       </c>
-      <c r="D253" s="4" t="n">
+      <c r="D253" s="7" t="n">
         <v>93.17688584496376</v>
       </c>
-      <c r="E253" s="4" t="n">
+      <c r="E253" s="7" t="n">
         <v>93.1968231201172</v>
       </c>
-      <c r="F253" s="4" t="n">
+      <c r="F253" s="8" t="n">
         <v>12498700</v>
       </c>
     </row>
@@ -5381,19 +5384,19 @@
       <c r="A254" s="6" t="n">
         <v>46160</v>
       </c>
-      <c r="B254" s="4" t="n">
+      <c r="B254" s="7" t="n">
         <v>93.30645104572598</v>
       </c>
-      <c r="C254" s="4" t="n">
+      <c r="C254" s="7" t="n">
         <v>93.43601291291536</v>
       </c>
-      <c r="D254" s="4" t="n">
+      <c r="D254" s="7" t="n">
         <v>93.02738243326527</v>
       </c>
-      <c r="E254" s="4" t="n">
+      <c r="E254" s="7" t="n">
         <v>93.15695190429688</v>
       </c>
-      <c r="F254" s="4" t="n">
+      <c r="F254" s="8" t="n">
         <v>8422900</v>
       </c>
     </row>
@@ -5401,19 +5404,19 @@
       <c r="A255" s="6" t="n">
         <v>46161</v>
       </c>
-      <c r="B255" s="4" t="n">
+      <c r="B255" s="7" t="n">
         <v>92.8180864086212</v>
       </c>
-      <c r="C255" s="4" t="n">
+      <c r="C255" s="7" t="n">
         <v>92.95761691252729</v>
       </c>
-      <c r="D255" s="4" t="n">
+      <c r="D255" s="7" t="n">
         <v>92.63868896019304</v>
       </c>
-      <c r="E255" s="4" t="n">
+      <c r="E255" s="7" t="n">
         <v>92.79815673828124</v>
       </c>
-      <c r="F255" s="4" t="n">
+      <c r="F255" s="8" t="n">
         <v>10069800</v>
       </c>
     </row>
@@ -5421,19 +5424,19 @@
       <c r="A256" s="6" t="n">
         <v>46162</v>
       </c>
-      <c r="B256" s="4" t="n">
+      <c r="B256" s="7" t="n">
         <v>92.85795760011084</v>
       </c>
-      <c r="C256" s="4" t="n">
+      <c r="C256" s="7" t="n">
         <v>93.49581353395244</v>
       </c>
-      <c r="D256" s="4" t="n">
+      <c r="D256" s="7" t="n">
         <v>92.8380279288594</v>
       </c>
-      <c r="E256" s="4" t="n">
+      <c r="E256" s="7" t="n">
         <v>93.42604827880859</v>
       </c>
-      <c r="F256" s="4" t="n">
+      <c r="F256" s="8" t="n">
         <v>14892500</v>
       </c>
     </row>
@@ -5441,19 +5444,19 @@
       <c r="A257" s="6" t="n">
         <v>46163</v>
       </c>
-      <c r="B257" s="4" t="n">
+      <c r="B257" s="7" t="n">
         <v>93.15695088636282</v>
       </c>
-      <c r="C257" s="4" t="n">
+      <c r="C257" s="7" t="n">
         <v>93.52570681350404</v>
       </c>
-      <c r="D257" s="4" t="n">
+      <c r="D257" s="7" t="n">
         <v>92.99748310955638</v>
       </c>
-      <c r="E257" s="4" t="n">
+      <c r="E257" s="7" t="n">
         <v>93.48584747314452</v>
       </c>
-      <c r="F257" s="4" t="n">
+      <c r="F257" s="8" t="n">
         <v>7762000</v>
       </c>
     </row>
@@ -5461,19 +5464,19 @@
       <c r="A258" s="6" t="n">
         <v>46164</v>
       </c>
-      <c r="B258" s="4" t="n">
+      <c r="B258" s="7" t="n">
         <v>93.64530853515627</v>
       </c>
-      <c r="C258" s="4" t="n">
+      <c r="C258" s="7" t="n">
         <v>93.6752068426308</v>
       </c>
-      <c r="D258" s="4" t="n">
+      <c r="D258" s="7" t="n">
         <v>93.31641194525211</v>
       </c>
-      <c r="E258" s="4" t="n">
+      <c r="E258" s="7" t="n">
         <v>93.56557464599609</v>
       </c>
-      <c r="F258" s="4" t="n">
+      <c r="F258" s="8" t="n">
         <v>6321900</v>
       </c>
     </row>
@@ -5481,19 +5484,19 @@
       <c r="A259" s="6" t="n">
         <v>46168</v>
       </c>
-      <c r="B259" s="4" t="n">
+      <c r="B259" s="7" t="n">
         <v>94.02403764567016</v>
       </c>
-      <c r="C259" s="4" t="n">
+      <c r="C259" s="7" t="n">
         <v>94.03400628325736</v>
       </c>
-      <c r="D259" s="4" t="n">
+      <c r="D259" s="7" t="n">
         <v>93.81474187939416</v>
       </c>
-      <c r="E259" s="4" t="n">
+      <c r="E259" s="7" t="n">
         <v>93.96424102783205</v>
       </c>
-      <c r="F259" s="4" t="n">
+      <c r="F259" s="8" t="n">
         <v>5494400</v>
       </c>
     </row>
@@ -5501,19 +5504,19 @@
       <c r="A260" s="6" t="n">
         <v>46169</v>
       </c>
-      <c r="B260" s="4" t="n">
+      <c r="B260" s="7" t="n">
         <v>94.0340029221082</v>
       </c>
-      <c r="C260" s="4" t="n">
+      <c r="C260" s="7" t="n">
         <v>94.16357239458289</v>
       </c>
-      <c r="D260" s="4" t="n">
+      <c r="D260" s="7" t="n">
         <v>93.97420630640744</v>
       </c>
-      <c r="E260" s="4" t="n">
+      <c r="E260" s="7" t="n">
         <v>94.0041046142578</v>
       </c>
-      <c r="F260" s="4" t="n">
+      <c r="F260" s="8" t="n">
         <v>5958800</v>
       </c>
     </row>
@@ -5521,19 +5524,19 @@
       <c r="A261" s="6" t="n">
         <v>46170</v>
       </c>
-      <c r="B261" s="4" t="n">
+      <c r="B261" s="7" t="n">
         <v>94.03399970200064</v>
       </c>
-      <c r="C261" s="4" t="n">
+      <c r="C261" s="7" t="n">
         <v>94.35292764788709</v>
       </c>
-      <c r="D261" s="4" t="n">
+      <c r="D261" s="7" t="n">
         <v>93.97420308834756</v>
       </c>
-      <c r="E261" s="4" t="n">
+      <c r="E261" s="7" t="n">
         <v>94.22336578369141</v>
       </c>
-      <c r="F261" s="4" t="n">
+      <c r="F261" s="8" t="n">
         <v>5938300</v>
       </c>
     </row>
@@ -5541,19 +5544,19 @@
       <c r="A262" s="6" t="n">
         <v>46171</v>
       </c>
-      <c r="B262" s="4" t="n">
+      <c r="B262" s="7" t="n">
         <v>94.32303154598291</v>
       </c>
-      <c r="C262" s="4" t="n">
+      <c r="C262" s="7" t="n">
         <v>94.42269510568184</v>
       </c>
-      <c r="D262" s="4" t="n">
+      <c r="D262" s="7" t="n">
         <v>94.21339934916148</v>
       </c>
-      <c r="E262" s="4" t="n">
+      <c r="E262" s="7" t="n">
         <v>94.33300018310548</v>
       </c>
-      <c r="F262" s="4" t="n">
+      <c r="F262" s="8" t="n">
         <v>9639700</v>
       </c>
     </row>
@@ -5561,19 +5564,19 @@
       <c r="A263" s="6" t="n">
         <v>46174</v>
       </c>
-      <c r="B263" s="4" t="n">
+      <c r="B263" s="7" t="n">
         <v>93.91000366210938</v>
       </c>
-      <c r="C263" s="4" t="n">
+      <c r="C263" s="7" t="n">
         <v>94.1999969482422</v>
       </c>
-      <c r="D263" s="4" t="n">
+      <c r="D263" s="7" t="n">
         <v>93.80999755859376</v>
       </c>
-      <c r="E263" s="4" t="n">
+      <c r="E263" s="7" t="n">
         <v>94.16999816894533</v>
       </c>
-      <c r="F263" s="4" t="n">
+      <c r="F263" s="8" t="n">
         <v>8054100</v>
       </c>
     </row>
@@ -5581,19 +5584,19 @@
       <c r="A264" s="6" t="n">
         <v>46175</v>
       </c>
-      <c r="B264" s="4" t="n">
+      <c r="B264" s="7" t="n">
         <v>94.33000183105467</v>
       </c>
-      <c r="C264" s="4" t="n">
+      <c r="C264" s="7" t="n">
         <v>94.33000183105467</v>
       </c>
-      <c r="D264" s="4" t="n">
+      <c r="D264" s="7" t="n">
         <v>94.16000366210938</v>
       </c>
-      <c r="E264" s="4" t="n">
+      <c r="E264" s="7" t="n">
         <v>94.23999786376952</v>
       </c>
-      <c r="F264" s="4" t="n">
+      <c r="F264" s="8" t="n">
         <v>15426600</v>
       </c>
     </row>
@@ -5601,19 +5604,19 @@
       <c r="A265" s="6" t="n">
         <v>46176</v>
       </c>
-      <c r="B265" s="4" t="n">
+      <c r="B265" s="7" t="n">
         <v>93.98999786376952</v>
       </c>
-      <c r="C265" s="4" t="n">
+      <c r="C265" s="7" t="n">
         <v>94.09999847412109</v>
       </c>
-      <c r="D265" s="4" t="n">
+      <c r="D265" s="7" t="n">
         <v>93.91000366210938</v>
       </c>
-      <c r="E265" s="4" t="n">
+      <c r="E265" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="F265" s="4" t="n">
+      <c r="F265" s="8" t="n">
         <v>7056500</v>
       </c>
     </row>
@@ -5621,19 +5624,19 @@
       <c r="A266" s="6" t="n">
         <v>46177</v>
       </c>
-      <c r="B266" s="4" t="n">
+      <c r="B266" s="7" t="n">
         <v>94.1999969482422</v>
       </c>
-      <c r="C266" s="4" t="n">
+      <c r="C266" s="7" t="n">
         <v>94.27999877929688</v>
       </c>
-      <c r="D266" s="4" t="n">
+      <c r="D266" s="7" t="n">
         <v>94.08999633789062</v>
       </c>
-      <c r="E266" s="4" t="n">
+      <c r="E266" s="7" t="n">
         <v>94.12000274658205</v>
       </c>
-      <c r="F266" s="4" t="n">
+      <c r="F266" s="8" t="n">
         <v>4417100</v>
       </c>
     </row>
